--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -3806,48 +3806,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125781666</v>
+        <v>125779848</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>98345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611652</v>
+        <v>611545</v>
       </c>
       <c r="R33" t="n">
-        <v>7203680</v>
+        <v>7203710</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,19 +3874,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780608</v>
+        <v>125781666</v>
       </c>
       <c r="B34" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3948,13 +3938,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611445</v>
+        <v>611652</v>
       </c>
       <c r="R34" t="n">
-        <v>7203816</v>
+        <v>7203680</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3978,12 +3968,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125779834</v>
+        <v>125780608</v>
       </c>
       <c r="B35" t="n">
-        <v>75066</v>
+        <v>80070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,34 +4021,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611547</v>
+        <v>611445</v>
       </c>
       <c r="R35" t="n">
-        <v>7203635</v>
+        <v>7203816</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4075,12 +4075,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,22 +4095,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125779884</v>
+        <v>125779834</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>75066</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611666</v>
+        <v>611547</v>
       </c>
       <c r="R36" t="n">
-        <v>7203678</v>
+        <v>7203635</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125780606</v>
+        <v>125779884</v>
       </c>
       <c r="B37" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611311</v>
+        <v>611666</v>
       </c>
       <c r="R37" t="n">
-        <v>7203689</v>
+        <v>7203678</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,57 +4289,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779848</v>
+        <v>125780606</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611545</v>
+        <v>611311</v>
       </c>
       <c r="R38" t="n">
-        <v>7203710</v>
+        <v>7203689</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,22 +4386,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779853</v>
+        <v>125779844</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>80099</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611691</v>
+        <v>611644</v>
       </c>
       <c r="R39" t="n">
-        <v>7203679</v>
+        <v>7203690</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779844</v>
+        <v>125779773</v>
       </c>
       <c r="B40" t="n">
-        <v>80099</v>
+        <v>80106</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611644</v>
+        <v>611662</v>
       </c>
       <c r="R40" t="n">
-        <v>7203690</v>
+        <v>7203612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,57 +4580,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779773</v>
+        <v>125779337</v>
       </c>
       <c r="B41" t="n">
-        <v>80106</v>
+        <v>78967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611662</v>
+        <v>611615</v>
       </c>
       <c r="R41" t="n">
-        <v>7203612</v>
+        <v>7203678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,22 +4677,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779337</v>
+        <v>125779319</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,34 +4700,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611615</v>
+        <v>611663</v>
       </c>
       <c r="R42" t="n">
-        <v>7203678</v>
+        <v>7203613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4760,6 +4768,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4786,7 +4799,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779319</v>
+        <v>125779316</v>
       </c>
       <c r="B43" t="n">
         <v>57651</v>
@@ -4829,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611663</v>
+        <v>611507</v>
       </c>
       <c r="R43" t="n">
-        <v>7203613</v>
+        <v>7203685</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4869,7 +4882,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4896,7 +4909,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779316</v>
+        <v>125779318</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -4939,10 +4952,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611507</v>
+        <v>611725</v>
       </c>
       <c r="R44" t="n">
-        <v>7203685</v>
+        <v>7203707</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,53 +5019,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779318</v>
+        <v>125779853</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>98345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611725</v>
+        <v>611691</v>
       </c>
       <c r="R45" t="n">
-        <v>7203707</v>
+        <v>7203679</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5087,11 +5092,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5104,12 +5104,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6035,45 +6035,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779320</v>
+        <v>125779850</v>
       </c>
       <c r="B55" t="n">
-        <v>91586</v>
+        <v>98345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611543</v>
+        <v>611637</v>
       </c>
       <c r="R55" t="n">
-        <v>7203697</v>
+        <v>7203685</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6120,60 +6120,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125781664</v>
+        <v>125776365</v>
       </c>
       <c r="B56" t="n">
-        <v>78967</v>
+        <v>98345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611539</v>
+        <v>611567</v>
       </c>
       <c r="R56" t="n">
-        <v>7203643</v>
+        <v>7203714</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6200,19 +6200,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,22 +6217,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779869</v>
+        <v>125780620</v>
       </c>
       <c r="B57" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6250,34 +6240,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611687</v>
+        <v>611381</v>
       </c>
       <c r="R57" t="n">
-        <v>7203684</v>
+        <v>7203809</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6304,12 +6299,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6324,57 +6319,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779867</v>
+        <v>125779320</v>
       </c>
       <c r="B58" t="n">
-        <v>80070</v>
+        <v>91586</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1506</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611694</v>
+        <v>611543</v>
       </c>
       <c r="R58" t="n">
-        <v>7203678</v>
+        <v>7203697</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6421,19 +6416,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779344</v>
+        <v>125781664</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -6468,13 +6463,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611653</v>
+        <v>611539</v>
       </c>
       <c r="R59" t="n">
-        <v>7203626</v>
+        <v>7203643</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6501,9 +6496,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6518,22 +6523,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779881</v>
+        <v>125779869</v>
       </c>
       <c r="B60" t="n">
-        <v>91238</v>
+        <v>80070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6541,21 +6546,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6565,10 +6570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611650</v>
+        <v>611687</v>
       </c>
       <c r="R60" t="n">
-        <v>7203647</v>
+        <v>7203684</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6627,32 +6632,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779842</v>
+        <v>125779867</v>
       </c>
       <c r="B61" t="n">
-        <v>80099</v>
+        <v>80070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6662,10 +6667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611593</v>
+        <v>611694</v>
       </c>
       <c r="R61" t="n">
-        <v>7203711</v>
+        <v>7203678</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6724,45 +6729,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779850</v>
+        <v>125779344</v>
       </c>
       <c r="B62" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611637</v>
+        <v>611653</v>
       </c>
       <c r="R62" t="n">
-        <v>7203685</v>
+        <v>7203626</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6809,44 +6814,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125776365</v>
+        <v>125779881</v>
       </c>
       <c r="B63" t="n">
-        <v>98345</v>
+        <v>91238</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6856,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611567</v>
+        <v>611650</v>
       </c>
       <c r="R63" t="n">
-        <v>7203714</v>
+        <v>7203647</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6906,62 +6911,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125780620</v>
+        <v>125779842</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611381</v>
+        <v>611593</v>
       </c>
       <c r="R64" t="n">
-        <v>7203809</v>
+        <v>7203711</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7008,22 +7008,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125779308</v>
+        <v>125781642</v>
       </c>
       <c r="B65" t="n">
-        <v>80099</v>
+        <v>56843</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7031,37 +7031,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611684</v>
+        <v>611705</v>
       </c>
       <c r="R65" t="n">
-        <v>7203690</v>
+        <v>7203676</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7088,9 +7093,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7105,22 +7120,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125781642</v>
+        <v>125779308</v>
       </c>
       <c r="B66" t="n">
-        <v>56843</v>
+        <v>80099</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7128,42 +7143,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611705</v>
+        <v>611684</v>
       </c>
       <c r="R66" t="n">
-        <v>7203676</v>
+        <v>7203690</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7190,19 +7200,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,12 +7217,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7443,45 +7443,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125776142</v>
+        <v>125779339</v>
       </c>
       <c r="B69" t="n">
-        <v>91791</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611684</v>
+        <v>611640</v>
       </c>
       <c r="R69" t="n">
-        <v>7203683</v>
+        <v>7203677</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7528,22 +7528,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125779339</v>
+        <v>125779859</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7551,34 +7551,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611640</v>
+        <v>611687</v>
       </c>
       <c r="R70" t="n">
-        <v>7203677</v>
+        <v>7203684</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,28 +7619,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779859</v>
+        <v>125779333</v>
       </c>
       <c r="B71" t="n">
-        <v>80071</v>
+        <v>91238</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7648,34 +7649,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611687</v>
+        <v>611659</v>
       </c>
       <c r="R71" t="n">
-        <v>7203684</v>
+        <v>7203648</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7716,64 +7717,63 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125779333</v>
+        <v>125776142</v>
       </c>
       <c r="B72" t="n">
-        <v>91238</v>
+        <v>91791</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611659</v>
+        <v>611684</v>
       </c>
       <c r="R72" t="n">
-        <v>7203648</v>
+        <v>7203683</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7820,12 +7820,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125781627</v>
+        <v>125779313</v>
       </c>
       <c r="B78" t="n">
-        <v>91185</v>
+        <v>98345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,21 +8328,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8352,13 +8352,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611526</v>
+        <v>611663</v>
       </c>
       <c r="R78" t="n">
-        <v>7203708</v>
+        <v>7203664</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,19 +8385,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8412,22 +8402,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779875</v>
+        <v>125779847</v>
       </c>
       <c r="B79" t="n">
-        <v>80106</v>
+        <v>98345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8435,21 +8425,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8459,10 +8449,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611687</v>
+        <v>611502</v>
       </c>
       <c r="R79" t="n">
-        <v>7203684</v>
+        <v>7203644</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8521,10 +8511,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779307</v>
+        <v>125781627</v>
       </c>
       <c r="B80" t="n">
-        <v>80099</v>
+        <v>91185</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8532,21 +8522,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8556,13 +8546,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611707</v>
+        <v>611526</v>
       </c>
       <c r="R80" t="n">
-        <v>7203701</v>
+        <v>7203708</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8589,9 +8579,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,57 +8606,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779332</v>
+        <v>125779875</v>
       </c>
       <c r="B81" t="n">
-        <v>91238</v>
+        <v>80106</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611525</v>
+        <v>611687</v>
       </c>
       <c r="R81" t="n">
-        <v>7203705</v>
+        <v>7203684</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8703,22 +8703,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779313</v>
+        <v>125779307</v>
       </c>
       <c r="B82" t="n">
-        <v>98345</v>
+        <v>80099</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611663</v>
+        <v>611707</v>
       </c>
       <c r="R82" t="n">
-        <v>7203664</v>
+        <v>7203701</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8812,45 +8812,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779847</v>
+        <v>125779332</v>
       </c>
       <c r="B83" t="n">
-        <v>98345</v>
+        <v>91238</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611502</v>
+        <v>611525</v>
       </c>
       <c r="R83" t="n">
-        <v>7203644</v>
+        <v>7203705</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,12 +8897,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125779345</v>
+        <v>125776367</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611661</v>
+        <v>611653</v>
       </c>
       <c r="R2" t="n">
-        <v>7203650</v>
+        <v>7203665</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +748,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125776148</v>
+        <v>125779334</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -816,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611660</v>
+        <v>611526</v>
       </c>
       <c r="R3" t="n">
-        <v>7203684</v>
+        <v>7203706</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125776367</v>
+        <v>125776148</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -913,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611653</v>
+        <v>611660</v>
       </c>
       <c r="R4" t="n">
-        <v>7203665</v>
+        <v>7203684</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125779334</v>
+        <v>125779345</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611526</v>
+        <v>611661</v>
       </c>
       <c r="R5" t="n">
-        <v>7203706</v>
+        <v>7203650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125781649</v>
+        <v>125781662</v>
       </c>
       <c r="B6" t="n">
-        <v>91513</v>
+        <v>91245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611536</v>
+        <v>611570</v>
       </c>
       <c r="R6" t="n">
-        <v>7203694</v>
+        <v>7203707</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125779303</v>
+        <v>125781649</v>
       </c>
       <c r="B7" t="n">
-        <v>91220</v>
+        <v>91520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611631</v>
+        <v>611536</v>
       </c>
       <c r="R7" t="n">
-        <v>7203681</v>
+        <v>7203694</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1251,9 +1251,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,22 +1278,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125781662</v>
+        <v>125779303</v>
       </c>
       <c r="B8" t="n">
-        <v>91238</v>
+        <v>91227</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,13 +1325,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611570</v>
+        <v>611631</v>
       </c>
       <c r="R8" t="n">
-        <v>7203707</v>
+        <v>7203681</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1348,19 +1358,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,12 +1375,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1601,53 +1601,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125781637</v>
+        <v>125779323</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>80098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611631</v>
+        <v>611667</v>
       </c>
       <c r="R11" t="n">
-        <v>7203695</v>
+        <v>7203673</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,19 +1669,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1701,22 +1686,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125780615</v>
+        <v>125779769</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1724,39 +1709,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611292</v>
+        <v>611696</v>
       </c>
       <c r="R12" t="n">
-        <v>7203703</v>
+        <v>7203681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,12 +1763,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,44 +1783,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779322</v>
+        <v>125781663</v>
       </c>
       <c r="B13" t="n">
-        <v>80098</v>
+        <v>78967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,13 +1830,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611700</v>
+        <v>611570</v>
       </c>
       <c r="R13" t="n">
-        <v>7203701</v>
+        <v>7203700</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1883,9 +1863,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1900,44 +1890,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125781663</v>
+        <v>125779322</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>80098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,13 +1937,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611570</v>
+        <v>611700</v>
       </c>
       <c r="R14" t="n">
-        <v>7203700</v>
+        <v>7203701</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1980,19 +1970,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2007,22 +1987,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125779769</v>
+        <v>125776139</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2030,34 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611696</v>
+        <v>611678</v>
       </c>
       <c r="R15" t="n">
-        <v>7203681</v>
+        <v>7203688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,22 +2084,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125776139</v>
+        <v>125780615</v>
       </c>
       <c r="B16" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2127,34 +2107,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611678</v>
+        <v>611292</v>
       </c>
       <c r="R16" t="n">
-        <v>7203688</v>
+        <v>7203703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,12 +2166,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,60 +2186,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125779323</v>
+        <v>125781637</v>
       </c>
       <c r="B17" t="n">
-        <v>80098</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611667</v>
+        <v>611631</v>
       </c>
       <c r="R17" t="n">
-        <v>7203673</v>
+        <v>7203695</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2281,9 +2271,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2313,7 +2313,7 @@
         <v>125779311</v>
       </c>
       <c r="B18" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>125776366</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,32 +2614,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125780622</v>
+        <v>125779338</v>
       </c>
       <c r="B21" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611490</v>
+        <v>611631</v>
       </c>
       <c r="R21" t="n">
-        <v>7203838</v>
+        <v>7203681</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2699,12 +2699,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125779338</v>
+        <v>125780607</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611631</v>
+        <v>611445</v>
       </c>
       <c r="R23" t="n">
-        <v>7203681</v>
+        <v>7203816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2893,22 +2893,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125780607</v>
+        <v>125779317</v>
       </c>
       <c r="B24" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,34 +2916,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611445</v>
+        <v>611723</v>
       </c>
       <c r="R24" t="n">
-        <v>7203816</v>
+        <v>7203703</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,12 +2978,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2990,65 +3003,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125779317</v>
+        <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>611723</v>
+        <v>611490</v>
       </c>
       <c r="R25" t="n">
-        <v>7203703</v>
+        <v>7203838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3075,17 +3080,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,22 +3100,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125781660</v>
+        <v>125776147</v>
       </c>
       <c r="B26" t="n">
-        <v>91234</v>
+        <v>78967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,37 +3123,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611570</v>
+        <v>611642</v>
       </c>
       <c r="R26" t="n">
-        <v>7203708</v>
+        <v>7203689</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3180,19 +3180,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,44 +3197,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125779886</v>
+        <v>125779763</v>
       </c>
       <c r="B27" t="n">
-        <v>91791</v>
+        <v>80099</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3254,10 +3244,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611704</v>
+        <v>611644</v>
       </c>
       <c r="R27" t="n">
-        <v>7203679</v>
+        <v>7203694</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3304,19 +3294,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125779763</v>
+        <v>125779838</v>
       </c>
       <c r="B28" t="n">
         <v>80099</v>
@@ -3351,10 +3341,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611644</v>
+        <v>611513</v>
       </c>
       <c r="R28" t="n">
-        <v>7203694</v>
+        <v>7203698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,60 +3391,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125779838</v>
+        <v>125781660</v>
       </c>
       <c r="B29" t="n">
-        <v>80099</v>
+        <v>91241</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611513</v>
+        <v>611570</v>
       </c>
       <c r="R29" t="n">
-        <v>7203698</v>
+        <v>7203708</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3481,9 +3471,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3498,57 +3498,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125776147</v>
+        <v>125779886</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>91798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611642</v>
+        <v>611704</v>
       </c>
       <c r="R30" t="n">
-        <v>7203689</v>
+        <v>7203679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3595,57 +3595,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125779767</v>
+        <v>125780614</v>
       </c>
       <c r="B31" t="n">
-        <v>98345</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611673</v>
+        <v>611292</v>
       </c>
       <c r="R31" t="n">
-        <v>7203670</v>
+        <v>7203687</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3672,12 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3692,62 +3697,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125780614</v>
+        <v>125779767</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611292</v>
+        <v>611673</v>
       </c>
       <c r="R32" t="n">
-        <v>7203687</v>
+        <v>7203670</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,44 +3794,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779848</v>
+        <v>125779834</v>
       </c>
       <c r="B33" t="n">
-        <v>98345</v>
+        <v>75066</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611545</v>
+        <v>611547</v>
       </c>
       <c r="R33" t="n">
-        <v>7203710</v>
+        <v>7203635</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,14 +4003,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125780608</v>
+        <v>125780606</v>
       </c>
       <c r="B35" t="n">
         <v>80070</v>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611445</v>
+        <v>611311</v>
       </c>
       <c r="R35" t="n">
-        <v>7203816</v>
+        <v>7203689</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125779834</v>
+        <v>125779884</v>
       </c>
       <c r="B36" t="n">
-        <v>75066</v>
+        <v>78967</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611547</v>
+        <v>611666</v>
       </c>
       <c r="R36" t="n">
-        <v>7203635</v>
+        <v>7203678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779884</v>
+        <v>125780608</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611666</v>
+        <v>611445</v>
       </c>
       <c r="R37" t="n">
-        <v>7203678</v>
+        <v>7203816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,57 +4289,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125780606</v>
+        <v>125779848</v>
       </c>
       <c r="B38" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611311</v>
+        <v>611545</v>
       </c>
       <c r="R38" t="n">
-        <v>7203689</v>
+        <v>7203710</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,57 +4386,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779844</v>
+        <v>125779319</v>
       </c>
       <c r="B39" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611644</v>
+        <v>611663</v>
       </c>
       <c r="R39" t="n">
-        <v>7203690</v>
+        <v>7203613</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4471,6 +4479,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4483,57 +4496,65 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779773</v>
+        <v>125779316</v>
       </c>
       <c r="B40" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611662</v>
+        <v>611507</v>
       </c>
       <c r="R40" t="n">
-        <v>7203612</v>
+        <v>7203685</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4568,6 +4589,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4580,22 +4606,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779337</v>
+        <v>125779318</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,34 +4629,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611615</v>
+        <v>611725</v>
       </c>
       <c r="R41" t="n">
-        <v>7203678</v>
+        <v>7203707</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4663,6 +4697,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4689,53 +4728,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779319</v>
+        <v>125779853</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611663</v>
+        <v>611691</v>
       </c>
       <c r="R42" t="n">
-        <v>7203613</v>
+        <v>7203679</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4770,11 +4801,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4787,65 +4813,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779316</v>
+        <v>125779773</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>80106</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611507</v>
+        <v>611662</v>
       </c>
       <c r="R43" t="n">
-        <v>7203685</v>
+        <v>7203612</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4880,11 +4898,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4897,22 +4910,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779318</v>
+        <v>125779337</v>
       </c>
       <c r="B44" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,42 +4933,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611725</v>
+        <v>611615</v>
       </c>
       <c r="R44" t="n">
-        <v>7203707</v>
+        <v>7203678</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4988,11 +4993,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779853</v>
+        <v>125779844</v>
       </c>
       <c r="B45" t="n">
-        <v>98345</v>
+        <v>80099</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611691</v>
+        <v>611644</v>
       </c>
       <c r="R45" t="n">
-        <v>7203679</v>
+        <v>7203690</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5116,53 +5116,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125779346</v>
+        <v>125776134</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>611666</v>
+        <v>611647</v>
       </c>
       <c r="R46" t="n">
-        <v>7203652</v>
+        <v>7203694</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5197,11 +5189,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5214,22 +5201,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125781648</v>
+        <v>125779346</v>
       </c>
       <c r="B47" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5237,37 +5224,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>611683</v>
+        <v>611666</v>
       </c>
       <c r="R47" t="n">
-        <v>7203710</v>
+        <v>7203652</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5294,19 +5289,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5321,60 +5311,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125776134</v>
+        <v>125781648</v>
       </c>
       <c r="B48" t="n">
-        <v>80099</v>
+        <v>80071</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>611647</v>
+        <v>611683</v>
       </c>
       <c r="R48" t="n">
-        <v>7203694</v>
+        <v>7203710</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5401,9 +5391,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5418,68 +5418,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125779863</v>
+        <v>125781628</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>91192</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611623</v>
+        <v>611568</v>
       </c>
       <c r="R49" t="n">
-        <v>7203692</v>
+        <v>7203718</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5506,14 +5498,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5528,44 +5525,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779309</v>
+        <v>125779315</v>
       </c>
       <c r="B50" t="n">
-        <v>80099</v>
+        <v>80071</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5575,10 +5572,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611679</v>
+        <v>611617</v>
       </c>
       <c r="R50" t="n">
-        <v>7203682</v>
+        <v>7203677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5637,48 +5634,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125781628</v>
+        <v>125779863</v>
       </c>
       <c r="B51" t="n">
-        <v>91185</v>
+        <v>57651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611568</v>
+        <v>611623</v>
       </c>
       <c r="R51" t="n">
-        <v>7203718</v>
+        <v>7203692</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5705,19 +5710,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:19</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5732,44 +5732,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779315</v>
+        <v>125779309</v>
       </c>
       <c r="B52" t="n">
-        <v>80071</v>
+        <v>80099</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611617</v>
+        <v>611679</v>
       </c>
       <c r="R52" t="n">
-        <v>7203677</v>
+        <v>7203682</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,45 +5841,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779876</v>
+        <v>125779343</v>
       </c>
       <c r="B53" t="n">
-        <v>80106</v>
+        <v>78967</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611661</v>
+        <v>611670</v>
       </c>
       <c r="R53" t="n">
-        <v>7203604</v>
+        <v>7203656</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5926,57 +5926,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779343</v>
+        <v>125779876</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>80106</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611670</v>
+        <v>611661</v>
       </c>
       <c r="R54" t="n">
-        <v>7203656</v>
+        <v>7203604</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
         <v>125779850</v>
       </c>
       <c r="B55" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>125776365</v>
       </c>
       <c r="B56" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6229,50 +6229,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125780620</v>
+        <v>125779842</v>
       </c>
       <c r="B57" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611381</v>
+        <v>611593</v>
       </c>
       <c r="R57" t="n">
-        <v>7203809</v>
+        <v>7203711</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6299,12 +6294,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6319,44 +6314,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779320</v>
+        <v>125781664</v>
       </c>
       <c r="B58" t="n">
-        <v>91586</v>
+        <v>78967</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6366,13 +6361,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611543</v>
+        <v>611539</v>
       </c>
       <c r="R58" t="n">
-        <v>7203697</v>
+        <v>7203643</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6399,9 +6394,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6416,22 +6421,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125781664</v>
+        <v>125779867</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6439,37 +6444,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611539</v>
+        <v>611694</v>
       </c>
       <c r="R59" t="n">
-        <v>7203643</v>
+        <v>7203678</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6496,19 +6501,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6523,12 +6518,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6632,10 +6627,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779867</v>
+        <v>125779344</v>
       </c>
       <c r="B61" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6643,34 +6638,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611694</v>
+        <v>611653</v>
       </c>
       <c r="R61" t="n">
-        <v>7203678</v>
+        <v>7203626</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6717,22 +6712,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779344</v>
+        <v>125780620</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6740,34 +6735,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611653</v>
+        <v>611381</v>
       </c>
       <c r="R62" t="n">
-        <v>7203626</v>
+        <v>7203809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,57 +6814,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779881</v>
+        <v>125779320</v>
       </c>
       <c r="B63" t="n">
-        <v>91238</v>
+        <v>91593</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611650</v>
+        <v>611543</v>
       </c>
       <c r="R63" t="n">
-        <v>7203647</v>
+        <v>7203697</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,44 +6911,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125779842</v>
+        <v>125779881</v>
       </c>
       <c r="B64" t="n">
-        <v>80099</v>
+        <v>91245</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611593</v>
+        <v>611650</v>
       </c>
       <c r="R64" t="n">
-        <v>7203711</v>
+        <v>7203647</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7540,45 +7540,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125779859</v>
+        <v>125776142</v>
       </c>
       <c r="B70" t="n">
-        <v>80071</v>
+        <v>91798</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611687</v>
+        <v>611684</v>
       </c>
       <c r="R70" t="n">
-        <v>7203684</v>
+        <v>7203683</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,29 +7619,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779333</v>
+        <v>125779859</v>
       </c>
       <c r="B71" t="n">
-        <v>91238</v>
+        <v>80071</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7649,34 +7648,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611659</v>
+        <v>611687</v>
       </c>
       <c r="R71" t="n">
-        <v>7203648</v>
+        <v>7203684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,63 +7716,64 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125776142</v>
+        <v>125779333</v>
       </c>
       <c r="B72" t="n">
-        <v>91791</v>
+        <v>91245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>760</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611684</v>
+        <v>611659</v>
       </c>
       <c r="R72" t="n">
-        <v>7203683</v>
+        <v>7203648</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7820,44 +7820,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779312</v>
+        <v>125779340</v>
       </c>
       <c r="B73" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611683</v>
+        <v>611680</v>
       </c>
       <c r="R73" t="n">
-        <v>7203677</v>
+        <v>7203713</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7929,45 +7929,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779310</v>
+        <v>125779771</v>
       </c>
       <c r="B74" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611700</v>
+        <v>611686</v>
       </c>
       <c r="R74" t="n">
-        <v>7203703</v>
+        <v>7203685</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,22 +8014,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779771</v>
+        <v>125779880</v>
       </c>
       <c r="B75" t="n">
-        <v>80070</v>
+        <v>91245</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,21 +8037,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611686</v>
+        <v>611743</v>
       </c>
       <c r="R75" t="n">
-        <v>7203685</v>
+        <v>7203706</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,57 +8111,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779880</v>
+        <v>125779312</v>
       </c>
       <c r="B76" t="n">
-        <v>91238</v>
+        <v>98352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611743</v>
+        <v>611683</v>
       </c>
       <c r="R76" t="n">
-        <v>7203706</v>
+        <v>7203677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8208,44 +8208,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779340</v>
+        <v>125779310</v>
       </c>
       <c r="B77" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611680</v>
+        <v>611700</v>
       </c>
       <c r="R77" t="n">
-        <v>7203713</v>
+        <v>7203703</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125779313</v>
+        <v>125779875</v>
       </c>
       <c r="B78" t="n">
-        <v>98345</v>
+        <v>80106</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,34 +8328,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611663</v>
+        <v>611687</v>
       </c>
       <c r="R78" t="n">
-        <v>7203664</v>
+        <v>7203684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8402,22 +8402,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779847</v>
+        <v>125779313</v>
       </c>
       <c r="B79" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8445,14 +8445,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611502</v>
+        <v>611663</v>
       </c>
       <c r="R79" t="n">
-        <v>7203644</v>
+        <v>7203664</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,22 +8499,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125781627</v>
+        <v>125779307</v>
       </c>
       <c r="B80" t="n">
-        <v>91185</v>
+        <v>80099</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8522,21 +8522,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8546,13 +8546,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611526</v>
+        <v>611707</v>
       </c>
       <c r="R80" t="n">
-        <v>7203708</v>
+        <v>7203701</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8579,19 +8579,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,22 +8596,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779875</v>
+        <v>125779847</v>
       </c>
       <c r="B81" t="n">
-        <v>80106</v>
+        <v>98352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8629,21 +8619,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8653,10 +8643,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611687</v>
+        <v>611502</v>
       </c>
       <c r="R81" t="n">
-        <v>7203684</v>
+        <v>7203644</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8715,10 +8705,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779307</v>
+        <v>125781627</v>
       </c>
       <c r="B82" t="n">
-        <v>80099</v>
+        <v>91192</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8726,21 +8716,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8750,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611707</v>
+        <v>611526</v>
       </c>
       <c r="R82" t="n">
-        <v>7203701</v>
+        <v>7203708</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8783,9 +8773,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8800,12 +8800,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8815,7 +8815,7 @@
         <v>125779332</v>
       </c>
       <c r="B83" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8909,48 +8909,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125781650</v>
+        <v>125779873</v>
       </c>
       <c r="B84" t="n">
-        <v>91586</v>
+        <v>80106</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611521</v>
+        <v>611693</v>
       </c>
       <c r="R84" t="n">
-        <v>7203626</v>
+        <v>7203707</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,19 +8977,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9004,22 +8994,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125776368</v>
+        <v>125781650</v>
       </c>
       <c r="B85" t="n">
-        <v>91791</v>
+        <v>91593</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9027,37 +9017,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>760</v>
+        <v>1506</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611705</v>
+        <v>611521</v>
       </c>
       <c r="R85" t="n">
-        <v>7203679</v>
+        <v>7203626</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9084,9 +9074,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9101,65 +9101,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125781638</v>
+        <v>125776368</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>91798</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611645</v>
+        <v>611705</v>
       </c>
       <c r="R86" t="n">
-        <v>7203676</v>
+        <v>7203679</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9186,19 +9181,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9213,19 +9198,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125779347</v>
+        <v>125781638</v>
       </c>
       <c r="B87" t="n">
         <v>57651</v>
@@ -9254,27 +9239,24 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611688</v>
+        <v>611645</v>
       </c>
       <c r="R87" t="n">
-        <v>7203713</v>
+        <v>7203676</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9301,14 +9283,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9323,57 +9310,65 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125779873</v>
+        <v>125779347</v>
       </c>
       <c r="B88" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611693</v>
+        <v>611688</v>
       </c>
       <c r="R88" t="n">
-        <v>7203707</v>
+        <v>7203713</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9408,6 +9403,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,22 +9420,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125779874</v>
+        <v>125779324</v>
       </c>
       <c r="B89" t="n">
-        <v>80106</v>
+        <v>80098</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9443,34 +9443,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>611704</v>
+        <v>611659</v>
       </c>
       <c r="R89" t="n">
-        <v>7203676</v>
+        <v>7203623</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9517,22 +9517,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125779324</v>
+        <v>125779874</v>
       </c>
       <c r="B90" t="n">
-        <v>80098</v>
+        <v>80106</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9540,34 +9540,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>611659</v>
+        <v>611704</v>
       </c>
       <c r="R90" t="n">
-        <v>7203623</v>
+        <v>7203676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9614,22 +9614,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779764</v>
+        <v>125779852</v>
       </c>
       <c r="B91" t="n">
-        <v>80099</v>
+        <v>98352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611648</v>
+        <v>611711</v>
       </c>
       <c r="R91" t="n">
-        <v>7203687</v>
+        <v>7203685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9711,22 +9711,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125776127</v>
+        <v>125779846</v>
       </c>
       <c r="B92" t="n">
-        <v>80106</v>
+        <v>80099</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9734,34 +9734,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611681</v>
+        <v>611717</v>
       </c>
       <c r="R92" t="n">
-        <v>7203685</v>
+        <v>7203689</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9808,22 +9808,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125779846</v>
+        <v>125776127</v>
       </c>
       <c r="B93" t="n">
-        <v>80099</v>
+        <v>80106</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611717</v>
+        <v>611681</v>
       </c>
       <c r="R93" t="n">
-        <v>7203689</v>
+        <v>7203685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,22 +9905,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125779852</v>
+        <v>125779764</v>
       </c>
       <c r="B94" t="n">
-        <v>98345</v>
+        <v>80099</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9928,21 +9928,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9952,10 +9952,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611711</v>
+        <v>611648</v>
       </c>
       <c r="R94" t="n">
-        <v>7203685</v>
+        <v>7203687</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10002,22 +10002,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779349</v>
+        <v>125779302</v>
       </c>
       <c r="B95" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,42 +10025,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611652</v>
+        <v>611618</v>
       </c>
       <c r="R95" t="n">
-        <v>7203627</v>
+        <v>7203674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10093,11 +10085,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10124,45 +10111,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779314</v>
+        <v>125779885</v>
       </c>
       <c r="B96" t="n">
-        <v>98345</v>
+        <v>78967</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611663</v>
+        <v>611661</v>
       </c>
       <c r="R96" t="n">
-        <v>7203673</v>
+        <v>7203604</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10209,22 +10196,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779302</v>
+        <v>125779349</v>
       </c>
       <c r="B97" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10232,34 +10219,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611618</v>
+        <v>611652</v>
       </c>
       <c r="R97" t="n">
-        <v>7203674</v>
+        <v>7203627</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10292,6 +10287,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10318,45 +10318,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779885</v>
+        <v>125779314</v>
       </c>
       <c r="B98" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611661</v>
+        <v>611663</v>
       </c>
       <c r="R98" t="n">
-        <v>7203604</v>
+        <v>7203673</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10403,57 +10403,57 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779851</v>
+        <v>125779299</v>
       </c>
       <c r="B99" t="n">
-        <v>98345</v>
+        <v>75066</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611690</v>
+        <v>611561</v>
       </c>
       <c r="R99" t="n">
-        <v>7203710</v>
+        <v>7203692</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10500,12 +10500,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10706,45 +10706,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779299</v>
+        <v>125779851</v>
       </c>
       <c r="B102" t="n">
-        <v>75066</v>
+        <v>98352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611561</v>
+        <v>611690</v>
       </c>
       <c r="R102" t="n">
-        <v>7203692</v>
+        <v>7203710</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>125803940</v>
       </c>
       <c r="B104" t="n">
-        <v>91216</v>
+        <v>91223</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>125803917</v>
       </c>
       <c r="B105" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>125803950</v>
       </c>
       <c r="B106" t="n">
-        <v>91586</v>
+        <v>91593</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>125803668</v>
       </c>
       <c r="B107" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11648,10 +11648,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125803771</v>
+        <v>125803886</v>
       </c>
       <c r="B111" t="n">
-        <v>80106</v>
+        <v>98352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11659,30 +11659,27 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -11690,10 +11687,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>611602</v>
+        <v>611575</v>
       </c>
       <c r="R111" t="n">
-        <v>7203692</v>
+        <v>7203713</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11753,10 +11750,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125803886</v>
+        <v>125803771</v>
       </c>
       <c r="B112" t="n">
-        <v>98345</v>
+        <v>80106</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11764,27 +11761,30 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>611575</v>
+        <v>611602</v>
       </c>
       <c r="R112" t="n">
-        <v>7203713</v>
+        <v>7203692</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -3806,32 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779834</v>
+        <v>125779848</v>
       </c>
       <c r="B33" t="n">
-        <v>75066</v>
+        <v>98352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611547</v>
+        <v>611545</v>
       </c>
       <c r="R33" t="n">
-        <v>7203635</v>
+        <v>7203710</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125781666</v>
+        <v>125779834</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>75066</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,37 +3914,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611652</v>
+        <v>611547</v>
       </c>
       <c r="R34" t="n">
-        <v>7203680</v>
+        <v>7203635</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3971,19 +3971,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,22 +3988,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125780606</v>
+        <v>125781666</v>
       </c>
       <c r="B35" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,13 +4035,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611311</v>
+        <v>611652</v>
       </c>
       <c r="R35" t="n">
-        <v>7203689</v>
+        <v>7203680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4075,12 +4065,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125779884</v>
+        <v>125780606</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611666</v>
+        <v>611311</v>
       </c>
       <c r="R36" t="n">
-        <v>7203678</v>
+        <v>7203689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,22 +4192,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125780608</v>
+        <v>125779884</v>
       </c>
       <c r="B37" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611445</v>
+        <v>611666</v>
       </c>
       <c r="R37" t="n">
-        <v>7203816</v>
+        <v>7203678</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,57 +4289,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779848</v>
+        <v>125780608</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>80070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611545</v>
+        <v>611445</v>
       </c>
       <c r="R38" t="n">
-        <v>7203710</v>
+        <v>7203816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,65 +4386,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779319</v>
+        <v>125779773</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>80106</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611663</v>
+        <v>611662</v>
       </c>
       <c r="R39" t="n">
-        <v>7203613</v>
+        <v>7203612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4479,11 +4471,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4496,22 +4483,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779316</v>
+        <v>125779337</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4519,42 +4506,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611507</v>
+        <v>611615</v>
       </c>
       <c r="R40" t="n">
-        <v>7203685</v>
+        <v>7203678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4566,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,53 +4592,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779318</v>
+        <v>125779844</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611725</v>
+        <v>611644</v>
       </c>
       <c r="R41" t="n">
-        <v>7203707</v>
+        <v>7203690</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4699,11 +4665,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4716,57 +4677,65 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779853</v>
+        <v>125779319</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611691</v>
+        <v>611663</v>
       </c>
       <c r="R42" t="n">
-        <v>7203679</v>
+        <v>7203613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4801,6 +4770,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4813,57 +4787,65 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779773</v>
+        <v>125779316</v>
       </c>
       <c r="B43" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611662</v>
+        <v>611507</v>
       </c>
       <c r="R43" t="n">
-        <v>7203612</v>
+        <v>7203685</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4898,6 +4880,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4910,22 +4897,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779337</v>
+        <v>125779318</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4933,34 +4920,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611615</v>
+        <v>611725</v>
       </c>
       <c r="R44" t="n">
-        <v>7203678</v>
+        <v>7203707</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,6 +4988,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5019,10 +5019,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779844</v>
+        <v>125779853</v>
       </c>
       <c r="B45" t="n">
-        <v>80099</v>
+        <v>98352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611644</v>
+        <v>611691</v>
       </c>
       <c r="R45" t="n">
-        <v>7203690</v>
+        <v>7203679</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6035,45 +6035,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779850</v>
+        <v>125779320</v>
       </c>
       <c r="B55" t="n">
-        <v>98352</v>
+        <v>91593</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611637</v>
+        <v>611543</v>
       </c>
       <c r="R55" t="n">
-        <v>7203685</v>
+        <v>7203697</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6120,44 +6120,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125776365</v>
+        <v>125779881</v>
       </c>
       <c r="B56" t="n">
-        <v>98352</v>
+        <v>91245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611567</v>
+        <v>611650</v>
       </c>
       <c r="R56" t="n">
-        <v>7203714</v>
+        <v>7203647</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,22 +6217,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779842</v>
+        <v>125779850</v>
       </c>
       <c r="B57" t="n">
-        <v>80099</v>
+        <v>98352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611593</v>
+        <v>611637</v>
       </c>
       <c r="R57" t="n">
-        <v>7203711</v>
+        <v>7203685</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6326,48 +6326,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125781664</v>
+        <v>125776365</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>98352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611539</v>
+        <v>611567</v>
       </c>
       <c r="R58" t="n">
-        <v>7203643</v>
+        <v>7203714</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6394,19 +6394,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6421,44 +6411,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779867</v>
+        <v>125779842</v>
       </c>
       <c r="B59" t="n">
-        <v>80070</v>
+        <v>80099</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6468,10 +6458,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611694</v>
+        <v>611593</v>
       </c>
       <c r="R59" t="n">
-        <v>7203678</v>
+        <v>7203711</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6530,10 +6520,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779869</v>
+        <v>125781664</v>
       </c>
       <c r="B60" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6541,37 +6531,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611687</v>
+        <v>611539</v>
       </c>
       <c r="R60" t="n">
-        <v>7203684</v>
+        <v>7203643</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6598,9 +6588,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6615,22 +6615,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779344</v>
+        <v>125779867</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6638,34 +6638,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611653</v>
+        <v>611694</v>
       </c>
       <c r="R61" t="n">
-        <v>7203626</v>
+        <v>7203678</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6712,22 +6712,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125780620</v>
+        <v>125779869</v>
       </c>
       <c r="B62" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6735,39 +6735,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611381</v>
+        <v>611687</v>
       </c>
       <c r="R62" t="n">
-        <v>7203809</v>
+        <v>7203684</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6794,12 +6789,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,44 +6809,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779320</v>
+        <v>125779344</v>
       </c>
       <c r="B63" t="n">
-        <v>91593</v>
+        <v>78967</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6856,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611543</v>
+        <v>611653</v>
       </c>
       <c r="R63" t="n">
-        <v>7203697</v>
+        <v>7203626</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6923,10 +6918,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125779881</v>
+        <v>125780620</v>
       </c>
       <c r="B64" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6934,34 +6929,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611650</v>
+        <v>611381</v>
       </c>
       <c r="R64" t="n">
-        <v>7203647</v>
+        <v>7203809</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7008,22 +7008,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125781642</v>
+        <v>125779308</v>
       </c>
       <c r="B65" t="n">
-        <v>56843</v>
+        <v>80099</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7031,42 +7031,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611705</v>
+        <v>611684</v>
       </c>
       <c r="R65" t="n">
-        <v>7203676</v>
+        <v>7203690</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7093,19 +7088,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7120,60 +7105,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125779308</v>
+        <v>125781635</v>
       </c>
       <c r="B66" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611684</v>
+        <v>611535</v>
       </c>
       <c r="R66" t="n">
-        <v>7203690</v>
+        <v>7203644</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7200,9 +7190,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,19 +7217,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125781635</v>
+        <v>125780618</v>
       </c>
       <c r="B67" t="n">
         <v>57651</v>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611535</v>
+        <v>611378</v>
       </c>
       <c r="R67" t="n">
-        <v>7203644</v>
+        <v>7203714</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7299,22 +7299,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7334,45 +7324,45 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125780618</v>
+        <v>125781642</v>
       </c>
       <c r="B68" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7381,13 +7371,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611378</v>
+        <v>611705</v>
       </c>
       <c r="R68" t="n">
-        <v>7203714</v>
+        <v>7203676</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7411,12 +7401,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7436,52 +7436,52 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125779339</v>
+        <v>125776142</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>91798</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611640</v>
+        <v>611684</v>
       </c>
       <c r="R69" t="n">
-        <v>7203677</v>
+        <v>7203683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7528,57 +7528,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125776142</v>
+        <v>125779859</v>
       </c>
       <c r="B70" t="n">
-        <v>91798</v>
+        <v>80071</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611684</v>
+        <v>611687</v>
       </c>
       <c r="R70" t="n">
-        <v>7203683</v>
+        <v>7203684</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,28 +7619,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779859</v>
+        <v>125779333</v>
       </c>
       <c r="B71" t="n">
-        <v>80071</v>
+        <v>91245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7648,34 +7649,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611687</v>
+        <v>611659</v>
       </c>
       <c r="R71" t="n">
-        <v>7203684</v>
+        <v>7203648</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7716,29 +7717,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125779333</v>
+        <v>125779339</v>
       </c>
       <c r="B72" t="n">
-        <v>91245</v>
+        <v>78967</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7746,21 +7746,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611659</v>
+        <v>611640</v>
       </c>
       <c r="R72" t="n">
-        <v>7203648</v>
+        <v>7203677</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779852</v>
+        <v>125779846</v>
       </c>
       <c r="B91" t="n">
-        <v>98352</v>
+        <v>80099</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611711</v>
+        <v>611717</v>
       </c>
       <c r="R91" t="n">
-        <v>7203685</v>
+        <v>7203689</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9723,7 +9723,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125779846</v>
+        <v>125779764</v>
       </c>
       <c r="B92" t="n">
         <v>80099</v>
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611717</v>
+        <v>611648</v>
       </c>
       <c r="R92" t="n">
-        <v>7203689</v>
+        <v>7203687</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9808,12 +9808,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9917,10 +9917,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125779764</v>
+        <v>125779852</v>
       </c>
       <c r="B94" t="n">
-        <v>80099</v>
+        <v>98352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9928,21 +9928,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9952,10 +9952,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611648</v>
+        <v>611711</v>
       </c>
       <c r="R94" t="n">
-        <v>7203687</v>
+        <v>7203685</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10002,44 +10002,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779302</v>
+        <v>125779314</v>
       </c>
       <c r="B95" t="n">
-        <v>91227</v>
+        <v>98352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10049,10 +10049,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611618</v>
+        <v>611663</v>
       </c>
       <c r="R95" t="n">
-        <v>7203674</v>
+        <v>7203673</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10111,10 +10111,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779885</v>
+        <v>125779302</v>
       </c>
       <c r="B96" t="n">
-        <v>78967</v>
+        <v>91227</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10122,34 +10122,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611661</v>
+        <v>611618</v>
       </c>
       <c r="R96" t="n">
-        <v>7203604</v>
+        <v>7203674</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,22 +10196,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779349</v>
+        <v>125779885</v>
       </c>
       <c r="B97" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10219,42 +10219,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611652</v>
+        <v>611661</v>
       </c>
       <c r="R97" t="n">
-        <v>7203627</v>
+        <v>7203604</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10289,11 +10281,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10306,57 +10293,65 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779314</v>
+        <v>125779349</v>
       </c>
       <c r="B98" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611663</v>
+        <v>611652</v>
       </c>
       <c r="R98" t="n">
-        <v>7203673</v>
+        <v>7203627</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10389,6 +10384,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11648,10 +11648,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125803886</v>
+        <v>125803771</v>
       </c>
       <c r="B111" t="n">
-        <v>98352</v>
+        <v>80106</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11659,27 +11659,30 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -11687,10 +11690,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>611575</v>
+        <v>611602</v>
       </c>
       <c r="R111" t="n">
-        <v>7203713</v>
+        <v>7203692</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11750,10 +11753,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125803771</v>
+        <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>80106</v>
+        <v>98352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11761,30 +11764,27 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>611602</v>
+        <v>611575</v>
       </c>
       <c r="R112" t="n">
-        <v>7203692</v>
+        <v>7203713</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125781662</v>
+        <v>125781636</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611570</v>
+        <v>611590</v>
       </c>
       <c r="R6" t="n">
-        <v>7203707</v>
+        <v>7203713</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1146,7 +1151,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1156,7 +1161,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125781649</v>
+        <v>125780621</v>
       </c>
       <c r="B7" t="n">
-        <v>91520</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,37 +1199,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611536</v>
+        <v>611445</v>
       </c>
       <c r="R7" t="n">
-        <v>7203694</v>
+        <v>7203814</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1248,22 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125779303</v>
+        <v>125781662</v>
       </c>
       <c r="B8" t="n">
-        <v>91227</v>
+        <v>91245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611631</v>
+        <v>611570</v>
       </c>
       <c r="R8" t="n">
-        <v>7203681</v>
+        <v>7203707</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1358,9 +1358,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,22 +1385,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125781636</v>
+        <v>125781649</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>91520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611590</v>
+        <v>611536</v>
       </c>
       <c r="R9" t="n">
-        <v>7203713</v>
+        <v>7203694</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1462,7 +1467,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1472,7 +1477,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125780621</v>
+        <v>125779303</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>91227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,39 +1515,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611445</v>
+        <v>611631</v>
       </c>
       <c r="R10" t="n">
-        <v>7203814</v>
+        <v>7203681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,57 +1589,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125779323</v>
+        <v>125779769</v>
       </c>
       <c r="B11" t="n">
-        <v>80098</v>
+        <v>80070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611667</v>
+        <v>611696</v>
       </c>
       <c r="R11" t="n">
-        <v>7203673</v>
+        <v>7203681</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,22 +1686,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125779769</v>
+        <v>125781663</v>
       </c>
       <c r="B12" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1709,37 +1709,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611696</v>
+        <v>611570</v>
       </c>
       <c r="R12" t="n">
-        <v>7203681</v>
+        <v>7203700</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,9 +1766,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1783,44 +1793,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125781663</v>
+        <v>125779322</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>80098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1830,13 +1840,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611570</v>
+        <v>611700</v>
       </c>
       <c r="R13" t="n">
-        <v>7203700</v>
+        <v>7203701</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1863,19 +1873,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1890,57 +1890,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125779322</v>
+        <v>125776139</v>
       </c>
       <c r="B14" t="n">
-        <v>80098</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611700</v>
+        <v>611678</v>
       </c>
       <c r="R14" t="n">
-        <v>7203701</v>
+        <v>7203688</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1987,57 +1987,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125776139</v>
+        <v>125779323</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611678</v>
+        <v>611667</v>
       </c>
       <c r="R15" t="n">
-        <v>7203688</v>
+        <v>7203673</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,12 +2084,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2310,45 +2310,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779311</v>
+        <v>125779864</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611690</v>
+        <v>611742</v>
       </c>
       <c r="R18" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,6 +2391,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2395,19 +2408,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125776366</v>
+        <v>125779311</v>
       </c>
       <c r="B19" t="n">
         <v>98352</v>
@@ -2438,11 +2451,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611679</v>
+        <v>611690</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2492,65 +2505,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125779864</v>
+        <v>125776366</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611742</v>
+        <v>611679</v>
       </c>
       <c r="R20" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2585,11 +2590,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,12 +2602,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125776147</v>
+        <v>125780614</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,34 +3123,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611642</v>
+        <v>611292</v>
       </c>
       <c r="R26" t="n">
-        <v>7203689</v>
+        <v>7203687</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3177,12 +3182,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,22 +3202,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125779763</v>
+        <v>125779767</v>
       </c>
       <c r="B27" t="n">
-        <v>80099</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3220,21 +3225,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3244,10 +3249,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611644</v>
+        <v>611673</v>
       </c>
       <c r="R27" t="n">
-        <v>7203694</v>
+        <v>7203670</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3306,45 +3311,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125779838</v>
+        <v>125776147</v>
       </c>
       <c r="B28" t="n">
-        <v>80099</v>
+        <v>78967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611513</v>
+        <v>611642</v>
       </c>
       <c r="R28" t="n">
-        <v>7203698</v>
+        <v>7203689</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,60 +3396,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125781660</v>
+        <v>125779763</v>
       </c>
       <c r="B29" t="n">
-        <v>91241</v>
+        <v>80099</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611570</v>
+        <v>611644</v>
       </c>
       <c r="R29" t="n">
-        <v>7203708</v>
+        <v>7203694</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3471,19 +3476,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3498,44 +3493,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125779886</v>
+        <v>125779838</v>
       </c>
       <c r="B30" t="n">
-        <v>91798</v>
+        <v>80099</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3540,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611704</v>
+        <v>611513</v>
       </c>
       <c r="R30" t="n">
-        <v>7203679</v>
+        <v>7203698</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3607,10 +3602,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125780614</v>
+        <v>125781660</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>91241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3618,42 +3613,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611292</v>
+        <v>611570</v>
       </c>
       <c r="R31" t="n">
-        <v>7203687</v>
+        <v>7203708</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3677,12 +3667,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3702,39 +3702,39 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125779767</v>
+        <v>125779886</v>
       </c>
       <c r="B32" t="n">
-        <v>98352</v>
+        <v>91798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>760</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611673</v>
+        <v>611704</v>
       </c>
       <c r="R32" t="n">
-        <v>7203670</v>
+        <v>7203679</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,12 +3794,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125781628</v>
+        <v>125779309</v>
       </c>
       <c r="B49" t="n">
-        <v>91192</v>
+        <v>80099</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,21 +5441,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611568</v>
+        <v>611679</v>
       </c>
       <c r="R49" t="n">
-        <v>7203718</v>
+        <v>7203682</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5498,19 +5498,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5525,22 +5515,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779315</v>
+        <v>125779343</v>
       </c>
       <c r="B50" t="n">
-        <v>80071</v>
+        <v>78967</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,21 +5538,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5572,10 +5562,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611617</v>
+        <v>611670</v>
       </c>
       <c r="R50" t="n">
-        <v>7203677</v>
+        <v>7203656</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5634,53 +5624,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779863</v>
+        <v>125779876</v>
       </c>
       <c r="B51" t="n">
-        <v>57651</v>
+        <v>80106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611623</v>
+        <v>611661</v>
       </c>
       <c r="R51" t="n">
-        <v>7203692</v>
+        <v>7203604</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5713,11 +5695,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5744,10 +5721,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779309</v>
+        <v>125781628</v>
       </c>
       <c r="B52" t="n">
-        <v>80099</v>
+        <v>91192</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5755,21 +5732,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5779,13 +5756,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611679</v>
+        <v>611568</v>
       </c>
       <c r="R52" t="n">
-        <v>7203682</v>
+        <v>7203718</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5812,9 +5789,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5829,22 +5816,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779343</v>
+        <v>125779315</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,21 +5839,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5876,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611670</v>
+        <v>611617</v>
       </c>
       <c r="R53" t="n">
-        <v>7203656</v>
+        <v>7203677</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5938,45 +5925,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779876</v>
+        <v>125779863</v>
       </c>
       <c r="B54" t="n">
-        <v>80106</v>
+        <v>57651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611661</v>
+        <v>611623</v>
       </c>
       <c r="R54" t="n">
-        <v>7203604</v>
+        <v>7203692</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6009,6 +6004,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7020,10 +7020,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125779308</v>
+        <v>125781642</v>
       </c>
       <c r="B65" t="n">
-        <v>80099</v>
+        <v>56843</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7031,37 +7031,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611684</v>
+        <v>611705</v>
       </c>
       <c r="R65" t="n">
-        <v>7203690</v>
+        <v>7203676</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7088,9 +7093,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7105,65 +7120,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125781635</v>
+        <v>125779308</v>
       </c>
       <c r="B66" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611535</v>
+        <v>611684</v>
       </c>
       <c r="R66" t="n">
-        <v>7203644</v>
+        <v>7203690</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7190,19 +7200,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,19 +7217,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125780618</v>
+        <v>125781635</v>
       </c>
       <c r="B67" t="n">
         <v>57651</v>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611378</v>
+        <v>611535</v>
       </c>
       <c r="R67" t="n">
-        <v>7203714</v>
+        <v>7203644</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7299,12 +7299,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7324,45 +7334,45 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125781642</v>
+        <v>125780618</v>
       </c>
       <c r="B68" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7371,13 +7381,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611705</v>
+        <v>611378</v>
       </c>
       <c r="R68" t="n">
-        <v>7203676</v>
+        <v>7203714</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7401,22 +7411,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7436,52 +7436,52 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125776142</v>
+        <v>125779339</v>
       </c>
       <c r="B69" t="n">
-        <v>91798</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611684</v>
+        <v>611640</v>
       </c>
       <c r="R69" t="n">
-        <v>7203683</v>
+        <v>7203677</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7528,57 +7528,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125779859</v>
+        <v>125776142</v>
       </c>
       <c r="B70" t="n">
-        <v>80071</v>
+        <v>91798</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611687</v>
+        <v>611684</v>
       </c>
       <c r="R70" t="n">
-        <v>7203684</v>
+        <v>7203683</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,29 +7619,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779333</v>
+        <v>125779859</v>
       </c>
       <c r="B71" t="n">
-        <v>91245</v>
+        <v>80071</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7649,34 +7648,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611659</v>
+        <v>611687</v>
       </c>
       <c r="R71" t="n">
-        <v>7203648</v>
+        <v>7203684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,28 +7716,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125779339</v>
+        <v>125779333</v>
       </c>
       <c r="B72" t="n">
-        <v>78967</v>
+        <v>91245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7746,21 +7746,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611640</v>
+        <v>611659</v>
       </c>
       <c r="R72" t="n">
-        <v>7203677</v>
+        <v>7203648</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7832,10 +7832,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779340</v>
+        <v>125779880</v>
       </c>
       <c r="B73" t="n">
-        <v>78967</v>
+        <v>91245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7843,34 +7843,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611680</v>
+        <v>611743</v>
       </c>
       <c r="R73" t="n">
-        <v>7203713</v>
+        <v>7203706</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7917,57 +7917,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779771</v>
+        <v>125779310</v>
       </c>
       <c r="B74" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611686</v>
+        <v>611700</v>
       </c>
       <c r="R74" t="n">
-        <v>7203685</v>
+        <v>7203703</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,22 +8014,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779880</v>
+        <v>125779340</v>
       </c>
       <c r="B75" t="n">
-        <v>91245</v>
+        <v>78967</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,34 +8037,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611743</v>
+        <v>611680</v>
       </c>
       <c r="R75" t="n">
-        <v>7203706</v>
+        <v>7203713</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,57 +8111,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779312</v>
+        <v>125779771</v>
       </c>
       <c r="B76" t="n">
-        <v>98352</v>
+        <v>80070</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611683</v>
+        <v>611686</v>
       </c>
       <c r="R76" t="n">
-        <v>7203677</v>
+        <v>7203685</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8208,19 +8208,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779310</v>
+        <v>125779312</v>
       </c>
       <c r="B77" t="n">
         <v>98352</v>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611700</v>
+        <v>611683</v>
       </c>
       <c r="R77" t="n">
-        <v>7203703</v>
+        <v>7203677</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779313</v>
+        <v>125779307</v>
       </c>
       <c r="B79" t="n">
-        <v>98352</v>
+        <v>80099</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,21 +8425,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611663</v>
+        <v>611707</v>
       </c>
       <c r="R79" t="n">
-        <v>7203664</v>
+        <v>7203701</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8511,10 +8511,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779307</v>
+        <v>125781627</v>
       </c>
       <c r="B80" t="n">
-        <v>80099</v>
+        <v>91192</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8522,21 +8522,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8546,13 +8546,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611707</v>
+        <v>611526</v>
       </c>
       <c r="R80" t="n">
-        <v>7203701</v>
+        <v>7203708</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8579,9 +8579,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8596,57 +8606,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779847</v>
+        <v>125779332</v>
       </c>
       <c r="B81" t="n">
-        <v>98352</v>
+        <v>91245</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611502</v>
+        <v>611525</v>
       </c>
       <c r="R81" t="n">
-        <v>7203644</v>
+        <v>7203705</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8693,22 +8703,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125781627</v>
+        <v>125779313</v>
       </c>
       <c r="B82" t="n">
-        <v>91192</v>
+        <v>98352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8716,21 +8726,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,13 +8750,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611526</v>
+        <v>611663</v>
       </c>
       <c r="R82" t="n">
-        <v>7203708</v>
+        <v>7203664</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8773,19 +8783,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8800,57 +8800,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779332</v>
+        <v>125779847</v>
       </c>
       <c r="B83" t="n">
-        <v>91245</v>
+        <v>98352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611525</v>
+        <v>611502</v>
       </c>
       <c r="R83" t="n">
-        <v>7203705</v>
+        <v>7203644</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,12 +8897,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10014,32 +10014,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779314</v>
+        <v>125779302</v>
       </c>
       <c r="B95" t="n">
-        <v>98352</v>
+        <v>91227</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10049,10 +10049,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611663</v>
+        <v>611618</v>
       </c>
       <c r="R95" t="n">
-        <v>7203673</v>
+        <v>7203674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10111,10 +10111,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779302</v>
+        <v>125779885</v>
       </c>
       <c r="B96" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10122,34 +10122,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611618</v>
+        <v>611661</v>
       </c>
       <c r="R96" t="n">
-        <v>7203674</v>
+        <v>7203604</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,22 +10196,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779885</v>
+        <v>125779349</v>
       </c>
       <c r="B97" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10219,34 +10219,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611661</v>
+        <v>611652</v>
       </c>
       <c r="R97" t="n">
-        <v>7203604</v>
+        <v>7203627</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10281,6 +10289,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10293,65 +10306,57 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779349</v>
+        <v>125779314</v>
       </c>
       <c r="B98" t="n">
-        <v>57651</v>
+        <v>98352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611652</v>
+        <v>611663</v>
       </c>
       <c r="R98" t="n">
-        <v>7203627</v>
+        <v>7203673</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10384,11 +10389,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>125803940</v>
       </c>
       <c r="B104" t="n">
-        <v>91223</v>
+        <v>91224</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>125803917</v>
       </c>
       <c r="B105" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>125803950</v>
       </c>
       <c r="B106" t="n">
-        <v>91593</v>
+        <v>91594</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>125803668</v>
       </c>
       <c r="B107" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11648,10 +11648,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125803771</v>
+        <v>125803886</v>
       </c>
       <c r="B111" t="n">
-        <v>80106</v>
+        <v>98353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11659,30 +11659,27 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -11690,10 +11687,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>611602</v>
+        <v>611575</v>
       </c>
       <c r="R111" t="n">
-        <v>7203692</v>
+        <v>7203713</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11753,10 +11750,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125803886</v>
+        <v>125803771</v>
       </c>
       <c r="B112" t="n">
-        <v>98352</v>
+        <v>80107</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11764,27 +11761,30 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>611575</v>
+        <v>611602</v>
       </c>
       <c r="R112" t="n">
-        <v>7203713</v>
+        <v>7203692</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125776367</v>
+        <v>125779345</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611653</v>
+        <v>611661</v>
       </c>
       <c r="R2" t="n">
-        <v>7203665</v>
+        <v>7203650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +756,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -760,22 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125779334</v>
+        <v>125776148</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,14 +816,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611526</v>
+        <v>611660</v>
       </c>
       <c r="R3" t="n">
-        <v>7203706</v>
+        <v>7203684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +870,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125776148</v>
+        <v>125776367</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,14 +913,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611660</v>
+        <v>611653</v>
       </c>
       <c r="R4" t="n">
-        <v>7203684</v>
+        <v>7203665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +967,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125779345</v>
+        <v>125779334</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611661</v>
+        <v>611526</v>
       </c>
       <c r="R5" t="n">
-        <v>7203650</v>
+        <v>7203706</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1050,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125781636</v>
+        <v>125781662</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>91246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,39 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611590</v>
+        <v>611570</v>
       </c>
       <c r="R6" t="n">
-        <v>7203713</v>
+        <v>7203707</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1151,7 +1146,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1161,7 +1156,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125780621</v>
+        <v>125781649</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>91524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,42 +1194,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611445</v>
+        <v>611536</v>
       </c>
       <c r="R7" t="n">
-        <v>7203814</v>
+        <v>7203694</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,12 +1248,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125781662</v>
+        <v>125779303</v>
       </c>
       <c r="B8" t="n">
-        <v>91245</v>
+        <v>91228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611570</v>
+        <v>611631</v>
       </c>
       <c r="R8" t="n">
-        <v>7203707</v>
+        <v>7203681</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1358,19 +1358,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,22 +1375,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125781649</v>
+        <v>125781636</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611536</v>
+        <v>611590</v>
       </c>
       <c r="R9" t="n">
-        <v>7203694</v>
+        <v>7203713</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1467,7 +1462,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1477,7 +1472,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125779303</v>
+        <v>125780621</v>
       </c>
       <c r="B10" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1515,34 +1510,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611631</v>
+        <v>611445</v>
       </c>
       <c r="R10" t="n">
-        <v>7203681</v>
+        <v>7203814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,57 +1589,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125779769</v>
+        <v>125779322</v>
       </c>
       <c r="B11" t="n">
-        <v>80070</v>
+        <v>80099</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611696</v>
+        <v>611700</v>
       </c>
       <c r="R11" t="n">
-        <v>7203681</v>
+        <v>7203701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,12 +1686,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
         <v>125781663</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,45 +1805,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779322</v>
+        <v>125779769</v>
       </c>
       <c r="B13" t="n">
-        <v>80098</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611700</v>
+        <v>611696</v>
       </c>
       <c r="R13" t="n">
-        <v>7203701</v>
+        <v>7203681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,12 +1890,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1905,7 +1905,7 @@
         <v>125776139</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>125779323</v>
       </c>
       <c r="B15" t="n">
-        <v>80098</v>
+        <v>80099</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,53 +2310,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779864</v>
+        <v>125779311</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611742</v>
+        <v>611690</v>
       </c>
       <c r="R18" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,11 +2383,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2408,22 +2395,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125779311</v>
+        <v>125776366</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,11 +2438,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611690</v>
+        <v>611679</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2505,57 +2492,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125776366</v>
+        <v>125779864</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611679</v>
+        <v>611742</v>
       </c>
       <c r="R20" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,6 +2585,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,22 +2602,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125779338</v>
+        <v>125779317</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,34 +2625,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611631</v>
+        <v>611723</v>
       </c>
       <c r="R21" t="n">
-        <v>7203681</v>
+        <v>7203703</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2714,7 +2727,7 @@
         <v>125779336</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2808,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125780607</v>
+        <v>125779338</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,21 +2832,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2843,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611445</v>
+        <v>611631</v>
       </c>
       <c r="R23" t="n">
-        <v>7203816</v>
+        <v>7203681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2873,12 +2886,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2893,22 +2906,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779317</v>
+        <v>125780607</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>80072</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,42 +2929,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611723</v>
+        <v>611445</v>
       </c>
       <c r="R24" t="n">
-        <v>7203703</v>
+        <v>7203816</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2978,17 +2983,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,12 +3003,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,50 +3112,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125780614</v>
+        <v>125779767</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611292</v>
+        <v>611673</v>
       </c>
       <c r="R26" t="n">
-        <v>7203687</v>
+        <v>7203670</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3182,12 +3177,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3202,22 +3197,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125779767</v>
+        <v>125779763</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>80100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,21 +3220,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,10 +3244,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611673</v>
+        <v>611644</v>
       </c>
       <c r="R27" t="n">
-        <v>7203670</v>
+        <v>7203694</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,45 +3306,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125776147</v>
+        <v>125779838</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>80100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611642</v>
+        <v>611513</v>
       </c>
       <c r="R28" t="n">
-        <v>7203689</v>
+        <v>7203698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,57 +3391,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125779763</v>
+        <v>125776147</v>
       </c>
       <c r="B29" t="n">
-        <v>80099</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611644</v>
+        <v>611642</v>
       </c>
       <c r="R29" t="n">
-        <v>7203694</v>
+        <v>7203689</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,60 +3488,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125779838</v>
+        <v>125781660</v>
       </c>
       <c r="B30" t="n">
-        <v>80099</v>
+        <v>91242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611513</v>
+        <v>611570</v>
       </c>
       <c r="R30" t="n">
-        <v>7203698</v>
+        <v>7203708</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3573,9 +3568,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3590,60 +3595,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125781660</v>
+        <v>125779886</v>
       </c>
       <c r="B31" t="n">
-        <v>91241</v>
+        <v>91802</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611570</v>
+        <v>611704</v>
       </c>
       <c r="R31" t="n">
-        <v>7203708</v>
+        <v>7203679</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3670,19 +3675,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,57 +3692,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125779886</v>
+        <v>125780614</v>
       </c>
       <c r="B32" t="n">
-        <v>91798</v>
+        <v>57651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611704</v>
+        <v>611292</v>
       </c>
       <c r="R32" t="n">
-        <v>7203679</v>
+        <v>7203687</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,12 +3794,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
         <v>125779848</v>
       </c>
       <c r="B33" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125779834</v>
+        <v>125781666</v>
       </c>
       <c r="B34" t="n">
-        <v>75066</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,37 +3914,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611547</v>
+        <v>611652</v>
       </c>
       <c r="R34" t="n">
-        <v>7203635</v>
+        <v>7203680</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3971,9 +3971,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,22 +3998,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125781666</v>
+        <v>125780608</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,13 +4045,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611652</v>
+        <v>611445</v>
       </c>
       <c r="R35" t="n">
-        <v>7203680</v>
+        <v>7203816</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4065,22 +4075,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125780606</v>
+        <v>125779834</v>
       </c>
       <c r="B36" t="n">
-        <v>80070</v>
+        <v>75067</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611311</v>
+        <v>611547</v>
       </c>
       <c r="R36" t="n">
-        <v>7203689</v>
+        <v>7203635</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,12 +4192,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
         <v>125779884</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125780608</v>
+        <v>125780606</v>
       </c>
       <c r="B38" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611445</v>
+        <v>611311</v>
       </c>
       <c r="R38" t="n">
-        <v>7203816</v>
+        <v>7203689</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779773</v>
+        <v>125779853</v>
       </c>
       <c r="B39" t="n">
-        <v>80106</v>
+        <v>98355</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611662</v>
+        <v>611691</v>
       </c>
       <c r="R39" t="n">
-        <v>7203612</v>
+        <v>7203679</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,57 +4483,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779337</v>
+        <v>125779844</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>80100</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611615</v>
+        <v>611644</v>
       </c>
       <c r="R40" t="n">
-        <v>7203678</v>
+        <v>7203690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,22 +4580,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779844</v>
+        <v>125779773</v>
       </c>
       <c r="B41" t="n">
-        <v>80099</v>
+        <v>80107</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611644</v>
+        <v>611662</v>
       </c>
       <c r="R41" t="n">
-        <v>7203690</v>
+        <v>7203612</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,22 +4677,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779319</v>
+        <v>125779337</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,42 +4700,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611663</v>
+        <v>611615</v>
       </c>
       <c r="R42" t="n">
-        <v>7203613</v>
+        <v>7203678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,11 +4760,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4799,7 +4786,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779316</v>
+        <v>125779319</v>
       </c>
       <c r="B43" t="n">
         <v>57651</v>
@@ -4842,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611507</v>
+        <v>611663</v>
       </c>
       <c r="R43" t="n">
-        <v>7203685</v>
+        <v>7203613</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4882,7 +4869,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4909,7 +4896,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779318</v>
+        <v>125779316</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -4952,10 +4939,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611725</v>
+        <v>611507</v>
       </c>
       <c r="R44" t="n">
-        <v>7203707</v>
+        <v>7203685</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5019,45 +5006,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779853</v>
+        <v>125779318</v>
       </c>
       <c r="B45" t="n">
-        <v>98352</v>
+        <v>57651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611691</v>
+        <v>611725</v>
       </c>
       <c r="R45" t="n">
-        <v>7203679</v>
+        <v>7203707</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5092,6 +5087,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5104,60 +5104,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125776134</v>
+        <v>125781648</v>
       </c>
       <c r="B46" t="n">
-        <v>80099</v>
+        <v>80072</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>611647</v>
+        <v>611683</v>
       </c>
       <c r="R46" t="n">
-        <v>7203694</v>
+        <v>7203710</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5184,9 +5184,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5201,65 +5211,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125779346</v>
+        <v>125776134</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>80100</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>611666</v>
+        <v>611647</v>
       </c>
       <c r="R47" t="n">
-        <v>7203652</v>
+        <v>7203694</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5294,11 +5296,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5311,22 +5308,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125781648</v>
+        <v>125779346</v>
       </c>
       <c r="B48" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,37 +5331,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>611683</v>
+        <v>611666</v>
       </c>
       <c r="R48" t="n">
-        <v>7203710</v>
+        <v>7203652</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5391,19 +5396,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5433,7 +5433,7 @@
         <v>125779309</v>
       </c>
       <c r="B49" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779343</v>
+        <v>125779315</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>80072</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5538,21 +5538,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611670</v>
+        <v>611617</v>
       </c>
       <c r="R50" t="n">
-        <v>7203656</v>
+        <v>7203677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5624,45 +5624,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779876</v>
+        <v>125779343</v>
       </c>
       <c r="B51" t="n">
-        <v>80106</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611661</v>
+        <v>611670</v>
       </c>
       <c r="R51" t="n">
-        <v>7203604</v>
+        <v>7203656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5709,60 +5709,68 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125781628</v>
+        <v>125779863</v>
       </c>
       <c r="B52" t="n">
-        <v>91192</v>
+        <v>57651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611568</v>
+        <v>611623</v>
       </c>
       <c r="R52" t="n">
-        <v>7203718</v>
+        <v>7203692</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5789,19 +5797,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:19</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5816,44 +5819,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779315</v>
+        <v>125781628</v>
       </c>
       <c r="B53" t="n">
-        <v>80071</v>
+        <v>91193</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,13 +5866,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611617</v>
+        <v>611568</v>
       </c>
       <c r="R53" t="n">
-        <v>7203677</v>
+        <v>7203718</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5896,9 +5899,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5913,65 +5926,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779863</v>
+        <v>125779876</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>80107</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611623</v>
+        <v>611661</v>
       </c>
       <c r="R54" t="n">
-        <v>7203692</v>
+        <v>7203604</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6004,11 +6009,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6035,32 +6035,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779320</v>
+        <v>125781664</v>
       </c>
       <c r="B55" t="n">
-        <v>91593</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611543</v>
+        <v>611539</v>
       </c>
       <c r="R55" t="n">
-        <v>7203697</v>
+        <v>7203643</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6103,9 +6103,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6120,22 +6130,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125779881</v>
+        <v>125779869</v>
       </c>
       <c r="B56" t="n">
-        <v>91245</v>
+        <v>80071</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,21 +6153,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6167,10 +6177,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611650</v>
+        <v>611687</v>
       </c>
       <c r="R56" t="n">
-        <v>7203647</v>
+        <v>7203684</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6229,32 +6239,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779850</v>
+        <v>125779867</v>
       </c>
       <c r="B57" t="n">
-        <v>98352</v>
+        <v>80071</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6264,10 +6274,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611637</v>
+        <v>611694</v>
       </c>
       <c r="R57" t="n">
-        <v>7203685</v>
+        <v>7203678</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6326,45 +6336,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125776365</v>
+        <v>125779344</v>
       </c>
       <c r="B58" t="n">
-        <v>98352</v>
+        <v>78968</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611567</v>
+        <v>611653</v>
       </c>
       <c r="R58" t="n">
-        <v>7203714</v>
+        <v>7203626</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6411,44 +6421,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779842</v>
+        <v>125779881</v>
       </c>
       <c r="B59" t="n">
-        <v>80099</v>
+        <v>91246</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6458,10 +6468,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611593</v>
+        <v>611650</v>
       </c>
       <c r="R59" t="n">
-        <v>7203711</v>
+        <v>7203647</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6520,48 +6530,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125781664</v>
+        <v>125779842</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>80100</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611539</v>
+        <v>611593</v>
       </c>
       <c r="R60" t="n">
-        <v>7203643</v>
+        <v>7203711</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6588,19 +6598,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6615,57 +6615,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779867</v>
+        <v>125779320</v>
       </c>
       <c r="B61" t="n">
-        <v>80070</v>
+        <v>91597</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1506</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611694</v>
+        <v>611543</v>
       </c>
       <c r="R61" t="n">
-        <v>7203678</v>
+        <v>7203697</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6712,22 +6712,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779869</v>
+        <v>125780620</v>
       </c>
       <c r="B62" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6735,34 +6735,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611687</v>
+        <v>611381</v>
       </c>
       <c r="R62" t="n">
-        <v>7203684</v>
+        <v>7203809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6789,12 +6794,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6809,57 +6814,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779344</v>
+        <v>125779850</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>98355</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611653</v>
+        <v>611637</v>
       </c>
       <c r="R63" t="n">
-        <v>7203626</v>
+        <v>7203685</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6906,62 +6911,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125780620</v>
+        <v>125776365</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611381</v>
+        <v>611567</v>
       </c>
       <c r="R64" t="n">
-        <v>7203809</v>
+        <v>7203714</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7008,22 +7008,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125781642</v>
+        <v>125779308</v>
       </c>
       <c r="B65" t="n">
-        <v>56843</v>
+        <v>80100</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7031,42 +7031,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611705</v>
+        <v>611684</v>
       </c>
       <c r="R65" t="n">
-        <v>7203676</v>
+        <v>7203690</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7093,19 +7088,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7120,60 +7105,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125779308</v>
+        <v>125781635</v>
       </c>
       <c r="B66" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611684</v>
+        <v>611535</v>
       </c>
       <c r="R66" t="n">
-        <v>7203690</v>
+        <v>7203644</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7200,9 +7190,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,19 +7217,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125781635</v>
+        <v>125780618</v>
       </c>
       <c r="B67" t="n">
         <v>57651</v>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611535</v>
+        <v>611378</v>
       </c>
       <c r="R67" t="n">
-        <v>7203644</v>
+        <v>7203714</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7299,22 +7299,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7334,45 +7324,45 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125780618</v>
+        <v>125781642</v>
       </c>
       <c r="B68" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7381,13 +7371,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611378</v>
+        <v>611705</v>
       </c>
       <c r="R68" t="n">
-        <v>7203714</v>
+        <v>7203676</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7411,12 +7401,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7446,7 +7446,7 @@
         <v>125779339</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7540,45 +7540,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125776142</v>
+        <v>125779859</v>
       </c>
       <c r="B70" t="n">
-        <v>91798</v>
+        <v>80072</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611684</v>
+        <v>611687</v>
       </c>
       <c r="R70" t="n">
-        <v>7203683</v>
+        <v>7203684</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,28 +7619,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779859</v>
+        <v>125779333</v>
       </c>
       <c r="B71" t="n">
-        <v>80071</v>
+        <v>91246</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7648,34 +7649,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611687</v>
+        <v>611659</v>
       </c>
       <c r="R71" t="n">
-        <v>7203684</v>
+        <v>7203648</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7716,64 +7717,63 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125779333</v>
+        <v>125776142</v>
       </c>
       <c r="B72" t="n">
-        <v>91245</v>
+        <v>91802</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611659</v>
+        <v>611684</v>
       </c>
       <c r="R72" t="n">
-        <v>7203648</v>
+        <v>7203683</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7820,57 +7820,57 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779880</v>
+        <v>125779312</v>
       </c>
       <c r="B73" t="n">
-        <v>91245</v>
+        <v>98355</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611743</v>
+        <v>611683</v>
       </c>
       <c r="R73" t="n">
-        <v>7203706</v>
+        <v>7203677</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7917,12 +7917,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7932,7 +7932,7 @@
         <v>125779310</v>
       </c>
       <c r="B74" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779340</v>
+        <v>125779771</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,34 +8037,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611680</v>
+        <v>611686</v>
       </c>
       <c r="R75" t="n">
-        <v>7203713</v>
+        <v>7203685</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,22 +8111,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779771</v>
+        <v>125779880</v>
       </c>
       <c r="B76" t="n">
-        <v>80070</v>
+        <v>91246</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8134,21 +8134,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611686</v>
+        <v>611743</v>
       </c>
       <c r="R76" t="n">
-        <v>7203685</v>
+        <v>7203706</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8208,44 +8208,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779312</v>
+        <v>125779340</v>
       </c>
       <c r="B77" t="n">
-        <v>98352</v>
+        <v>78968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611683</v>
+        <v>611680</v>
       </c>
       <c r="R77" t="n">
-        <v>7203677</v>
+        <v>7203713</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125779875</v>
+        <v>125781627</v>
       </c>
       <c r="B78" t="n">
-        <v>80106</v>
+        <v>91193</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611687</v>
+        <v>611526</v>
       </c>
       <c r="R78" t="n">
-        <v>7203684</v>
+        <v>7203708</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,9 +8385,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8402,22 +8412,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779307</v>
+        <v>125779875</v>
       </c>
       <c r="B79" t="n">
-        <v>80099</v>
+        <v>80107</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,34 +8435,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611707</v>
+        <v>611687</v>
       </c>
       <c r="R79" t="n">
-        <v>7203701</v>
+        <v>7203684</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,22 +8509,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125781627</v>
+        <v>125779307</v>
       </c>
       <c r="B80" t="n">
-        <v>91192</v>
+        <v>80100</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8522,21 +8532,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8546,13 +8556,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611526</v>
+        <v>611707</v>
       </c>
       <c r="R80" t="n">
-        <v>7203708</v>
+        <v>7203701</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8579,19 +8589,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,12 +8606,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8621,7 +8621,7 @@
         <v>125779332</v>
       </c>
       <c r="B81" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>125779313</v>
       </c>
       <c r="B82" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>125779847</v>
       </c>
       <c r="B83" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>125779873</v>
       </c>
       <c r="B84" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>125781650</v>
       </c>
       <c r="B85" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9113,48 +9113,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125776368</v>
+        <v>125781638</v>
       </c>
       <c r="B86" t="n">
-        <v>91798</v>
+        <v>57651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611705</v>
+        <v>611645</v>
       </c>
       <c r="R86" t="n">
-        <v>7203679</v>
+        <v>7203676</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9181,9 +9186,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9198,19 +9213,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125781638</v>
+        <v>125779347</v>
       </c>
       <c r="B87" t="n">
         <v>57651</v>
@@ -9239,24 +9254,27 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611645</v>
+        <v>611688</v>
       </c>
       <c r="R87" t="n">
-        <v>7203676</v>
+        <v>7203713</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9283,19 +9301,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:57</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9310,65 +9323,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125779347</v>
+        <v>125776368</v>
       </c>
       <c r="B88" t="n">
-        <v>57651</v>
+        <v>91802</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611688</v>
+        <v>611705</v>
       </c>
       <c r="R88" t="n">
-        <v>7203713</v>
+        <v>7203679</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9403,11 +9408,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,22 +9420,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125779324</v>
+        <v>125779874</v>
       </c>
       <c r="B89" t="n">
-        <v>80098</v>
+        <v>80107</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9443,34 +9443,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>611659</v>
+        <v>611704</v>
       </c>
       <c r="R89" t="n">
-        <v>7203623</v>
+        <v>7203676</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9517,22 +9517,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125779874</v>
+        <v>125779324</v>
       </c>
       <c r="B90" t="n">
-        <v>80106</v>
+        <v>80099</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9540,34 +9540,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>611704</v>
+        <v>611659</v>
       </c>
       <c r="R90" t="n">
-        <v>7203676</v>
+        <v>7203623</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9614,22 +9614,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779846</v>
+        <v>125776127</v>
       </c>
       <c r="B91" t="n">
-        <v>80099</v>
+        <v>80107</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,34 +9637,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611717</v>
+        <v>611681</v>
       </c>
       <c r="R91" t="n">
-        <v>7203689</v>
+        <v>7203685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9711,12 +9711,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9726,7 +9726,7 @@
         <v>125779764</v>
       </c>
       <c r="B92" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9820,10 +9820,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125776127</v>
+        <v>125779846</v>
       </c>
       <c r="B93" t="n">
-        <v>80106</v>
+        <v>80100</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611681</v>
+        <v>611717</v>
       </c>
       <c r="R93" t="n">
-        <v>7203685</v>
+        <v>7203689</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,12 +9905,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -9920,7 +9920,7 @@
         <v>125779852</v>
       </c>
       <c r="B94" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10014,10 +10014,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779302</v>
+        <v>125779885</v>
       </c>
       <c r="B95" t="n">
-        <v>91227</v>
+        <v>78968</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,34 +10025,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611618</v>
+        <v>611661</v>
       </c>
       <c r="R95" t="n">
-        <v>7203674</v>
+        <v>7203604</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10099,22 +10099,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779885</v>
+        <v>125779302</v>
       </c>
       <c r="B96" t="n">
-        <v>78967</v>
+        <v>91228</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10122,34 +10122,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611661</v>
+        <v>611618</v>
       </c>
       <c r="R96" t="n">
-        <v>7203604</v>
+        <v>7203674</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10321,7 +10321,7 @@
         <v>125779314</v>
       </c>
       <c r="B98" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779299</v>
+        <v>125779329</v>
       </c>
       <c r="B99" t="n">
-        <v>75066</v>
+        <v>80071</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611561</v>
+        <v>611623</v>
       </c>
       <c r="R99" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10512,45 +10512,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779329</v>
+        <v>125779772</v>
       </c>
       <c r="B100" t="n">
-        <v>80070</v>
+        <v>80107</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611623</v>
+        <v>611680</v>
       </c>
       <c r="R100" t="n">
-        <v>7203677</v>
+        <v>7203679</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,57 +10597,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779772</v>
+        <v>125779299</v>
       </c>
       <c r="B101" t="n">
-        <v>80106</v>
+        <v>75067</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611680</v>
+        <v>611561</v>
       </c>
       <c r="R101" t="n">
-        <v>7203679</v>
+        <v>7203692</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,12 +10694,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10709,7 +10709,7 @@
         <v>125779851</v>
       </c>
       <c r="B102" t="n">
-        <v>98352</v>
+        <v>98355</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11115,41 +11115,42 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125803950</v>
+        <v>125803668</v>
       </c>
       <c r="B106" t="n">
-        <v>91594</v>
+        <v>98355</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1506</v>
+        <v>221952</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11157,10 +11158,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>611534</v>
+        <v>611679</v>
       </c>
       <c r="R106" t="n">
-        <v>7203710</v>
+        <v>7203707</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11220,42 +11221,41 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125803668</v>
+        <v>125803950</v>
       </c>
       <c r="B107" t="n">
-        <v>98353</v>
+        <v>91597</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221952</v>
+        <v>1506</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>611679</v>
+        <v>611534</v>
       </c>
       <c r="R107" t="n">
-        <v>7203707</v>
+        <v>7203710</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11648,10 +11648,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125803886</v>
+        <v>125803771</v>
       </c>
       <c r="B111" t="n">
-        <v>98353</v>
+        <v>80107</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11659,27 +11659,30 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -11687,10 +11690,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>611575</v>
+        <v>611602</v>
       </c>
       <c r="R111" t="n">
-        <v>7203713</v>
+        <v>7203692</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11750,10 +11753,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125803771</v>
+        <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>80107</v>
+        <v>98355</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11761,30 +11764,27 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>611602</v>
+        <v>611575</v>
       </c>
       <c r="R112" t="n">
-        <v>7203692</v>
+        <v>7203713</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11852,6 +11852,116 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>125779762</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>611672</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7203611</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125781662</v>
+        <v>125781649</v>
       </c>
       <c r="B6" t="n">
-        <v>91246</v>
+        <v>91524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611570</v>
+        <v>611536</v>
       </c>
       <c r="R6" t="n">
-        <v>7203707</v>
+        <v>7203694</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125781649</v>
+        <v>125779303</v>
       </c>
       <c r="B7" t="n">
-        <v>91524</v>
+        <v>91228</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611536</v>
+        <v>611631</v>
       </c>
       <c r="R7" t="n">
-        <v>7203694</v>
+        <v>7203681</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1251,19 +1251,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,22 +1268,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125779303</v>
+        <v>125781662</v>
       </c>
       <c r="B8" t="n">
-        <v>91228</v>
+        <v>91246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1291,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,13 +1315,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611631</v>
+        <v>611570</v>
       </c>
       <c r="R8" t="n">
-        <v>7203681</v>
+        <v>7203707</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1358,9 +1348,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,12 +1375,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1601,45 +1601,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125779322</v>
+        <v>125780615</v>
       </c>
       <c r="B11" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611700</v>
+        <v>611292</v>
       </c>
       <c r="R11" t="n">
-        <v>7203701</v>
+        <v>7203703</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1666,12 +1671,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,22 +1691,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125781663</v>
+        <v>125781637</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1709,34 +1714,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611570</v>
+        <v>611631</v>
       </c>
       <c r="R12" t="n">
-        <v>7203700</v>
+        <v>7203695</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1768,7 +1778,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1778,7 +1788,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,45 +1815,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779769</v>
+        <v>125779322</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80099</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611696</v>
+        <v>611700</v>
       </c>
       <c r="R13" t="n">
-        <v>7203681</v>
+        <v>7203701</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,22 +1900,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125776139</v>
+        <v>125781663</v>
       </c>
       <c r="B14" t="n">
-        <v>80072</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1913,37 +1923,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611678</v>
+        <v>611570</v>
       </c>
       <c r="R14" t="n">
-        <v>7203688</v>
+        <v>7203700</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,9 +1980,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1987,57 +2007,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125779323</v>
+        <v>125779769</v>
       </c>
       <c r="B15" t="n">
-        <v>80099</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611667</v>
+        <v>611696</v>
       </c>
       <c r="R15" t="n">
-        <v>7203673</v>
+        <v>7203681</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,22 +2104,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125780615</v>
+        <v>125776139</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>80072</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,39 +2127,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611292</v>
+        <v>611678</v>
       </c>
       <c r="R16" t="n">
-        <v>7203703</v>
+        <v>7203688</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,12 +2181,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2186,65 +2201,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125781637</v>
+        <v>125779323</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>80099</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611631</v>
+        <v>611667</v>
       </c>
       <c r="R17" t="n">
-        <v>7203695</v>
+        <v>7203673</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,19 +2281,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,57 +2298,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779311</v>
+        <v>125779864</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611690</v>
+        <v>611742</v>
       </c>
       <c r="R18" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,6 +2391,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2395,19 +2408,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125776366</v>
+        <v>125779311</v>
       </c>
       <c r="B19" t="n">
         <v>98355</v>
@@ -2438,11 +2451,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611679</v>
+        <v>611690</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2492,65 +2505,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125779864</v>
+        <v>125776366</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>98355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611742</v>
+        <v>611679</v>
       </c>
       <c r="R20" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2585,11 +2590,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,12 +2602,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125781666</v>
+        <v>125780606</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>80071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,13 +3938,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611652</v>
+        <v>611311</v>
       </c>
       <c r="R34" t="n">
-        <v>7203680</v>
+        <v>7203689</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3968,22 +3968,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4003,17 +3993,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125780608</v>
+        <v>125781666</v>
       </c>
       <c r="B35" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,13 +4035,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611445</v>
+        <v>611652</v>
       </c>
       <c r="R35" t="n">
-        <v>7203816</v>
+        <v>7203680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4075,12 +4065,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125779834</v>
+        <v>125780608</v>
       </c>
       <c r="B36" t="n">
-        <v>75067</v>
+        <v>80071</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611547</v>
+        <v>611445</v>
       </c>
       <c r="R36" t="n">
-        <v>7203635</v>
+        <v>7203816</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,22 +4192,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779884</v>
+        <v>125779834</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>75067</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,21 +4215,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611666</v>
+        <v>611547</v>
       </c>
       <c r="R37" t="n">
-        <v>7203678</v>
+        <v>7203635</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,10 +4301,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125780606</v>
+        <v>125779884</v>
       </c>
       <c r="B38" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4312,34 +4312,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611311</v>
+        <v>611666</v>
       </c>
       <c r="R38" t="n">
-        <v>7203689</v>
+        <v>7203678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,12 +4386,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125779309</v>
+        <v>125781628</v>
       </c>
       <c r="B49" t="n">
-        <v>80100</v>
+        <v>91193</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,21 +5441,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611679</v>
+        <v>611568</v>
       </c>
       <c r="R49" t="n">
-        <v>7203682</v>
+        <v>7203718</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5498,9 +5498,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5515,57 +5525,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779315</v>
+        <v>125779876</v>
       </c>
       <c r="B50" t="n">
-        <v>80072</v>
+        <v>80107</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611617</v>
+        <v>611661</v>
       </c>
       <c r="R50" t="n">
-        <v>7203677</v>
+        <v>7203604</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5612,44 +5622,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779343</v>
+        <v>125779309</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>80100</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5659,10 +5669,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611670</v>
+        <v>611679</v>
       </c>
       <c r="R51" t="n">
-        <v>7203656</v>
+        <v>7203682</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5721,10 +5731,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779863</v>
+        <v>125779315</v>
       </c>
       <c r="B52" t="n">
-        <v>57651</v>
+        <v>80072</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5732,42 +5742,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611623</v>
+        <v>611617</v>
       </c>
       <c r="R52" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5802,11 +5804,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5819,44 +5816,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125781628</v>
+        <v>125779343</v>
       </c>
       <c r="B53" t="n">
-        <v>91193</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5866,13 +5863,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611568</v>
+        <v>611670</v>
       </c>
       <c r="R53" t="n">
-        <v>7203718</v>
+        <v>7203656</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5899,19 +5896,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5926,57 +5913,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779876</v>
+        <v>125779863</v>
       </c>
       <c r="B54" t="n">
-        <v>80107</v>
+        <v>57651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611661</v>
+        <v>611623</v>
       </c>
       <c r="R54" t="n">
-        <v>7203604</v>
+        <v>7203692</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6009,6 +6004,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7832,45 +7832,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779312</v>
+        <v>125779771</v>
       </c>
       <c r="B73" t="n">
-        <v>98355</v>
+        <v>80071</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611683</v>
+        <v>611686</v>
       </c>
       <c r="R73" t="n">
-        <v>7203677</v>
+        <v>7203685</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7917,57 +7917,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779310</v>
+        <v>125779880</v>
       </c>
       <c r="B74" t="n">
-        <v>98355</v>
+        <v>91246</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611700</v>
+        <v>611743</v>
       </c>
       <c r="R74" t="n">
-        <v>7203703</v>
+        <v>7203706</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,22 +8014,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779771</v>
+        <v>125779340</v>
       </c>
       <c r="B75" t="n">
-        <v>80071</v>
+        <v>78968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,34 +8037,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611686</v>
+        <v>611680</v>
       </c>
       <c r="R75" t="n">
-        <v>7203685</v>
+        <v>7203713</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,57 +8111,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779880</v>
+        <v>125779312</v>
       </c>
       <c r="B76" t="n">
-        <v>91246</v>
+        <v>98355</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611743</v>
+        <v>611683</v>
       </c>
       <c r="R76" t="n">
-        <v>7203706</v>
+        <v>7203677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8208,44 +8208,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779340</v>
+        <v>125779310</v>
       </c>
       <c r="B77" t="n">
-        <v>78968</v>
+        <v>98355</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611680</v>
+        <v>611700</v>
       </c>
       <c r="R77" t="n">
-        <v>7203713</v>
+        <v>7203703</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9006,45 +9006,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125781650</v>
+        <v>125781638</v>
       </c>
       <c r="B85" t="n">
-        <v>91597</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611521</v>
+        <v>611645</v>
       </c>
       <c r="R85" t="n">
-        <v>7203626</v>
+        <v>7203676</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9076,7 +9081,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9086,7 +9091,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9113,7 +9118,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125781638</v>
+        <v>125779347</v>
       </c>
       <c r="B86" t="n">
         <v>57651</v>
@@ -9142,24 +9147,27 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611645</v>
+        <v>611688</v>
       </c>
       <c r="R86" t="n">
-        <v>7203676</v>
+        <v>7203713</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9186,19 +9194,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>10:57</t>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9213,68 +9216,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125779347</v>
+        <v>125781650</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>91597</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611688</v>
+        <v>611521</v>
       </c>
       <c r="R87" t="n">
-        <v>7203713</v>
+        <v>7203626</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9301,14 +9296,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9323,12 +9323,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10014,10 +10014,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779885</v>
+        <v>125779349</v>
       </c>
       <c r="B95" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,34 +10025,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611661</v>
+        <v>611652</v>
       </c>
       <c r="R95" t="n">
-        <v>7203604</v>
+        <v>7203627</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10087,6 +10095,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10099,22 +10112,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779302</v>
+        <v>125779885</v>
       </c>
       <c r="B96" t="n">
-        <v>91228</v>
+        <v>78968</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10122,34 +10135,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611618</v>
+        <v>611661</v>
       </c>
       <c r="R96" t="n">
-        <v>7203674</v>
+        <v>7203604</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,22 +10209,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779349</v>
+        <v>125779302</v>
       </c>
       <c r="B97" t="n">
-        <v>57651</v>
+        <v>91228</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10219,42 +10232,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611652</v>
+        <v>611618</v>
       </c>
       <c r="R97" t="n">
-        <v>7203627</v>
+        <v>7203674</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10287,11 +10292,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10415,45 +10415,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779329</v>
+        <v>125779851</v>
       </c>
       <c r="B99" t="n">
-        <v>80071</v>
+        <v>98355</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611623</v>
+        <v>611690</v>
       </c>
       <c r="R99" t="n">
-        <v>7203677</v>
+        <v>7203710</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10500,57 +10500,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779772</v>
+        <v>125779299</v>
       </c>
       <c r="B100" t="n">
-        <v>80107</v>
+        <v>75067</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611680</v>
+        <v>611561</v>
       </c>
       <c r="R100" t="n">
-        <v>7203679</v>
+        <v>7203692</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,22 +10597,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779299</v>
+        <v>125779329</v>
       </c>
       <c r="B101" t="n">
-        <v>75067</v>
+        <v>80071</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10620,21 +10620,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611561</v>
+        <v>611623</v>
       </c>
       <c r="R101" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10706,10 +10706,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779851</v>
+        <v>125779772</v>
       </c>
       <c r="B102" t="n">
-        <v>98355</v>
+        <v>80107</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10717,21 +10717,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611690</v>
+        <v>611680</v>
       </c>
       <c r="R102" t="n">
-        <v>7203710</v>
+        <v>7203679</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125779345</v>
+        <v>125776148</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611661</v>
+        <v>611660</v>
       </c>
       <c r="R2" t="n">
-        <v>7203650</v>
+        <v>7203684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +748,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125776148</v>
+        <v>125776367</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611660</v>
+        <v>611653</v>
       </c>
       <c r="R3" t="n">
-        <v>7203684</v>
+        <v>7203665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125776367</v>
+        <v>125779334</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611653</v>
+        <v>611526</v>
       </c>
       <c r="R4" t="n">
-        <v>7203665</v>
+        <v>7203706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125779334</v>
+        <v>125779345</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611526</v>
+        <v>611661</v>
       </c>
       <c r="R5" t="n">
-        <v>7203706</v>
+        <v>7203650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1050,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,7 +1079,7 @@
         <v>125781649</v>
       </c>
       <c r="B6" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>125779303</v>
       </c>
       <c r="B7" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>125781662</v>
       </c>
       <c r="B8" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1601,50 +1601,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125780615</v>
+        <v>125779322</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>80103</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611292</v>
+        <v>611700</v>
       </c>
       <c r="R11" t="n">
-        <v>7203703</v>
+        <v>7203701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1671,12 +1666,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1691,22 +1686,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125781637</v>
+        <v>125781663</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,39 +1709,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611631</v>
+        <v>611570</v>
       </c>
       <c r="R12" t="n">
-        <v>7203695</v>
+        <v>7203700</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1778,7 +1768,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1788,7 +1778,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,45 +1805,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779322</v>
+        <v>125779769</v>
       </c>
       <c r="B13" t="n">
-        <v>80099</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611700</v>
+        <v>611696</v>
       </c>
       <c r="R13" t="n">
-        <v>7203701</v>
+        <v>7203681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,44 +1890,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125781663</v>
+        <v>125779323</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>80103</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1947,13 +1937,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611570</v>
+        <v>611667</v>
       </c>
       <c r="R14" t="n">
-        <v>7203700</v>
+        <v>7203673</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1980,19 +1970,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2007,22 +1987,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125779769</v>
+        <v>125776139</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2030,34 +2010,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611696</v>
+        <v>611678</v>
       </c>
       <c r="R15" t="n">
-        <v>7203681</v>
+        <v>7203688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,22 +2084,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125776139</v>
+        <v>125781637</v>
       </c>
       <c r="B16" t="n">
-        <v>80072</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2127,37 +2107,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611678</v>
+        <v>611631</v>
       </c>
       <c r="R16" t="n">
-        <v>7203688</v>
+        <v>7203695</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2184,9 +2169,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,57 +2196,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125779323</v>
+        <v>125780615</v>
       </c>
       <c r="B17" t="n">
-        <v>80099</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611667</v>
+        <v>611292</v>
       </c>
       <c r="R17" t="n">
-        <v>7203673</v>
+        <v>7203703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>125779311</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>125776366</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125779336</v>
+        <v>125780607</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,21 +2735,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611575</v>
+        <v>611445</v>
       </c>
       <c r="R22" t="n">
-        <v>7203712</v>
+        <v>7203816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,22 +2809,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125779338</v>
+        <v>125779336</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611631</v>
+        <v>611575</v>
       </c>
       <c r="R23" t="n">
-        <v>7203681</v>
+        <v>7203712</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125780607</v>
+        <v>125779338</v>
       </c>
       <c r="B24" t="n">
-        <v>80072</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,21 +2929,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611445</v>
+        <v>611631</v>
       </c>
       <c r="R24" t="n">
-        <v>7203816</v>
+        <v>7203681</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2983,12 +2983,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,12 +3003,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125779767</v>
+        <v>125779763</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,21 +3123,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611673</v>
+        <v>611644</v>
       </c>
       <c r="R26" t="n">
-        <v>7203670</v>
+        <v>7203694</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125779763</v>
+        <v>125779838</v>
       </c>
       <c r="B27" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611644</v>
+        <v>611513</v>
       </c>
       <c r="R27" t="n">
-        <v>7203694</v>
+        <v>7203698</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,60 +3294,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125779838</v>
+        <v>125781660</v>
       </c>
       <c r="B28" t="n">
-        <v>80100</v>
+        <v>91246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611513</v>
+        <v>611570</v>
       </c>
       <c r="R28" t="n">
-        <v>7203698</v>
+        <v>7203708</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3374,9 +3374,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3391,57 +3401,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125776147</v>
+        <v>125779886</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>91806</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611642</v>
+        <v>611704</v>
       </c>
       <c r="R29" t="n">
-        <v>7203689</v>
+        <v>7203679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,22 +3498,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125781660</v>
+        <v>125776147</v>
       </c>
       <c r="B30" t="n">
-        <v>91242</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3511,37 +3521,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611570</v>
+        <v>611642</v>
       </c>
       <c r="R30" t="n">
-        <v>7203708</v>
+        <v>7203689</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3568,19 +3578,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3595,57 +3595,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125779886</v>
+        <v>125780614</v>
       </c>
       <c r="B31" t="n">
-        <v>91802</v>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611704</v>
+        <v>611292</v>
       </c>
       <c r="R31" t="n">
-        <v>7203679</v>
+        <v>7203687</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3672,12 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3692,62 +3697,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125780614</v>
+        <v>125779767</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611292</v>
+        <v>611673</v>
       </c>
       <c r="R32" t="n">
-        <v>7203687</v>
+        <v>7203670</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,44 +3794,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779848</v>
+        <v>125779884</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611545</v>
+        <v>611666</v>
       </c>
       <c r="R33" t="n">
-        <v>7203710</v>
+        <v>7203678</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780606</v>
+        <v>125781666</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,13 +3938,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611311</v>
+        <v>611652</v>
       </c>
       <c r="R34" t="n">
-        <v>7203689</v>
+        <v>7203680</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3968,12 +3968,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3993,17 +4003,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125781666</v>
+        <v>125780608</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,13 +4045,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611652</v>
+        <v>611445</v>
       </c>
       <c r="R35" t="n">
-        <v>7203680</v>
+        <v>7203816</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4065,22 +4075,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125780608</v>
+        <v>125779834</v>
       </c>
       <c r="B36" t="n">
-        <v>80071</v>
+        <v>75067</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611445</v>
+        <v>611547</v>
       </c>
       <c r="R36" t="n">
-        <v>7203816</v>
+        <v>7203635</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,22 +4192,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779834</v>
+        <v>125780606</v>
       </c>
       <c r="B37" t="n">
-        <v>75067</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611547</v>
+        <v>611311</v>
       </c>
       <c r="R37" t="n">
-        <v>7203635</v>
+        <v>7203689</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,44 +4289,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779884</v>
+        <v>125779848</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611666</v>
+        <v>611545</v>
       </c>
       <c r="R38" t="n">
-        <v>7203678</v>
+        <v>7203710</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779853</v>
+        <v>125779844</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>80104</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611691</v>
+        <v>611644</v>
       </c>
       <c r="R39" t="n">
-        <v>7203679</v>
+        <v>7203690</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779844</v>
+        <v>125779773</v>
       </c>
       <c r="B40" t="n">
-        <v>80100</v>
+        <v>80111</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611644</v>
+        <v>611662</v>
       </c>
       <c r="R40" t="n">
-        <v>7203690</v>
+        <v>7203612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,57 +4580,65 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779773</v>
+        <v>125779318</v>
       </c>
       <c r="B41" t="n">
-        <v>80107</v>
+        <v>57651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611662</v>
+        <v>611725</v>
       </c>
       <c r="R41" t="n">
-        <v>7203612</v>
+        <v>7203707</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4673,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4677,12 +4690,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4692,7 +4705,7 @@
         <v>125779337</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5006,53 +5019,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779318</v>
+        <v>125779853</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611725</v>
+        <v>611691</v>
       </c>
       <c r="R45" t="n">
-        <v>7203707</v>
+        <v>7203679</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5087,11 +5092,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5104,60 +5104,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125781648</v>
+        <v>125776134</v>
       </c>
       <c r="B46" t="n">
-        <v>80072</v>
+        <v>80104</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>611683</v>
+        <v>611647</v>
       </c>
       <c r="R46" t="n">
-        <v>7203710</v>
+        <v>7203694</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5184,19 +5184,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5211,57 +5201,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125776134</v>
+        <v>125779346</v>
       </c>
       <c r="B47" t="n">
-        <v>80100</v>
+        <v>57651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>611647</v>
+        <v>611666</v>
       </c>
       <c r="R47" t="n">
-        <v>7203694</v>
+        <v>7203652</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5296,6 +5294,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5308,22 +5311,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125779346</v>
+        <v>125781648</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5331,45 +5334,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>611666</v>
+        <v>611683</v>
       </c>
       <c r="R48" t="n">
-        <v>7203652</v>
+        <v>7203710</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5396,14 +5391,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5418,44 +5418,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125781628</v>
+        <v>125779315</v>
       </c>
       <c r="B49" t="n">
-        <v>91193</v>
+        <v>80076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611568</v>
+        <v>611617</v>
       </c>
       <c r="R49" t="n">
-        <v>7203718</v>
+        <v>7203677</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5498,19 +5498,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5525,22 +5515,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779876</v>
+        <v>125781628</v>
       </c>
       <c r="B50" t="n">
-        <v>80107</v>
+        <v>91197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5548,37 +5538,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611661</v>
+        <v>611568</v>
       </c>
       <c r="R50" t="n">
-        <v>7203604</v>
+        <v>7203718</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5605,9 +5595,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5622,44 +5622,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779309</v>
+        <v>125779343</v>
       </c>
       <c r="B51" t="n">
-        <v>80100</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611679</v>
+        <v>611670</v>
       </c>
       <c r="R51" t="n">
-        <v>7203682</v>
+        <v>7203656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5731,32 +5731,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779315</v>
+        <v>125779309</v>
       </c>
       <c r="B52" t="n">
-        <v>80072</v>
+        <v>80104</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611617</v>
+        <v>611679</v>
       </c>
       <c r="R52" t="n">
-        <v>7203677</v>
+        <v>7203682</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5828,45 +5828,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779343</v>
+        <v>125779876</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>80111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611670</v>
+        <v>611661</v>
       </c>
       <c r="R53" t="n">
-        <v>7203656</v>
+        <v>7203604</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5913,12 +5913,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6035,48 +6035,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125781664</v>
+        <v>125779850</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611539</v>
+        <v>611637</v>
       </c>
       <c r="R55" t="n">
-        <v>7203643</v>
+        <v>7203685</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6103,19 +6103,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6130,44 +6120,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125779869</v>
+        <v>125776365</v>
       </c>
       <c r="B56" t="n">
-        <v>80071</v>
+        <v>98359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6177,10 +6167,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611687</v>
+        <v>611567</v>
       </c>
       <c r="R56" t="n">
-        <v>7203684</v>
+        <v>7203714</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6227,22 +6217,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779867</v>
+        <v>125779344</v>
       </c>
       <c r="B57" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6250,34 +6240,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611694</v>
+        <v>611653</v>
       </c>
       <c r="R57" t="n">
-        <v>7203678</v>
+        <v>7203626</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6324,22 +6314,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779344</v>
+        <v>125779881</v>
       </c>
       <c r="B58" t="n">
-        <v>78968</v>
+        <v>91250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6347,34 +6337,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611653</v>
+        <v>611650</v>
       </c>
       <c r="R58" t="n">
-        <v>7203626</v>
+        <v>7203647</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6421,57 +6411,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779881</v>
+        <v>125779320</v>
       </c>
       <c r="B59" t="n">
-        <v>91246</v>
+        <v>91601</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611650</v>
+        <v>611543</v>
       </c>
       <c r="R59" t="n">
-        <v>7203647</v>
+        <v>7203697</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6518,60 +6508,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779842</v>
+        <v>125781664</v>
       </c>
       <c r="B60" t="n">
-        <v>80100</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611593</v>
+        <v>611539</v>
       </c>
       <c r="R60" t="n">
-        <v>7203711</v>
+        <v>7203643</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6598,9 +6588,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6615,57 +6615,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779320</v>
+        <v>125779869</v>
       </c>
       <c r="B61" t="n">
-        <v>91597</v>
+        <v>80075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1506</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611543</v>
+        <v>611687</v>
       </c>
       <c r="R61" t="n">
-        <v>7203697</v>
+        <v>7203684</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6712,22 +6712,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125780620</v>
+        <v>125779867</v>
       </c>
       <c r="B62" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6735,39 +6735,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611381</v>
+        <v>611694</v>
       </c>
       <c r="R62" t="n">
-        <v>7203809</v>
+        <v>7203678</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6794,12 +6789,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,22 +6809,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779850</v>
+        <v>125779842</v>
       </c>
       <c r="B63" t="n">
-        <v>98355</v>
+        <v>80104</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6837,21 +6832,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6856,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611637</v>
+        <v>611593</v>
       </c>
       <c r="R63" t="n">
-        <v>7203685</v>
+        <v>7203711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6923,45 +6918,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125776365</v>
+        <v>125780620</v>
       </c>
       <c r="B64" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611567</v>
+        <v>611381</v>
       </c>
       <c r="R64" t="n">
-        <v>7203714</v>
+        <v>7203809</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7008,22 +7008,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125779308</v>
+        <v>125781642</v>
       </c>
       <c r="B65" t="n">
-        <v>80100</v>
+        <v>56843</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7031,37 +7031,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611684</v>
+        <v>611705</v>
       </c>
       <c r="R65" t="n">
-        <v>7203690</v>
+        <v>7203676</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7088,9 +7093,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7105,12 +7120,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7331,10 +7346,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125781642</v>
+        <v>125779308</v>
       </c>
       <c r="B68" t="n">
-        <v>56843</v>
+        <v>80104</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7342,42 +7357,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611705</v>
+        <v>611684</v>
       </c>
       <c r="R68" t="n">
-        <v>7203676</v>
+        <v>7203690</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7404,19 +7414,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7431,57 +7431,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125779339</v>
+        <v>125776142</v>
       </c>
       <c r="B69" t="n">
-        <v>78968</v>
+        <v>91806</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611640</v>
+        <v>611684</v>
       </c>
       <c r="R69" t="n">
-        <v>7203677</v>
+        <v>7203683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7528,12 +7528,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7543,7 +7543,7 @@
         <v>125779859</v>
       </c>
       <c r="B70" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779333</v>
+        <v>125779339</v>
       </c>
       <c r="B71" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7649,21 +7649,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611659</v>
+        <v>611640</v>
       </c>
       <c r="R71" t="n">
-        <v>7203648</v>
+        <v>7203677</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7735,45 +7735,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125776142</v>
+        <v>125779333</v>
       </c>
       <c r="B72" t="n">
-        <v>91802</v>
+        <v>91250</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>760</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611684</v>
+        <v>611659</v>
       </c>
       <c r="R72" t="n">
-        <v>7203683</v>
+        <v>7203648</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7820,22 +7820,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779771</v>
+        <v>125779880</v>
       </c>
       <c r="B73" t="n">
-        <v>80071</v>
+        <v>91250</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7843,21 +7843,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611686</v>
+        <v>611743</v>
       </c>
       <c r="R73" t="n">
-        <v>7203685</v>
+        <v>7203706</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7917,22 +7917,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779880</v>
+        <v>125779340</v>
       </c>
       <c r="B74" t="n">
-        <v>91246</v>
+        <v>78972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,34 +7940,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611743</v>
+        <v>611680</v>
       </c>
       <c r="R74" t="n">
-        <v>7203706</v>
+        <v>7203713</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,22 +8014,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779340</v>
+        <v>125779771</v>
       </c>
       <c r="B75" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,34 +8037,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611680</v>
+        <v>611686</v>
       </c>
       <c r="R75" t="n">
-        <v>7203713</v>
+        <v>7203685</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,12 +8111,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
         <v>125779312</v>
       </c>
       <c r="B76" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>125779310</v>
       </c>
       <c r="B77" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125781627</v>
+        <v>125779313</v>
       </c>
       <c r="B78" t="n">
-        <v>91193</v>
+        <v>98359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,21 +8328,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8352,13 +8352,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611526</v>
+        <v>611663</v>
       </c>
       <c r="R78" t="n">
-        <v>7203708</v>
+        <v>7203664</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,19 +8385,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8412,22 +8402,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779875</v>
+        <v>125779847</v>
       </c>
       <c r="B79" t="n">
-        <v>80107</v>
+        <v>98359</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8435,21 +8425,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8459,10 +8449,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611687</v>
+        <v>611502</v>
       </c>
       <c r="R79" t="n">
-        <v>7203684</v>
+        <v>7203644</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8521,10 +8511,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779307</v>
+        <v>125781627</v>
       </c>
       <c r="B80" t="n">
-        <v>80100</v>
+        <v>91197</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8532,21 +8522,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8556,13 +8546,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611707</v>
+        <v>611526</v>
       </c>
       <c r="R80" t="n">
-        <v>7203701</v>
+        <v>7203708</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8589,9 +8579,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,12 +8606,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8621,7 +8621,7 @@
         <v>125779332</v>
       </c>
       <c r="B81" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779313</v>
+        <v>125779875</v>
       </c>
       <c r="B82" t="n">
-        <v>98355</v>
+        <v>80111</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611663</v>
+        <v>611687</v>
       </c>
       <c r="R82" t="n">
-        <v>7203664</v>
+        <v>7203684</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8800,22 +8800,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779847</v>
+        <v>125779307</v>
       </c>
       <c r="B83" t="n">
-        <v>98355</v>
+        <v>80104</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8823,34 +8823,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611502</v>
+        <v>611707</v>
       </c>
       <c r="R83" t="n">
-        <v>7203644</v>
+        <v>7203701</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,60 +8897,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125779873</v>
+        <v>125781650</v>
       </c>
       <c r="B84" t="n">
-        <v>80107</v>
+        <v>91601</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611693</v>
+        <v>611521</v>
       </c>
       <c r="R84" t="n">
-        <v>7203707</v>
+        <v>7203626</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,9 +8977,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8994,65 +9004,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125781638</v>
+        <v>125776368</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>91806</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611645</v>
+        <v>611705</v>
       </c>
       <c r="R85" t="n">
-        <v>7203676</v>
+        <v>7203679</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9079,19 +9084,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9106,65 +9101,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125779347</v>
+        <v>125779873</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>80111</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611688</v>
+        <v>611693</v>
       </c>
       <c r="R86" t="n">
-        <v>7203713</v>
+        <v>7203707</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9199,11 +9186,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9216,57 +9198,62 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125781650</v>
+        <v>125781638</v>
       </c>
       <c r="B87" t="n">
-        <v>91597</v>
+        <v>57651</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611521</v>
+        <v>611645</v>
       </c>
       <c r="R87" t="n">
-        <v>7203626</v>
+        <v>7203676</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9298,7 +9285,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9308,7 +9295,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9335,45 +9322,53 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125776368</v>
+        <v>125779347</v>
       </c>
       <c r="B88" t="n">
-        <v>91802</v>
+        <v>57651</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611705</v>
+        <v>611688</v>
       </c>
       <c r="R88" t="n">
-        <v>7203679</v>
+        <v>7203713</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9408,6 +9403,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,12 +9420,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9435,7 +9435,7 @@
         <v>125779874</v>
       </c>
       <c r="B89" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>125779324</v>
       </c>
       <c r="B90" t="n">
-        <v>80099</v>
+        <v>80103</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>125776127</v>
       </c>
       <c r="B91" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>125779764</v>
       </c>
       <c r="B92" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>125779846</v>
       </c>
       <c r="B93" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>125779852</v>
       </c>
       <c r="B94" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10014,10 +10014,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779349</v>
+        <v>125779885</v>
       </c>
       <c r="B95" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,42 +10025,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611652</v>
+        <v>611661</v>
       </c>
       <c r="R95" t="n">
-        <v>7203627</v>
+        <v>7203604</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10095,11 +10087,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10112,57 +10099,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779885</v>
+        <v>125779314</v>
       </c>
       <c r="B96" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611661</v>
+        <v>611663</v>
       </c>
       <c r="R96" t="n">
-        <v>7203604</v>
+        <v>7203673</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10209,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10224,7 +10211,7 @@
         <v>125779302</v>
       </c>
       <c r="B97" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10318,45 +10305,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779314</v>
+        <v>125779349</v>
       </c>
       <c r="B98" t="n">
-        <v>98355</v>
+        <v>57651</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611663</v>
+        <v>611652</v>
       </c>
       <c r="R98" t="n">
-        <v>7203673</v>
+        <v>7203627</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10389,6 +10384,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10418,7 +10418,7 @@
         <v>125779851</v>
       </c>
       <c r="B99" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779299</v>
+        <v>125779329</v>
       </c>
       <c r="B100" t="n">
-        <v>75067</v>
+        <v>80075</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10523,21 +10523,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611561</v>
+        <v>611623</v>
       </c>
       <c r="R100" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10609,45 +10609,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779329</v>
+        <v>125779772</v>
       </c>
       <c r="B101" t="n">
-        <v>80071</v>
+        <v>80111</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611623</v>
+        <v>611680</v>
       </c>
       <c r="R101" t="n">
-        <v>7203677</v>
+        <v>7203679</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,57 +10694,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779772</v>
+        <v>125779299</v>
       </c>
       <c r="B102" t="n">
-        <v>80107</v>
+        <v>75067</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611680</v>
+        <v>611561</v>
       </c>
       <c r="R102" t="n">
-        <v>7203679</v>
+        <v>7203692</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>125803940</v>
       </c>
       <c r="B104" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>125803917</v>
       </c>
       <c r="B105" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>125803668</v>
       </c>
       <c r="B106" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>125803950</v>
       </c>
       <c r="B107" t="n">
-        <v>91597</v>
+        <v>91601</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>125803771</v>
       </c>
       <c r="B111" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -4398,45 +4398,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779844</v>
+        <v>125779337</v>
       </c>
       <c r="B39" t="n">
-        <v>80104</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611644</v>
+        <v>611615</v>
       </c>
       <c r="R39" t="n">
-        <v>7203690</v>
+        <v>7203678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,22 +4483,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779773</v>
+        <v>125779844</v>
       </c>
       <c r="B40" t="n">
-        <v>80111</v>
+        <v>80104</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611662</v>
+        <v>611644</v>
       </c>
       <c r="R40" t="n">
-        <v>7203612</v>
+        <v>7203690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,65 +4580,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779318</v>
+        <v>125779773</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>80111</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611725</v>
+        <v>611662</v>
       </c>
       <c r="R41" t="n">
-        <v>7203707</v>
+        <v>7203612</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4673,11 +4665,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4690,22 +4677,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779337</v>
+        <v>125779319</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4713,34 +4700,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611615</v>
+        <v>611663</v>
       </c>
       <c r="R42" t="n">
-        <v>7203678</v>
+        <v>7203613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4773,6 +4768,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4799,7 +4799,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779319</v>
+        <v>125779316</v>
       </c>
       <c r="B43" t="n">
         <v>57651</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611663</v>
+        <v>611507</v>
       </c>
       <c r="R43" t="n">
-        <v>7203613</v>
+        <v>7203685</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4909,7 +4909,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779316</v>
+        <v>125779318</v>
       </c>
       <c r="B44" t="n">
         <v>57651</v>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611507</v>
+        <v>611725</v>
       </c>
       <c r="R44" t="n">
-        <v>7203685</v>
+        <v>7203707</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6035,45 +6035,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779850</v>
+        <v>125780620</v>
       </c>
       <c r="B55" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611637</v>
+        <v>611381</v>
       </c>
       <c r="R55" t="n">
-        <v>7203685</v>
+        <v>7203809</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6100,12 +6105,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6120,57 +6125,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125776365</v>
+        <v>125779344</v>
       </c>
       <c r="B56" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611567</v>
+        <v>611653</v>
       </c>
       <c r="R56" t="n">
-        <v>7203714</v>
+        <v>7203626</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,22 +6222,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779344</v>
+        <v>125779881</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6240,34 +6245,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611653</v>
+        <v>611650</v>
       </c>
       <c r="R57" t="n">
-        <v>7203626</v>
+        <v>7203647</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6314,57 +6319,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779881</v>
+        <v>125779320</v>
       </c>
       <c r="B58" t="n">
-        <v>91250</v>
+        <v>91601</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611650</v>
+        <v>611543</v>
       </c>
       <c r="R58" t="n">
-        <v>7203647</v>
+        <v>7203697</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6411,44 +6416,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779320</v>
+        <v>125781664</v>
       </c>
       <c r="B59" t="n">
-        <v>91601</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6458,13 +6463,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611543</v>
+        <v>611539</v>
       </c>
       <c r="R59" t="n">
-        <v>7203697</v>
+        <v>7203643</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6491,9 +6496,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6508,22 +6523,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125781664</v>
+        <v>125779869</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6531,37 +6546,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611539</v>
+        <v>611687</v>
       </c>
       <c r="R60" t="n">
-        <v>7203643</v>
+        <v>7203684</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6588,19 +6603,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6615,19 +6620,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779869</v>
+        <v>125779867</v>
       </c>
       <c r="B61" t="n">
         <v>80075</v>
@@ -6662,10 +6667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611687</v>
+        <v>611694</v>
       </c>
       <c r="R61" t="n">
-        <v>7203684</v>
+        <v>7203678</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6724,32 +6729,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779867</v>
+        <v>125779842</v>
       </c>
       <c r="B62" t="n">
-        <v>80075</v>
+        <v>80104</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6759,10 +6764,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611694</v>
+        <v>611593</v>
       </c>
       <c r="R62" t="n">
-        <v>7203678</v>
+        <v>7203711</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6821,10 +6826,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779842</v>
+        <v>125779850</v>
       </c>
       <c r="B63" t="n">
-        <v>80104</v>
+        <v>98359</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6832,21 +6837,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6856,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611593</v>
+        <v>611637</v>
       </c>
       <c r="R63" t="n">
-        <v>7203711</v>
+        <v>7203685</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6918,50 +6923,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125780620</v>
+        <v>125776365</v>
       </c>
       <c r="B64" t="n">
-        <v>57651</v>
+        <v>98359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611381</v>
+        <v>611567</v>
       </c>
       <c r="R64" t="n">
-        <v>7203809</v>
+        <v>7203714</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7008,12 +7008,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8026,45 +8026,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779771</v>
+        <v>125779312</v>
       </c>
       <c r="B75" t="n">
-        <v>80075</v>
+        <v>98359</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611686</v>
+        <v>611683</v>
       </c>
       <c r="R75" t="n">
-        <v>7203685</v>
+        <v>7203677</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,19 +8111,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779312</v>
+        <v>125779310</v>
       </c>
       <c r="B76" t="n">
         <v>98359</v>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611683</v>
+        <v>611700</v>
       </c>
       <c r="R76" t="n">
-        <v>7203677</v>
+        <v>7203703</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779310</v>
+        <v>125779771</v>
       </c>
       <c r="B77" t="n">
-        <v>98359</v>
+        <v>80075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611700</v>
+        <v>611686</v>
       </c>
       <c r="R77" t="n">
-        <v>7203703</v>
+        <v>7203685</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8305,22 +8305,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125779313</v>
+        <v>125779875</v>
       </c>
       <c r="B78" t="n">
-        <v>98359</v>
+        <v>80111</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,34 +8328,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611663</v>
+        <v>611687</v>
       </c>
       <c r="R78" t="n">
-        <v>7203664</v>
+        <v>7203684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8402,22 +8402,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779847</v>
+        <v>125779307</v>
       </c>
       <c r="B79" t="n">
-        <v>98359</v>
+        <v>80104</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,34 +8425,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611502</v>
+        <v>611707</v>
       </c>
       <c r="R79" t="n">
-        <v>7203644</v>
+        <v>7203701</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,12 +8499,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779875</v>
+        <v>125779313</v>
       </c>
       <c r="B82" t="n">
-        <v>80111</v>
+        <v>98359</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8726,34 +8726,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611687</v>
+        <v>611663</v>
       </c>
       <c r="R82" t="n">
-        <v>7203684</v>
+        <v>7203664</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8800,22 +8800,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779307</v>
+        <v>125779847</v>
       </c>
       <c r="B83" t="n">
-        <v>80104</v>
+        <v>98359</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8823,34 +8823,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611707</v>
+        <v>611502</v>
       </c>
       <c r="R83" t="n">
-        <v>7203701</v>
+        <v>7203644</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,12 +8897,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125776148</v>
+        <v>125779345</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611660</v>
+        <v>611661</v>
       </c>
       <c r="R2" t="n">
-        <v>7203684</v>
+        <v>7203650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +756,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -760,19 +773,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125776367</v>
+        <v>125776148</v>
       </c>
       <c r="B3" t="n">
         <v>78972</v>
@@ -803,14 +816,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611653</v>
+        <v>611660</v>
       </c>
       <c r="R3" t="n">
-        <v>7203665</v>
+        <v>7203684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +870,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125779334</v>
+        <v>125776367</v>
       </c>
       <c r="B4" t="n">
         <v>78972</v>
@@ -900,14 +913,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611526</v>
+        <v>611653</v>
       </c>
       <c r="R4" t="n">
-        <v>7203706</v>
+        <v>7203665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +967,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125779345</v>
+        <v>125779334</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611661</v>
+        <v>611526</v>
       </c>
       <c r="R5" t="n">
-        <v>7203650</v>
+        <v>7203706</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1050,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125781649</v>
+        <v>125781636</v>
       </c>
       <c r="B6" t="n">
-        <v>91528</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,34 +1087,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611536</v>
+        <v>611590</v>
       </c>
       <c r="R6" t="n">
-        <v>7203694</v>
+        <v>7203713</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1146,7 +1151,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1156,7 +1161,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125779303</v>
+        <v>125780621</v>
       </c>
       <c r="B7" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,34 +1199,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611631</v>
+        <v>611445</v>
       </c>
       <c r="R7" t="n">
-        <v>7203681</v>
+        <v>7203814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,12 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,12 +1278,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125781636</v>
+        <v>125781649</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>91528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611590</v>
+        <v>611536</v>
       </c>
       <c r="R9" t="n">
-        <v>7203713</v>
+        <v>7203694</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1462,7 +1467,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1472,7 +1477,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125780621</v>
+        <v>125779303</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>91232</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,39 +1515,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611445</v>
+        <v>611631</v>
       </c>
       <c r="R10" t="n">
-        <v>7203814</v>
+        <v>7203681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,19 +1589,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125779322</v>
+        <v>125779323</v>
       </c>
       <c r="B11" t="n">
         <v>80103</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611700</v>
+        <v>611667</v>
       </c>
       <c r="R11" t="n">
-        <v>7203701</v>
+        <v>7203673</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125781663</v>
+        <v>125779769</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1709,37 +1709,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611570</v>
+        <v>611696</v>
       </c>
       <c r="R12" t="n">
-        <v>7203700</v>
+        <v>7203681</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,19 +1766,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1793,57 +1783,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779769</v>
+        <v>125779322</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611696</v>
+        <v>611700</v>
       </c>
       <c r="R13" t="n">
-        <v>7203681</v>
+        <v>7203701</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,60 +1880,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125779323</v>
+        <v>125781637</v>
       </c>
       <c r="B14" t="n">
-        <v>80103</v>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611667</v>
+        <v>611631</v>
       </c>
       <c r="R14" t="n">
-        <v>7203673</v>
+        <v>7203695</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,9 +1965,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1987,22 +1992,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125776139</v>
+        <v>125780615</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2010,34 +2015,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611678</v>
+        <v>611292</v>
       </c>
       <c r="R15" t="n">
-        <v>7203688</v>
+        <v>7203703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,12 +2074,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2084,22 +2094,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125781637</v>
+        <v>125781663</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,39 +2117,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611631</v>
+        <v>611570</v>
       </c>
       <c r="R16" t="n">
-        <v>7203695</v>
+        <v>7203700</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2171,7 +2176,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2181,7 +2186,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2208,10 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125780615</v>
+        <v>125776139</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2219,39 +2224,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611292</v>
+        <v>611678</v>
       </c>
       <c r="R17" t="n">
-        <v>7203703</v>
+        <v>7203688</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,65 +2298,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779864</v>
+        <v>125779311</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611742</v>
+        <v>611690</v>
       </c>
       <c r="R18" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,11 +2383,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2408,22 +2395,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125779311</v>
+        <v>125776366</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2451,11 +2438,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611690</v>
+        <v>611679</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2505,57 +2492,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125776366</v>
+        <v>125779864</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>57651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611679</v>
+        <v>611742</v>
       </c>
       <c r="R20" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,6 +2585,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,12 +2602,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125780607</v>
+        <v>125779336</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,21 +2735,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611445</v>
+        <v>611575</v>
       </c>
       <c r="R22" t="n">
-        <v>7203816</v>
+        <v>7203712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,19 +2809,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125779336</v>
+        <v>125779338</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611575</v>
+        <v>611631</v>
       </c>
       <c r="R23" t="n">
-        <v>7203712</v>
+        <v>7203681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779338</v>
+        <v>125780607</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,21 +2929,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611631</v>
+        <v>611445</v>
       </c>
       <c r="R24" t="n">
-        <v>7203681</v>
+        <v>7203816</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2983,12 +2983,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,12 +3003,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3018,7 +3018,7 @@
         <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125781660</v>
+        <v>125780614</v>
       </c>
       <c r="B28" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3317,37 +3317,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611570</v>
+        <v>611292</v>
       </c>
       <c r="R28" t="n">
-        <v>7203708</v>
+        <v>7203687</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3371,22 +3376,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3406,52 +3401,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125779886</v>
+        <v>125776147</v>
       </c>
       <c r="B29" t="n">
-        <v>91806</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611704</v>
+        <v>611642</v>
       </c>
       <c r="R29" t="n">
-        <v>7203679</v>
+        <v>7203689</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,22 +3493,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125776147</v>
+        <v>125781660</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>91246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3521,37 +3516,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611642</v>
+        <v>611570</v>
       </c>
       <c r="R30" t="n">
-        <v>7203689</v>
+        <v>7203708</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3578,9 +3573,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3595,62 +3600,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125780614</v>
+        <v>125779886</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>91806</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611292</v>
+        <v>611704</v>
       </c>
       <c r="R31" t="n">
-        <v>7203687</v>
+        <v>7203679</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,12 +3697,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3712,7 +3712,7 @@
         <v>125779767</v>
       </c>
       <c r="B32" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3806,32 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779884</v>
+        <v>125779848</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611666</v>
+        <v>611545</v>
       </c>
       <c r="R33" t="n">
-        <v>7203678</v>
+        <v>7203710</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125781666</v>
+        <v>125780606</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,13 +3938,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611652</v>
+        <v>611311</v>
       </c>
       <c r="R34" t="n">
-        <v>7203680</v>
+        <v>7203689</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3968,22 +3968,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4003,17 +3993,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125780608</v>
+        <v>125781666</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,13 +4035,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611445</v>
+        <v>611652</v>
       </c>
       <c r="R35" t="n">
-        <v>7203816</v>
+        <v>7203680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4075,12 +4065,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125779834</v>
+        <v>125779884</v>
       </c>
       <c r="B36" t="n">
-        <v>75067</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,21 +4118,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611547</v>
+        <v>611666</v>
       </c>
       <c r="R36" t="n">
-        <v>7203635</v>
+        <v>7203678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125780606</v>
+        <v>125779834</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>75067</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611311</v>
+        <v>611547</v>
       </c>
       <c r="R37" t="n">
-        <v>7203689</v>
+        <v>7203635</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,57 +4289,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779848</v>
+        <v>125780608</v>
       </c>
       <c r="B38" t="n">
-        <v>98359</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611545</v>
+        <v>611445</v>
       </c>
       <c r="R38" t="n">
-        <v>7203710</v>
+        <v>7203816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,22 +4386,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779337</v>
+        <v>125779319</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,34 +4409,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611615</v>
+        <v>611663</v>
       </c>
       <c r="R39" t="n">
-        <v>7203678</v>
+        <v>7203613</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,6 +4477,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4495,45 +4508,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779844</v>
+        <v>125779316</v>
       </c>
       <c r="B40" t="n">
-        <v>80104</v>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611644</v>
+        <v>611507</v>
       </c>
       <c r="R40" t="n">
-        <v>7203690</v>
+        <v>7203685</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4568,6 +4589,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4580,57 +4606,65 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779773</v>
+        <v>125779318</v>
       </c>
       <c r="B41" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611662</v>
+        <v>611725</v>
       </c>
       <c r="R41" t="n">
-        <v>7203612</v>
+        <v>7203707</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4699,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4677,22 +4716,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779319</v>
+        <v>125779337</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,42 +4739,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611663</v>
+        <v>611615</v>
       </c>
       <c r="R42" t="n">
-        <v>7203613</v>
+        <v>7203678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,11 +4799,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4799,53 +4825,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779316</v>
+        <v>125779853</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611507</v>
+        <v>611691</v>
       </c>
       <c r="R43" t="n">
-        <v>7203685</v>
+        <v>7203679</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4880,11 +4898,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4897,65 +4910,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779318</v>
+        <v>125779773</v>
       </c>
       <c r="B44" t="n">
-        <v>57651</v>
+        <v>80111</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611725</v>
+        <v>611662</v>
       </c>
       <c r="R44" t="n">
-        <v>7203707</v>
+        <v>7203612</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4990,11 +4995,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5007,22 +5007,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779853</v>
+        <v>125779844</v>
       </c>
       <c r="B45" t="n">
-        <v>98359</v>
+        <v>80104</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611691</v>
+        <v>611644</v>
       </c>
       <c r="R45" t="n">
-        <v>7203679</v>
+        <v>7203690</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5430,32 +5430,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125779315</v>
+        <v>125779309</v>
       </c>
       <c r="B49" t="n">
-        <v>80076</v>
+        <v>80104</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611617</v>
+        <v>611679</v>
       </c>
       <c r="R49" t="n">
-        <v>7203677</v>
+        <v>7203682</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125781628</v>
+        <v>125779876</v>
       </c>
       <c r="B50" t="n">
-        <v>91197</v>
+        <v>80111</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5538,37 +5538,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611568</v>
+        <v>611661</v>
       </c>
       <c r="R50" t="n">
-        <v>7203718</v>
+        <v>7203604</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5595,19 +5595,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5622,44 +5612,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779343</v>
+        <v>125781628</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>91197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,13 +5659,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611670</v>
+        <v>611568</v>
       </c>
       <c r="R51" t="n">
-        <v>7203656</v>
+        <v>7203718</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5702,9 +5692,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5719,44 +5719,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779309</v>
+        <v>125779315</v>
       </c>
       <c r="B52" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5766,10 +5766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611679</v>
+        <v>611617</v>
       </c>
       <c r="R52" t="n">
-        <v>7203682</v>
+        <v>7203677</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5828,45 +5828,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779876</v>
+        <v>125779863</v>
       </c>
       <c r="B53" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611661</v>
+        <v>611623</v>
       </c>
       <c r="R53" t="n">
-        <v>7203604</v>
+        <v>7203692</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5899,6 +5907,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5925,10 +5938,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779863</v>
+        <v>125779343</v>
       </c>
       <c r="B54" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5936,42 +5949,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611623</v>
+        <v>611670</v>
       </c>
       <c r="R54" t="n">
-        <v>7203692</v>
+        <v>7203656</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6006,11 +6011,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6023,62 +6023,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125780620</v>
+        <v>125779842</v>
       </c>
       <c r="B55" t="n">
-        <v>57651</v>
+        <v>80104</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611381</v>
+        <v>611593</v>
       </c>
       <c r="R55" t="n">
-        <v>7203809</v>
+        <v>7203711</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6105,12 +6100,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6125,22 +6120,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125779344</v>
+        <v>125779867</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6148,34 +6143,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611653</v>
+        <v>611694</v>
       </c>
       <c r="R56" t="n">
-        <v>7203626</v>
+        <v>7203678</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6222,22 +6217,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779881</v>
+        <v>125779869</v>
       </c>
       <c r="B57" t="n">
-        <v>91250</v>
+        <v>80075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6245,21 +6240,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6269,10 +6264,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611650</v>
+        <v>611687</v>
       </c>
       <c r="R57" t="n">
-        <v>7203647</v>
+        <v>7203684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6331,45 +6326,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779320</v>
+        <v>125780620</v>
       </c>
       <c r="B58" t="n">
-        <v>91601</v>
+        <v>57651</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611543</v>
+        <v>611381</v>
       </c>
       <c r="R58" t="n">
-        <v>7203697</v>
+        <v>7203809</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6396,12 +6396,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6416,44 +6416,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125781664</v>
+        <v>125779320</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>91601</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6463,13 +6463,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611539</v>
+        <v>611543</v>
       </c>
       <c r="R59" t="n">
-        <v>7203643</v>
+        <v>7203697</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6496,19 +6496,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6523,22 +6513,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779869</v>
+        <v>125781664</v>
       </c>
       <c r="B60" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6546,37 +6536,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611687</v>
+        <v>611539</v>
       </c>
       <c r="R60" t="n">
-        <v>7203684</v>
+        <v>7203643</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6603,9 +6593,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6620,22 +6620,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779867</v>
+        <v>125779344</v>
       </c>
       <c r="B61" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6643,34 +6643,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611694</v>
+        <v>611653</v>
       </c>
       <c r="R61" t="n">
-        <v>7203678</v>
+        <v>7203626</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6717,44 +6717,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779842</v>
+        <v>125779881</v>
       </c>
       <c r="B62" t="n">
-        <v>80104</v>
+        <v>91250</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611593</v>
+        <v>611650</v>
       </c>
       <c r="R62" t="n">
-        <v>7203711</v>
+        <v>7203647</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6829,7 +6829,7 @@
         <v>125779850</v>
       </c>
       <c r="B63" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>125776365</v>
       </c>
       <c r="B64" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7020,10 +7020,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125781642</v>
+        <v>125779308</v>
       </c>
       <c r="B65" t="n">
-        <v>56843</v>
+        <v>80104</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7031,42 +7031,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611705</v>
+        <v>611684</v>
       </c>
       <c r="R65" t="n">
-        <v>7203676</v>
+        <v>7203690</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7093,19 +7088,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7120,12 +7105,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7346,10 +7331,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125779308</v>
+        <v>125781642</v>
       </c>
       <c r="B68" t="n">
-        <v>80104</v>
+        <v>56843</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7357,37 +7342,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611684</v>
+        <v>611705</v>
       </c>
       <c r="R68" t="n">
-        <v>7203690</v>
+        <v>7203676</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7414,9 +7404,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7431,57 +7431,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125776142</v>
+        <v>125779339</v>
       </c>
       <c r="B69" t="n">
-        <v>91806</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611684</v>
+        <v>611640</v>
       </c>
       <c r="R69" t="n">
-        <v>7203683</v>
+        <v>7203677</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7528,57 +7528,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125779859</v>
+        <v>125776142</v>
       </c>
       <c r="B70" t="n">
-        <v>80076</v>
+        <v>91806</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611687</v>
+        <v>611684</v>
       </c>
       <c r="R70" t="n">
-        <v>7203684</v>
+        <v>7203683</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,29 +7619,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779339</v>
+        <v>125779859</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7649,34 +7648,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611640</v>
+        <v>611687</v>
       </c>
       <c r="R71" t="n">
-        <v>7203677</v>
+        <v>7203684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,18 +7716,19 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8029,7 +8029,7 @@
         <v>125779312</v>
       </c>
       <c r="B75" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>125779310</v>
       </c>
       <c r="B76" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8511,32 +8511,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125781627</v>
+        <v>125779332</v>
       </c>
       <c r="B80" t="n">
-        <v>91197</v>
+        <v>91250</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8546,13 +8546,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611526</v>
+        <v>611525</v>
       </c>
       <c r="R80" t="n">
-        <v>7203708</v>
+        <v>7203705</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8579,19 +8579,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,57 +8596,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779332</v>
+        <v>125779847</v>
       </c>
       <c r="B81" t="n">
-        <v>91250</v>
+        <v>98360</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611525</v>
+        <v>611502</v>
       </c>
       <c r="R81" t="n">
-        <v>7203705</v>
+        <v>7203644</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8703,22 +8693,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779313</v>
+        <v>125781627</v>
       </c>
       <c r="B82" t="n">
-        <v>98359</v>
+        <v>91197</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8726,21 +8716,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8750,13 +8740,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611663</v>
+        <v>611526</v>
       </c>
       <c r="R82" t="n">
-        <v>7203664</v>
+        <v>7203708</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8783,9 +8773,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8800,22 +8800,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779847</v>
+        <v>125779313</v>
       </c>
       <c r="B83" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,14 +8843,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611502</v>
+        <v>611663</v>
       </c>
       <c r="R83" t="n">
-        <v>7203644</v>
+        <v>7203664</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,60 +8897,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125781650</v>
+        <v>125779873</v>
       </c>
       <c r="B84" t="n">
-        <v>91601</v>
+        <v>80111</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611521</v>
+        <v>611693</v>
       </c>
       <c r="R84" t="n">
-        <v>7203626</v>
+        <v>7203707</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,19 +8977,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9004,60 +8994,65 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125776368</v>
+        <v>125781638</v>
       </c>
       <c r="B85" t="n">
-        <v>91806</v>
+        <v>57651</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611705</v>
+        <v>611645</v>
       </c>
       <c r="R85" t="n">
-        <v>7203679</v>
+        <v>7203676</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9084,9 +9079,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9101,57 +9106,65 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125779873</v>
+        <v>125779347</v>
       </c>
       <c r="B86" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611693</v>
+        <v>611688</v>
       </c>
       <c r="R86" t="n">
-        <v>7203707</v>
+        <v>7203713</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9186,6 +9199,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9198,62 +9216,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125781638</v>
+        <v>125781650</v>
       </c>
       <c r="B87" t="n">
-        <v>57651</v>
+        <v>91601</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611645</v>
+        <v>611521</v>
       </c>
       <c r="R87" t="n">
-        <v>7203676</v>
+        <v>7203626</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9285,7 +9298,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9295,7 +9308,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9322,53 +9335,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125779347</v>
+        <v>125776368</v>
       </c>
       <c r="B88" t="n">
-        <v>57651</v>
+        <v>91806</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611688</v>
+        <v>611705</v>
       </c>
       <c r="R88" t="n">
-        <v>7203713</v>
+        <v>7203679</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9403,11 +9408,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,22 +9420,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125779874</v>
+        <v>125779324</v>
       </c>
       <c r="B89" t="n">
-        <v>80111</v>
+        <v>80103</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9443,34 +9443,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>611704</v>
+        <v>611659</v>
       </c>
       <c r="R89" t="n">
-        <v>7203676</v>
+        <v>7203623</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9517,22 +9517,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125779324</v>
+        <v>125779874</v>
       </c>
       <c r="B90" t="n">
-        <v>80103</v>
+        <v>80111</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9540,34 +9540,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>611659</v>
+        <v>611704</v>
       </c>
       <c r="R90" t="n">
-        <v>7203623</v>
+        <v>7203676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9614,22 +9614,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125776127</v>
+        <v>125779852</v>
       </c>
       <c r="B91" t="n">
-        <v>80111</v>
+        <v>98360</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,31 +9637,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611681</v>
+        <v>611711</v>
       </c>
       <c r="R91" t="n">
         <v>7203685</v>
@@ -9711,19 +9711,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125779764</v>
+        <v>125779846</v>
       </c>
       <c r="B92" t="n">
         <v>80104</v>
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611648</v>
+        <v>611717</v>
       </c>
       <c r="R92" t="n">
-        <v>7203687</v>
+        <v>7203689</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9808,19 +9808,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125779846</v>
+        <v>125779764</v>
       </c>
       <c r="B93" t="n">
         <v>80104</v>
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611717</v>
+        <v>611648</v>
       </c>
       <c r="R93" t="n">
-        <v>7203689</v>
+        <v>7203687</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,22 +9905,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125779852</v>
+        <v>125776127</v>
       </c>
       <c r="B94" t="n">
-        <v>98359</v>
+        <v>80111</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9928,31 +9928,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611711</v>
+        <v>611681</v>
       </c>
       <c r="R94" t="n">
         <v>7203685</v>
@@ -10002,22 +10002,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779885</v>
+        <v>125779302</v>
       </c>
       <c r="B95" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,34 +10025,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611661</v>
+        <v>611618</v>
       </c>
       <c r="R95" t="n">
-        <v>7203604</v>
+        <v>7203674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10099,57 +10099,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779314</v>
+        <v>125779885</v>
       </c>
       <c r="B96" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611663</v>
+        <v>611661</v>
       </c>
       <c r="R96" t="n">
-        <v>7203673</v>
+        <v>7203604</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,22 +10196,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779302</v>
+        <v>125779349</v>
       </c>
       <c r="B97" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10219,34 +10219,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611618</v>
+        <v>611652</v>
       </c>
       <c r="R97" t="n">
-        <v>7203674</v>
+        <v>7203627</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10279,6 +10287,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10305,53 +10318,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779349</v>
+        <v>125779314</v>
       </c>
       <c r="B98" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611652</v>
+        <v>611663</v>
       </c>
       <c r="R98" t="n">
-        <v>7203627</v>
+        <v>7203673</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10384,11 +10389,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10418,7 +10418,7 @@
         <v>125779851</v>
       </c>
       <c r="B99" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779329</v>
+        <v>125779299</v>
       </c>
       <c r="B100" t="n">
-        <v>80075</v>
+        <v>75067</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10523,21 +10523,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611623</v>
+        <v>611561</v>
       </c>
       <c r="R100" t="n">
-        <v>7203677</v>
+        <v>7203692</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10609,45 +10609,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779772</v>
+        <v>125779329</v>
       </c>
       <c r="B101" t="n">
-        <v>80111</v>
+        <v>80075</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611680</v>
+        <v>611623</v>
       </c>
       <c r="R101" t="n">
-        <v>7203679</v>
+        <v>7203677</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,57 +10694,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779299</v>
+        <v>125779772</v>
       </c>
       <c r="B102" t="n">
-        <v>75067</v>
+        <v>80111</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611561</v>
+        <v>611680</v>
       </c>
       <c r="R102" t="n">
-        <v>7203692</v>
+        <v>7203679</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11115,42 +11115,41 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125803668</v>
+        <v>125803950</v>
       </c>
       <c r="B106" t="n">
-        <v>98359</v>
+        <v>91601</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221952</v>
+        <v>1506</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11158,10 +11157,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>611679</v>
+        <v>611534</v>
       </c>
       <c r="R106" t="n">
-        <v>7203707</v>
+        <v>7203710</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11221,41 +11220,42 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125803950</v>
+        <v>125803668</v>
       </c>
       <c r="B107" t="n">
-        <v>91601</v>
+        <v>98360</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1506</v>
+        <v>221952</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>611534</v>
+        <v>611679</v>
       </c>
       <c r="R107" t="n">
-        <v>7203710</v>
+        <v>7203707</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125781636</v>
+        <v>125781662</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,39 +1087,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611590</v>
+        <v>611570</v>
       </c>
       <c r="R6" t="n">
-        <v>7203713</v>
+        <v>7203707</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1151,7 +1146,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1161,7 +1156,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125780621</v>
+        <v>125781649</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>91528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1199,42 +1194,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611445</v>
+        <v>611536</v>
       </c>
       <c r="R7" t="n">
-        <v>7203814</v>
+        <v>7203694</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,12 +1248,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125781662</v>
+        <v>125779303</v>
       </c>
       <c r="B8" t="n">
-        <v>91250</v>
+        <v>91232</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611570</v>
+        <v>611631</v>
       </c>
       <c r="R8" t="n">
-        <v>7203707</v>
+        <v>7203681</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1358,19 +1358,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1385,22 +1375,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125781649</v>
+        <v>125781636</v>
       </c>
       <c r="B9" t="n">
-        <v>91528</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611536</v>
+        <v>611590</v>
       </c>
       <c r="R9" t="n">
-        <v>7203694</v>
+        <v>7203713</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1467,7 +1462,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1477,7 +1472,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125779303</v>
+        <v>125780621</v>
       </c>
       <c r="B10" t="n">
-        <v>91232</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1515,34 +1510,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611631</v>
+        <v>611445</v>
       </c>
       <c r="R10" t="n">
-        <v>7203681</v>
+        <v>7203814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1589,12 +1589,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2310,45 +2310,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779311</v>
+        <v>125779864</v>
       </c>
       <c r="B18" t="n">
-        <v>98360</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611690</v>
+        <v>611742</v>
       </c>
       <c r="R18" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,6 +2391,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2395,19 +2408,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125776366</v>
+        <v>125779311</v>
       </c>
       <c r="B19" t="n">
         <v>98360</v>
@@ -2438,11 +2451,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611679</v>
+        <v>611690</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2492,65 +2505,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125779864</v>
+        <v>125776366</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611742</v>
+        <v>611679</v>
       </c>
       <c r="R20" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2585,11 +2590,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,12 +2602,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2724,32 +2724,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125779336</v>
+        <v>125780622</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611575</v>
+        <v>611490</v>
       </c>
       <c r="R22" t="n">
-        <v>7203712</v>
+        <v>7203838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,19 +2809,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125779338</v>
+        <v>125779336</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611631</v>
+        <v>611575</v>
       </c>
       <c r="R23" t="n">
-        <v>7203681</v>
+        <v>7203712</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125780607</v>
+        <v>125779338</v>
       </c>
       <c r="B24" t="n">
-        <v>80076</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,21 +2929,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611445</v>
+        <v>611631</v>
       </c>
       <c r="R24" t="n">
-        <v>7203816</v>
+        <v>7203681</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2983,12 +2983,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,44 +3003,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125780622</v>
+        <v>125780607</v>
       </c>
       <c r="B25" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3050,10 +3050,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>611490</v>
+        <v>611445</v>
       </c>
       <c r="R25" t="n">
-        <v>7203838</v>
+        <v>7203816</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4398,53 +4398,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779319</v>
+        <v>125779773</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>80111</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611663</v>
+        <v>611662</v>
       </c>
       <c r="R39" t="n">
-        <v>7203613</v>
+        <v>7203612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4479,11 +4471,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4496,65 +4483,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779316</v>
+        <v>125779844</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>80104</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611507</v>
+        <v>611644</v>
       </c>
       <c r="R40" t="n">
-        <v>7203685</v>
+        <v>7203690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4589,11 +4568,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4606,22 +4580,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779318</v>
+        <v>125779337</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,42 +4603,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611725</v>
+        <v>611615</v>
       </c>
       <c r="R41" t="n">
-        <v>7203707</v>
+        <v>7203678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,11 +4663,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4728,10 +4689,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779337</v>
+        <v>125779319</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4739,34 +4700,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611615</v>
+        <v>611663</v>
       </c>
       <c r="R42" t="n">
-        <v>7203678</v>
+        <v>7203613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4799,6 +4768,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4825,45 +4799,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779853</v>
+        <v>125779316</v>
       </c>
       <c r="B43" t="n">
-        <v>98360</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611691</v>
+        <v>611507</v>
       </c>
       <c r="R43" t="n">
-        <v>7203679</v>
+        <v>7203685</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4898,6 +4880,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4910,57 +4897,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779773</v>
+        <v>125779318</v>
       </c>
       <c r="B44" t="n">
-        <v>80111</v>
+        <v>57651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611662</v>
+        <v>611725</v>
       </c>
       <c r="R44" t="n">
-        <v>7203612</v>
+        <v>7203707</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,6 +4990,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5007,22 +5007,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779844</v>
+        <v>125779853</v>
       </c>
       <c r="B45" t="n">
-        <v>80104</v>
+        <v>98360</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611644</v>
+        <v>611691</v>
       </c>
       <c r="R45" t="n">
-        <v>7203690</v>
+        <v>7203679</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5624,48 +5624,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125781628</v>
+        <v>125779863</v>
       </c>
       <c r="B51" t="n">
-        <v>91197</v>
+        <v>57651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611568</v>
+        <v>611623</v>
       </c>
       <c r="R51" t="n">
-        <v>7203718</v>
+        <v>7203692</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5692,19 +5700,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:19</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5719,12 +5722,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5828,56 +5831,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779863</v>
+        <v>125781628</v>
       </c>
       <c r="B53" t="n">
-        <v>57651</v>
+        <v>91197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611623</v>
+        <v>611568</v>
       </c>
       <c r="R53" t="n">
-        <v>7203692</v>
+        <v>7203718</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5904,14 +5899,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5926,12 +5926,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7832,10 +7832,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779880</v>
+        <v>125779771</v>
       </c>
       <c r="B73" t="n">
-        <v>91250</v>
+        <v>80075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7843,21 +7843,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611743</v>
+        <v>611686</v>
       </c>
       <c r="R73" t="n">
-        <v>7203706</v>
+        <v>7203685</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7917,22 +7917,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779340</v>
+        <v>125779880</v>
       </c>
       <c r="B74" t="n">
-        <v>78972</v>
+        <v>91250</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,34 +7940,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611680</v>
+        <v>611743</v>
       </c>
       <c r="R74" t="n">
-        <v>7203713</v>
+        <v>7203706</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,44 +8014,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779312</v>
+        <v>125779340</v>
       </c>
       <c r="B75" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611683</v>
+        <v>611680</v>
       </c>
       <c r="R75" t="n">
-        <v>7203677</v>
+        <v>7203713</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8123,7 +8123,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779310</v>
+        <v>125779312</v>
       </c>
       <c r="B76" t="n">
         <v>98360</v>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611700</v>
+        <v>611683</v>
       </c>
       <c r="R76" t="n">
-        <v>7203703</v>
+        <v>7203677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779771</v>
+        <v>125779310</v>
       </c>
       <c r="B77" t="n">
-        <v>80075</v>
+        <v>98360</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611686</v>
+        <v>611700</v>
       </c>
       <c r="R77" t="n">
-        <v>7203685</v>
+        <v>7203703</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8305,12 +8305,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8414,10 +8414,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779307</v>
+        <v>125779313</v>
       </c>
       <c r="B79" t="n">
-        <v>80104</v>
+        <v>98360</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,21 +8425,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611707</v>
+        <v>611663</v>
       </c>
       <c r="R79" t="n">
-        <v>7203701</v>
+        <v>7203664</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8511,45 +8511,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779332</v>
+        <v>125779847</v>
       </c>
       <c r="B80" t="n">
-        <v>91250</v>
+        <v>98360</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611525</v>
+        <v>611502</v>
       </c>
       <c r="R80" t="n">
-        <v>7203705</v>
+        <v>7203644</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8596,22 +8596,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779847</v>
+        <v>125779307</v>
       </c>
       <c r="B81" t="n">
-        <v>98360</v>
+        <v>80104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8619,34 +8619,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611502</v>
+        <v>611707</v>
       </c>
       <c r="R81" t="n">
-        <v>7203644</v>
+        <v>7203701</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8693,12 +8693,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8812,32 +8812,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779313</v>
+        <v>125779332</v>
       </c>
       <c r="B83" t="n">
-        <v>98360</v>
+        <v>91250</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611663</v>
+        <v>611525</v>
       </c>
       <c r="R83" t="n">
-        <v>7203664</v>
+        <v>7203705</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125776367</v>
+        <v>125779334</v>
       </c>
       <c r="B4" t="n">
         <v>78972</v>
@@ -913,14 +913,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611653</v>
+        <v>611526</v>
       </c>
       <c r="R4" t="n">
-        <v>7203665</v>
+        <v>7203706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,19 +967,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125779334</v>
+        <v>125776367</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1010,14 +1010,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611526</v>
+        <v>611653</v>
       </c>
       <c r="R5" t="n">
-        <v>7203706</v>
+        <v>7203665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,12 +1064,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -3806,48 +3806,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779848</v>
+        <v>125781666</v>
       </c>
       <c r="B33" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611545</v>
+        <v>611652</v>
       </c>
       <c r="R33" t="n">
-        <v>7203710</v>
+        <v>7203680</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,9 +3874,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,22 +3901,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780606</v>
+        <v>125779884</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,34 +3924,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611311</v>
+        <v>611666</v>
       </c>
       <c r="R34" t="n">
-        <v>7203689</v>
+        <v>7203678</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3968,12 +3978,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,22 +3998,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125781666</v>
+        <v>125779834</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>75067</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,37 +4021,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611652</v>
+        <v>611547</v>
       </c>
       <c r="R35" t="n">
-        <v>7203680</v>
+        <v>7203635</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4068,19 +4078,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,22 +4095,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125779884</v>
+        <v>125780606</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611666</v>
+        <v>611311</v>
       </c>
       <c r="R36" t="n">
-        <v>7203678</v>
+        <v>7203689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,22 +4192,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779834</v>
+        <v>125780608</v>
       </c>
       <c r="B37" t="n">
-        <v>75067</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611547</v>
+        <v>611445</v>
       </c>
       <c r="R37" t="n">
-        <v>7203635</v>
+        <v>7203816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,57 +4289,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125780608</v>
+        <v>125779848</v>
       </c>
       <c r="B38" t="n">
-        <v>80075</v>
+        <v>98360</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611445</v>
+        <v>611545</v>
       </c>
       <c r="R38" t="n">
-        <v>7203816</v>
+        <v>7203710</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,12 +4386,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125779875</v>
+        <v>125781627</v>
       </c>
       <c r="B78" t="n">
-        <v>80111</v>
+        <v>91197</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611687</v>
+        <v>611526</v>
       </c>
       <c r="R78" t="n">
-        <v>7203684</v>
+        <v>7203708</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,9 +8385,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8402,12 +8412,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8511,10 +8521,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779847</v>
+        <v>125779875</v>
       </c>
       <c r="B80" t="n">
-        <v>98360</v>
+        <v>80111</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8522,21 +8532,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8546,10 +8556,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611502</v>
+        <v>611687</v>
       </c>
       <c r="R80" t="n">
-        <v>7203644</v>
+        <v>7203684</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8705,32 +8715,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125781627</v>
+        <v>125779332</v>
       </c>
       <c r="B82" t="n">
-        <v>91197</v>
+        <v>91250</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8740,13 +8750,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611526</v>
+        <v>611525</v>
       </c>
       <c r="R82" t="n">
-        <v>7203708</v>
+        <v>7203705</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8773,19 +8783,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8800,57 +8800,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779332</v>
+        <v>125779847</v>
       </c>
       <c r="B83" t="n">
-        <v>91250</v>
+        <v>98360</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611525</v>
+        <v>611502</v>
       </c>
       <c r="R83" t="n">
-        <v>7203705</v>
+        <v>7203644</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,12 +8897,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125779345</v>
+        <v>125776148</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611661</v>
+        <v>611660</v>
       </c>
       <c r="R2" t="n">
-        <v>7203650</v>
+        <v>7203684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +748,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125776148</v>
+        <v>125776367</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611660</v>
+        <v>611653</v>
       </c>
       <c r="R3" t="n">
-        <v>7203684</v>
+        <v>7203665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -885,7 +872,7 @@
         <v>125779334</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125776367</v>
+        <v>125779345</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611653</v>
+        <v>611661</v>
       </c>
       <c r="R5" t="n">
-        <v>7203665</v>
+        <v>7203650</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1064,12 +1064,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
         <v>125781662</v>
       </c>
       <c r="B6" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125781649</v>
+        <v>125779303</v>
       </c>
       <c r="B7" t="n">
-        <v>91528</v>
+        <v>91234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611536</v>
+        <v>611631</v>
       </c>
       <c r="R7" t="n">
-        <v>7203694</v>
+        <v>7203681</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1251,19 +1251,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,22 +1268,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125779303</v>
+        <v>125781649</v>
       </c>
       <c r="B8" t="n">
-        <v>91232</v>
+        <v>91530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1291,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,13 +1315,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611631</v>
+        <v>611536</v>
       </c>
       <c r="R8" t="n">
-        <v>7203681</v>
+        <v>7203694</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1358,9 +1348,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,12 +1375,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1390,7 +1390,7 @@
         <v>125781636</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>125780621</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,32 +1601,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125779323</v>
+        <v>125781663</v>
       </c>
       <c r="B11" t="n">
-        <v>80103</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611667</v>
+        <v>611570</v>
       </c>
       <c r="R11" t="n">
-        <v>7203673</v>
+        <v>7203700</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,9 +1669,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,22 +1696,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125779769</v>
+        <v>125776139</v>
       </c>
       <c r="B12" t="n">
-        <v>80075</v>
+        <v>80077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1709,34 +1719,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611696</v>
+        <v>611678</v>
       </c>
       <c r="R12" t="n">
-        <v>7203681</v>
+        <v>7203688</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,22 +1793,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779322</v>
+        <v>125779323</v>
       </c>
       <c r="B13" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1830,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611700</v>
+        <v>611667</v>
       </c>
       <c r="R13" t="n">
-        <v>7203701</v>
+        <v>7203673</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,10 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125781637</v>
+        <v>125779769</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,42 +1913,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611631</v>
+        <v>611696</v>
       </c>
       <c r="R14" t="n">
-        <v>7203695</v>
+        <v>7203681</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,19 +1970,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1992,62 +1987,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125780615</v>
+        <v>125779322</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>80104</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611292</v>
+        <v>611700</v>
       </c>
       <c r="R15" t="n">
-        <v>7203703</v>
+        <v>7203701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,12 +2064,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2094,22 +2084,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125781663</v>
+        <v>125781637</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2117,34 +2107,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611570</v>
+        <v>611631</v>
       </c>
       <c r="R16" t="n">
-        <v>7203700</v>
+        <v>7203695</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,7 +2171,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2186,7 +2181,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2213,10 +2208,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125776139</v>
+        <v>125780615</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2224,34 +2219,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611678</v>
+        <v>611292</v>
       </c>
       <c r="R17" t="n">
-        <v>7203688</v>
+        <v>7203703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2313,7 +2313,7 @@
         <v>125779864</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>125779311</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>125776366</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125779317</v>
+        <v>125779336</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,42 +2625,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611723</v>
+        <v>611575</v>
       </c>
       <c r="R21" t="n">
-        <v>7203703</v>
+        <v>7203712</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,11 +2685,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125780622</v>
+        <v>125779338</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611490</v>
+        <v>611631</v>
       </c>
       <c r="R22" t="n">
-        <v>7203838</v>
+        <v>7203681</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,12 +2776,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,22 +2796,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125779336</v>
+        <v>125780607</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>80077</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,21 +2819,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2856,10 +2843,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611575</v>
+        <v>611445</v>
       </c>
       <c r="R23" t="n">
-        <v>7203712</v>
+        <v>7203816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,12 +2873,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2906,44 +2893,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779338</v>
+        <v>125780622</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2953,10 +2940,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611631</v>
+        <v>611490</v>
       </c>
       <c r="R24" t="n">
-        <v>7203681</v>
+        <v>7203838</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2983,12 +2970,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,22 +2990,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125780607</v>
+        <v>125779317</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,34 +3013,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>611445</v>
+        <v>611723</v>
       </c>
       <c r="R25" t="n">
-        <v>7203816</v>
+        <v>7203703</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3080,12 +3075,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,57 +3100,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125779763</v>
+        <v>125776147</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611644</v>
+        <v>611642</v>
       </c>
       <c r="R26" t="n">
-        <v>7203694</v>
+        <v>7203689</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3197,60 +3197,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125779838</v>
+        <v>125781660</v>
       </c>
       <c r="B27" t="n">
-        <v>80104</v>
+        <v>91248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611513</v>
+        <v>611570</v>
       </c>
       <c r="R27" t="n">
-        <v>7203698</v>
+        <v>7203708</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3277,9 +3277,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3294,62 +3304,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125780614</v>
+        <v>125779886</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>91808</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611292</v>
+        <v>611704</v>
       </c>
       <c r="R28" t="n">
-        <v>7203687</v>
+        <v>7203679</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3376,12 +3381,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3396,57 +3401,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125776147</v>
+        <v>125779763</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>80105</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611642</v>
+        <v>611644</v>
       </c>
       <c r="R29" t="n">
-        <v>7203689</v>
+        <v>7203694</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,60 +3498,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125781660</v>
+        <v>125779838</v>
       </c>
       <c r="B30" t="n">
-        <v>91246</v>
+        <v>80105</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611570</v>
+        <v>611513</v>
       </c>
       <c r="R30" t="n">
-        <v>7203708</v>
+        <v>7203698</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3573,19 +3578,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3600,57 +3595,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125779886</v>
+        <v>125780614</v>
       </c>
       <c r="B31" t="n">
-        <v>91806</v>
+        <v>57652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611704</v>
+        <v>611292</v>
       </c>
       <c r="R31" t="n">
-        <v>7203679</v>
+        <v>7203687</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,12 +3697,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3712,7 +3712,7 @@
         <v>125779767</v>
       </c>
       <c r="B32" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125781666</v>
+        <v>125780606</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,13 +3841,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611652</v>
+        <v>611311</v>
       </c>
       <c r="R33" t="n">
-        <v>7203680</v>
+        <v>7203689</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3871,22 +3871,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3906,17 +3896,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125779884</v>
+        <v>125780608</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,34 +3914,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611666</v>
+        <v>611445</v>
       </c>
       <c r="R34" t="n">
-        <v>7203678</v>
+        <v>7203816</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3978,12 +3968,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,44 +3988,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125779834</v>
+        <v>125779848</v>
       </c>
       <c r="B35" t="n">
-        <v>75067</v>
+        <v>98362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611547</v>
+        <v>611545</v>
       </c>
       <c r="R35" t="n">
-        <v>7203635</v>
+        <v>7203710</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4107,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125780606</v>
+        <v>125781666</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4142,13 +4132,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611311</v>
+        <v>611652</v>
       </c>
       <c r="R36" t="n">
-        <v>7203689</v>
+        <v>7203680</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4172,12 +4162,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125780608</v>
+        <v>125779834</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>75068</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611445</v>
+        <v>611547</v>
       </c>
       <c r="R37" t="n">
-        <v>7203816</v>
+        <v>7203635</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,44 +4289,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779848</v>
+        <v>125779884</v>
       </c>
       <c r="B38" t="n">
-        <v>98360</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611545</v>
+        <v>611666</v>
       </c>
       <c r="R38" t="n">
-        <v>7203710</v>
+        <v>7203678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779773</v>
+        <v>125779853</v>
       </c>
       <c r="B39" t="n">
-        <v>80111</v>
+        <v>98362</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611662</v>
+        <v>611691</v>
       </c>
       <c r="R39" t="n">
-        <v>7203612</v>
+        <v>7203679</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,57 +4483,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779844</v>
+        <v>125779337</v>
       </c>
       <c r="B40" t="n">
-        <v>80104</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611644</v>
+        <v>611615</v>
       </c>
       <c r="R40" t="n">
-        <v>7203690</v>
+        <v>7203678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,57 +4580,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779337</v>
+        <v>125779773</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>80112</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611615</v>
+        <v>611662</v>
       </c>
       <c r="R41" t="n">
-        <v>7203678</v>
+        <v>7203612</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,65 +4677,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779319</v>
+        <v>125779844</v>
       </c>
       <c r="B42" t="n">
-        <v>57651</v>
+        <v>80105</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611663</v>
+        <v>611644</v>
       </c>
       <c r="R42" t="n">
-        <v>7203613</v>
+        <v>7203690</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4770,11 +4762,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4787,22 +4774,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779316</v>
+        <v>125779319</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4842,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611507</v>
+        <v>611663</v>
       </c>
       <c r="R43" t="n">
-        <v>7203685</v>
+        <v>7203613</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4882,7 +4869,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4909,10 +4896,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779318</v>
+        <v>125779316</v>
       </c>
       <c r="B44" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4952,10 +4939,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611725</v>
+        <v>611507</v>
       </c>
       <c r="R44" t="n">
-        <v>7203707</v>
+        <v>7203685</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5019,45 +5006,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779853</v>
+        <v>125779318</v>
       </c>
       <c r="B45" t="n">
-        <v>98360</v>
+        <v>57652</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611691</v>
+        <v>611725</v>
       </c>
       <c r="R45" t="n">
-        <v>7203679</v>
+        <v>7203707</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5092,6 +5087,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5104,60 +5104,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125776134</v>
+        <v>125781648</v>
       </c>
       <c r="B46" t="n">
-        <v>80104</v>
+        <v>80077</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>611647</v>
+        <v>611683</v>
       </c>
       <c r="R46" t="n">
-        <v>7203694</v>
+        <v>7203710</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5184,9 +5184,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5201,65 +5211,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125779346</v>
+        <v>125776134</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>80105</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>611666</v>
+        <v>611647</v>
       </c>
       <c r="R47" t="n">
-        <v>7203652</v>
+        <v>7203694</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5294,11 +5296,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5311,22 +5308,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125781648</v>
+        <v>125779346</v>
       </c>
       <c r="B48" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,37 +5331,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>611683</v>
+        <v>611666</v>
       </c>
       <c r="R48" t="n">
-        <v>7203710</v>
+        <v>7203652</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5391,19 +5396,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5418,22 +5418,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125779309</v>
+        <v>125781628</v>
       </c>
       <c r="B49" t="n">
-        <v>80104</v>
+        <v>91199</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,21 +5441,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611679</v>
+        <v>611568</v>
       </c>
       <c r="R49" t="n">
-        <v>7203682</v>
+        <v>7203718</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5498,9 +5498,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5515,57 +5525,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779876</v>
+        <v>125779315</v>
       </c>
       <c r="B50" t="n">
-        <v>80111</v>
+        <v>80077</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611661</v>
+        <v>611617</v>
       </c>
       <c r="R50" t="n">
-        <v>7203604</v>
+        <v>7203677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5612,22 +5622,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779863</v>
+        <v>125779343</v>
       </c>
       <c r="B51" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5635,42 +5645,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611623</v>
+        <v>611670</v>
       </c>
       <c r="R51" t="n">
-        <v>7203692</v>
+        <v>7203656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5705,11 +5707,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5722,22 +5719,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779315</v>
+        <v>125779863</v>
       </c>
       <c r="B52" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5745,34 +5742,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611617</v>
+        <v>611623</v>
       </c>
       <c r="R52" t="n">
-        <v>7203677</v>
+        <v>7203692</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5807,6 +5812,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5819,22 +5829,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125781628</v>
+        <v>125779309</v>
       </c>
       <c r="B53" t="n">
-        <v>91197</v>
+        <v>80105</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5842,21 +5852,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5866,13 +5876,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611568</v>
+        <v>611679</v>
       </c>
       <c r="R53" t="n">
-        <v>7203718</v>
+        <v>7203682</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5899,19 +5909,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5926,57 +5926,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779343</v>
+        <v>125779876</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>80112</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611670</v>
+        <v>611661</v>
       </c>
       <c r="R54" t="n">
-        <v>7203656</v>
+        <v>7203604</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6023,57 +6023,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779842</v>
+        <v>125779320</v>
       </c>
       <c r="B55" t="n">
-        <v>80104</v>
+        <v>91603</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611593</v>
+        <v>611543</v>
       </c>
       <c r="R55" t="n">
-        <v>7203711</v>
+        <v>7203697</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6120,22 +6120,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125779867</v>
+        <v>125781664</v>
       </c>
       <c r="B56" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,37 +6143,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611694</v>
+        <v>611539</v>
       </c>
       <c r="R56" t="n">
-        <v>7203678</v>
+        <v>7203643</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6200,9 +6200,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6217,22 +6227,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779869</v>
+        <v>125779344</v>
       </c>
       <c r="B57" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6240,34 +6250,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611687</v>
+        <v>611653</v>
       </c>
       <c r="R57" t="n">
-        <v>7203684</v>
+        <v>7203626</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6314,22 +6324,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125780620</v>
+        <v>125779881</v>
       </c>
       <c r="B58" t="n">
-        <v>57651</v>
+        <v>91252</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6337,39 +6347,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611381</v>
+        <v>611650</v>
       </c>
       <c r="R58" t="n">
-        <v>7203809</v>
+        <v>7203647</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6396,12 +6401,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6416,57 +6421,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779320</v>
+        <v>125779842</v>
       </c>
       <c r="B59" t="n">
-        <v>91601</v>
+        <v>80105</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1506</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611543</v>
+        <v>611593</v>
       </c>
       <c r="R59" t="n">
-        <v>7203697</v>
+        <v>7203711</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6513,22 +6518,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125781664</v>
+        <v>125779867</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6536,37 +6541,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611539</v>
+        <v>611694</v>
       </c>
       <c r="R60" t="n">
-        <v>7203643</v>
+        <v>7203678</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6593,19 +6598,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6620,22 +6615,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779344</v>
+        <v>125779869</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6643,34 +6638,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611653</v>
+        <v>611687</v>
       </c>
       <c r="R61" t="n">
-        <v>7203626</v>
+        <v>7203684</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6717,22 +6712,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779881</v>
+        <v>125780620</v>
       </c>
       <c r="B62" t="n">
-        <v>91250</v>
+        <v>57652</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6740,34 +6735,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611650</v>
+        <v>611381</v>
       </c>
       <c r="R62" t="n">
-        <v>7203647</v>
+        <v>7203809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,22 +6814,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779850</v>
+        <v>125776365</v>
       </c>
       <c r="B63" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611637</v>
+        <v>611567</v>
       </c>
       <c r="R63" t="n">
-        <v>7203685</v>
+        <v>7203714</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,22 +6911,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125776365</v>
+        <v>125779850</v>
       </c>
       <c r="B64" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611567</v>
+        <v>611637</v>
       </c>
       <c r="R64" t="n">
-        <v>7203714</v>
+        <v>7203685</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7008,12 +7008,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7023,7 +7023,7 @@
         <v>125779308</v>
       </c>
       <c r="B65" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>125781635</v>
       </c>
       <c r="B66" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>125780618</v>
       </c>
       <c r="B67" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>125781642</v>
       </c>
       <c r="B68" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>125779339</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7540,45 +7540,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125776142</v>
+        <v>125779859</v>
       </c>
       <c r="B70" t="n">
-        <v>91806</v>
+        <v>80077</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611684</v>
+        <v>611687</v>
       </c>
       <c r="R70" t="n">
-        <v>7203683</v>
+        <v>7203684</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,28 +7619,29 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779859</v>
+        <v>125779333</v>
       </c>
       <c r="B71" t="n">
-        <v>80076</v>
+        <v>91252</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7648,34 +7649,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611687</v>
+        <v>611659</v>
       </c>
       <c r="R71" t="n">
-        <v>7203684</v>
+        <v>7203648</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7716,64 +7717,63 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125779333</v>
+        <v>125776142</v>
       </c>
       <c r="B72" t="n">
-        <v>91250</v>
+        <v>91808</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611659</v>
+        <v>611684</v>
       </c>
       <c r="R72" t="n">
-        <v>7203648</v>
+        <v>7203683</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7820,22 +7820,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779771</v>
+        <v>125779880</v>
       </c>
       <c r="B73" t="n">
-        <v>80075</v>
+        <v>91252</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7843,21 +7843,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7867,10 +7867,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611686</v>
+        <v>611743</v>
       </c>
       <c r="R73" t="n">
-        <v>7203685</v>
+        <v>7203706</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7917,22 +7917,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779880</v>
+        <v>125779340</v>
       </c>
       <c r="B74" t="n">
-        <v>91250</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,34 +7940,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611743</v>
+        <v>611680</v>
       </c>
       <c r="R74" t="n">
-        <v>7203706</v>
+        <v>7203713</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,44 +8014,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779340</v>
+        <v>125779312</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>98362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611680</v>
+        <v>611683</v>
       </c>
       <c r="R75" t="n">
-        <v>7203713</v>
+        <v>7203677</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779312</v>
+        <v>125779310</v>
       </c>
       <c r="B76" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611683</v>
+        <v>611700</v>
       </c>
       <c r="R76" t="n">
-        <v>7203677</v>
+        <v>7203703</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779310</v>
+        <v>125779771</v>
       </c>
       <c r="B77" t="n">
-        <v>98360</v>
+        <v>80076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611700</v>
+        <v>611686</v>
       </c>
       <c r="R77" t="n">
-        <v>7203703</v>
+        <v>7203685</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8305,12 +8305,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8320,7 +8320,7 @@
         <v>125781627</v>
       </c>
       <c r="B78" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8424,32 +8424,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779313</v>
+        <v>125779332</v>
       </c>
       <c r="B79" t="n">
-        <v>98360</v>
+        <v>91252</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611663</v>
+        <v>611525</v>
       </c>
       <c r="R79" t="n">
-        <v>7203664</v>
+        <v>7203705</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8524,7 +8524,7 @@
         <v>125779875</v>
       </c>
       <c r="B80" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>125779307</v>
       </c>
       <c r="B81" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8715,32 +8715,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779332</v>
+        <v>125779313</v>
       </c>
       <c r="B82" t="n">
-        <v>91250</v>
+        <v>98362</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611525</v>
+        <v>611663</v>
       </c>
       <c r="R82" t="n">
-        <v>7203705</v>
+        <v>7203664</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8815,7 +8815,7 @@
         <v>125779847</v>
       </c>
       <c r="B83" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8909,48 +8909,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125779873</v>
+        <v>125781650</v>
       </c>
       <c r="B84" t="n">
-        <v>80111</v>
+        <v>91603</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611693</v>
+        <v>611521</v>
       </c>
       <c r="R84" t="n">
-        <v>7203707</v>
+        <v>7203626</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,9 +8977,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8994,65 +9004,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125781638</v>
+        <v>125776368</v>
       </c>
       <c r="B85" t="n">
-        <v>57651</v>
+        <v>91808</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611645</v>
+        <v>611705</v>
       </c>
       <c r="R85" t="n">
-        <v>7203676</v>
+        <v>7203679</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9079,19 +9084,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9106,65 +9101,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125779347</v>
+        <v>125779873</v>
       </c>
       <c r="B86" t="n">
-        <v>57651</v>
+        <v>80112</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611688</v>
+        <v>611693</v>
       </c>
       <c r="R86" t="n">
-        <v>7203713</v>
+        <v>7203707</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9199,11 +9186,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9216,57 +9198,62 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125781650</v>
+        <v>125781638</v>
       </c>
       <c r="B87" t="n">
-        <v>91601</v>
+        <v>57652</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611521</v>
+        <v>611645</v>
       </c>
       <c r="R87" t="n">
-        <v>7203626</v>
+        <v>7203676</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9298,7 +9285,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9308,7 +9295,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9335,45 +9322,53 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125776368</v>
+        <v>125779347</v>
       </c>
       <c r="B88" t="n">
-        <v>91806</v>
+        <v>57652</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611705</v>
+        <v>611688</v>
       </c>
       <c r="R88" t="n">
-        <v>7203679</v>
+        <v>7203713</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9408,6 +9403,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,12 +9420,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9435,7 +9435,7 @@
         <v>125779324</v>
       </c>
       <c r="B89" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>125779874</v>
       </c>
       <c r="B90" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779852</v>
+        <v>125779846</v>
       </c>
       <c r="B91" t="n">
-        <v>98360</v>
+        <v>80105</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611711</v>
+        <v>611717</v>
       </c>
       <c r="R91" t="n">
-        <v>7203685</v>
+        <v>7203689</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9723,10 +9723,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125779846</v>
+        <v>125779764</v>
       </c>
       <c r="B92" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611717</v>
+        <v>611648</v>
       </c>
       <c r="R92" t="n">
-        <v>7203689</v>
+        <v>7203687</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9808,22 +9808,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125779764</v>
+        <v>125776127</v>
       </c>
       <c r="B93" t="n">
-        <v>80104</v>
+        <v>80112</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611648</v>
+        <v>611681</v>
       </c>
       <c r="R93" t="n">
-        <v>7203687</v>
+        <v>7203685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,22 +9905,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125776127</v>
+        <v>125779852</v>
       </c>
       <c r="B94" t="n">
-        <v>80111</v>
+        <v>98362</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9928,31 +9928,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611681</v>
+        <v>611711</v>
       </c>
       <c r="R94" t="n">
         <v>7203685</v>
@@ -10002,12 +10002,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10017,7 +10017,7 @@
         <v>125779302</v>
       </c>
       <c r="B95" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10114,7 +10114,7 @@
         <v>125779885</v>
       </c>
       <c r="B96" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>125779349</v>
       </c>
       <c r="B97" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>125779314</v>
       </c>
       <c r="B98" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10415,45 +10415,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779851</v>
+        <v>125779299</v>
       </c>
       <c r="B99" t="n">
-        <v>98360</v>
+        <v>75068</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611690</v>
+        <v>611561</v>
       </c>
       <c r="R99" t="n">
-        <v>7203710</v>
+        <v>7203692</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10500,22 +10500,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779299</v>
+        <v>125779329</v>
       </c>
       <c r="B100" t="n">
-        <v>75067</v>
+        <v>80076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10523,21 +10523,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611561</v>
+        <v>611623</v>
       </c>
       <c r="R100" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10609,45 +10609,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779329</v>
+        <v>125779772</v>
       </c>
       <c r="B101" t="n">
-        <v>80075</v>
+        <v>80112</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611623</v>
+        <v>611680</v>
       </c>
       <c r="R101" t="n">
-        <v>7203677</v>
+        <v>7203679</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,22 +10694,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779772</v>
+        <v>125779851</v>
       </c>
       <c r="B102" t="n">
-        <v>80111</v>
+        <v>98362</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10717,21 +10717,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611680</v>
+        <v>611690</v>
       </c>
       <c r="R102" t="n">
-        <v>7203679</v>
+        <v>7203710</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>125803940</v>
       </c>
       <c r="B104" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>125803917</v>
       </c>
       <c r="B105" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11115,41 +11115,42 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125803950</v>
+        <v>125803668</v>
       </c>
       <c r="B106" t="n">
-        <v>91601</v>
+        <v>98362</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1506</v>
+        <v>221952</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11157,10 +11158,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>611534</v>
+        <v>611679</v>
       </c>
       <c r="R106" t="n">
-        <v>7203710</v>
+        <v>7203707</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11220,42 +11221,41 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125803668</v>
+        <v>125803950</v>
       </c>
       <c r="B107" t="n">
-        <v>98360</v>
+        <v>91603</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221952</v>
+        <v>1506</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>611679</v>
+        <v>611534</v>
       </c>
       <c r="R107" t="n">
-        <v>7203707</v>
+        <v>7203710</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>125803829</v>
       </c>
       <c r="B109" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>125804619</v>
       </c>
       <c r="B110" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>125803771</v>
       </c>
       <c r="B111" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>125779762</v>
       </c>
       <c r="B113" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -2310,53 +2310,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779864</v>
+        <v>125779311</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>98362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611742</v>
+        <v>611690</v>
       </c>
       <c r="R18" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,11 +2383,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2408,19 +2395,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125779311</v>
+        <v>125776366</v>
       </c>
       <c r="B19" t="n">
         <v>98362</v>
@@ -2451,11 +2438,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611690</v>
+        <v>611679</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2505,57 +2492,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125776366</v>
+        <v>125779864</v>
       </c>
       <c r="B20" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611679</v>
+        <v>611742</v>
       </c>
       <c r="R20" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,6 +2585,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,12 +2602,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2905,45 +2905,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125780622</v>
+        <v>125779317</v>
       </c>
       <c r="B24" t="n">
-        <v>98341</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611490</v>
+        <v>611723</v>
       </c>
       <c r="R24" t="n">
-        <v>7203838</v>
+        <v>7203703</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,12 +2978,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2990,65 +3003,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125779317</v>
+        <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>98341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>611723</v>
+        <v>611490</v>
       </c>
       <c r="R25" t="n">
-        <v>7203703</v>
+        <v>7203838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3075,17 +3080,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,12 +3100,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125780606</v>
+        <v>125781666</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,13 +3841,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611311</v>
+        <v>611652</v>
       </c>
       <c r="R33" t="n">
-        <v>7203689</v>
+        <v>7203680</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3871,12 +3871,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3896,17 +3906,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780608</v>
+        <v>125779834</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>75068</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,34 +3924,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611445</v>
+        <v>611547</v>
       </c>
       <c r="R34" t="n">
-        <v>7203816</v>
+        <v>7203635</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3968,12 +3978,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,44 +3998,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125779848</v>
+        <v>125779884</v>
       </c>
       <c r="B35" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611545</v>
+        <v>611666</v>
       </c>
       <c r="R35" t="n">
-        <v>7203710</v>
+        <v>7203678</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4097,10 +4107,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125781666</v>
+        <v>125780606</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4118,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,13 +4142,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611652</v>
+        <v>611311</v>
       </c>
       <c r="R36" t="n">
-        <v>7203680</v>
+        <v>7203689</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4162,22 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779834</v>
+        <v>125780608</v>
       </c>
       <c r="B37" t="n">
-        <v>75068</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611547</v>
+        <v>611445</v>
       </c>
       <c r="R37" t="n">
-        <v>7203635</v>
+        <v>7203816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,44 +4289,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779884</v>
+        <v>125779848</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>98362</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611666</v>
+        <v>611545</v>
       </c>
       <c r="R38" t="n">
-        <v>7203678</v>
+        <v>7203710</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4398,45 +4398,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779853</v>
+        <v>125779337</v>
       </c>
       <c r="B39" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611691</v>
+        <v>611615</v>
       </c>
       <c r="R39" t="n">
-        <v>7203679</v>
+        <v>7203678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,57 +4483,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779337</v>
+        <v>125779773</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>80112</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611615</v>
+        <v>611662</v>
       </c>
       <c r="R40" t="n">
-        <v>7203678</v>
+        <v>7203612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,22 +4580,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779773</v>
+        <v>125779844</v>
       </c>
       <c r="B41" t="n">
-        <v>80112</v>
+        <v>80105</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611662</v>
+        <v>611644</v>
       </c>
       <c r="R41" t="n">
-        <v>7203612</v>
+        <v>7203690</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,57 +4677,65 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779844</v>
+        <v>125779319</v>
       </c>
       <c r="B42" t="n">
-        <v>80105</v>
+        <v>57652</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611644</v>
+        <v>611663</v>
       </c>
       <c r="R42" t="n">
-        <v>7203690</v>
+        <v>7203613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4762,6 +4770,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4774,19 +4787,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779319</v>
+        <v>125779316</v>
       </c>
       <c r="B43" t="n">
         <v>57652</v>
@@ -4829,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611663</v>
+        <v>611507</v>
       </c>
       <c r="R43" t="n">
-        <v>7203613</v>
+        <v>7203685</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4869,7 +4882,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4896,7 +4909,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779316</v>
+        <v>125779318</v>
       </c>
       <c r="B44" t="n">
         <v>57652</v>
@@ -4939,10 +4952,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611507</v>
+        <v>611725</v>
       </c>
       <c r="R44" t="n">
-        <v>7203685</v>
+        <v>7203707</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,53 +5019,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779318</v>
+        <v>125779853</v>
       </c>
       <c r="B45" t="n">
-        <v>57652</v>
+        <v>98362</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611725</v>
+        <v>611691</v>
       </c>
       <c r="R45" t="n">
-        <v>7203707</v>
+        <v>7203679</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5087,11 +5092,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5104,12 +5104,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -7020,48 +7020,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125779308</v>
+        <v>125781635</v>
       </c>
       <c r="B65" t="n">
-        <v>80105</v>
+        <v>57652</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611684</v>
+        <v>611535</v>
       </c>
       <c r="R65" t="n">
-        <v>7203690</v>
+        <v>7203644</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7088,9 +7093,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7105,19 +7120,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125781635</v>
+        <v>125780618</v>
       </c>
       <c r="B66" t="n">
         <v>57652</v>
@@ -7157,13 +7172,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611535</v>
+        <v>611378</v>
       </c>
       <c r="R66" t="n">
-        <v>7203644</v>
+        <v>7203714</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7187,22 +7202,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7222,45 +7227,45 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125780618</v>
+        <v>125781642</v>
       </c>
       <c r="B67" t="n">
-        <v>57652</v>
+        <v>56844</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7269,13 +7274,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611378</v>
+        <v>611705</v>
       </c>
       <c r="R67" t="n">
-        <v>7203714</v>
+        <v>7203676</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7299,12 +7304,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7324,17 +7339,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125781642</v>
+        <v>125779308</v>
       </c>
       <c r="B68" t="n">
-        <v>56844</v>
+        <v>80105</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7342,42 +7357,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611705</v>
+        <v>611684</v>
       </c>
       <c r="R68" t="n">
-        <v>7203676</v>
+        <v>7203690</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7404,19 +7414,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7431,12 +7431,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779846</v>
+        <v>125779852</v>
       </c>
       <c r="B91" t="n">
-        <v>80105</v>
+        <v>98362</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611717</v>
+        <v>611711</v>
       </c>
       <c r="R91" t="n">
-        <v>7203689</v>
+        <v>7203685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9723,7 +9723,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125779764</v>
+        <v>125779846</v>
       </c>
       <c r="B92" t="n">
         <v>80105</v>
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611648</v>
+        <v>611717</v>
       </c>
       <c r="R92" t="n">
-        <v>7203687</v>
+        <v>7203689</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9808,22 +9808,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125776127</v>
+        <v>125779764</v>
       </c>
       <c r="B93" t="n">
-        <v>80112</v>
+        <v>80105</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611681</v>
+        <v>611648</v>
       </c>
       <c r="R93" t="n">
-        <v>7203685</v>
+        <v>7203687</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,22 +9905,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125779852</v>
+        <v>125776127</v>
       </c>
       <c r="B94" t="n">
-        <v>98362</v>
+        <v>80112</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9928,31 +9928,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611711</v>
+        <v>611681</v>
       </c>
       <c r="R94" t="n">
         <v>7203685</v>
@@ -10002,44 +10002,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779302</v>
+        <v>125779314</v>
       </c>
       <c r="B95" t="n">
-        <v>91234</v>
+        <v>98362</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10049,10 +10049,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611618</v>
+        <v>611663</v>
       </c>
       <c r="R95" t="n">
-        <v>7203674</v>
+        <v>7203673</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10111,10 +10111,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779885</v>
+        <v>125779302</v>
       </c>
       <c r="B96" t="n">
-        <v>78973</v>
+        <v>91234</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10122,34 +10122,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611661</v>
+        <v>611618</v>
       </c>
       <c r="R96" t="n">
-        <v>7203604</v>
+        <v>7203674</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,22 +10196,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779349</v>
+        <v>125779885</v>
       </c>
       <c r="B97" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10219,42 +10219,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611652</v>
+        <v>611661</v>
       </c>
       <c r="R97" t="n">
-        <v>7203627</v>
+        <v>7203604</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10289,11 +10281,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10306,57 +10293,65 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779314</v>
+        <v>125779349</v>
       </c>
       <c r="B98" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611663</v>
+        <v>611652</v>
       </c>
       <c r="R98" t="n">
-        <v>7203673</v>
+        <v>7203627</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10389,6 +10384,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11115,42 +11115,41 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125803668</v>
+        <v>125803950</v>
       </c>
       <c r="B106" t="n">
-        <v>98362</v>
+        <v>91603</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221952</v>
+        <v>1506</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11158,10 +11157,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>611679</v>
+        <v>611534</v>
       </c>
       <c r="R106" t="n">
-        <v>7203707</v>
+        <v>7203710</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11221,41 +11220,42 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125803950</v>
+        <v>125803668</v>
       </c>
       <c r="B107" t="n">
-        <v>91603</v>
+        <v>98362</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1506</v>
+        <v>221952</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>611534</v>
+        <v>611679</v>
       </c>
       <c r="R107" t="n">
-        <v>7203710</v>
+        <v>7203707</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1079,7 +1079,7 @@
         <v>125781662</v>
       </c>
       <c r="B6" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,17 +1176,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125779303</v>
+        <v>125781649</v>
       </c>
       <c r="B7" t="n">
-        <v>91234</v>
+        <v>91532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611631</v>
+        <v>611536</v>
       </c>
       <c r="R7" t="n">
-        <v>7203681</v>
+        <v>7203694</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1251,9 +1251,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,22 +1278,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125781649</v>
+        <v>125779303</v>
       </c>
       <c r="B8" t="n">
-        <v>91530</v>
+        <v>91236</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,21 +1301,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1315,13 +1325,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611536</v>
+        <v>611631</v>
       </c>
       <c r="R8" t="n">
-        <v>7203694</v>
+        <v>7203681</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1348,19 +1358,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,12 +1375,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125781663</v>
+        <v>125781637</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1612,34 +1612,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611570</v>
+        <v>611631</v>
       </c>
       <c r="R11" t="n">
-        <v>7203700</v>
+        <v>7203695</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1671,7 +1676,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1681,7 +1686,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1701,7 +1706,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1805,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779323</v>
+        <v>125779322</v>
       </c>
       <c r="B13" t="n">
         <v>80104</v>
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611667</v>
+        <v>611700</v>
       </c>
       <c r="R13" t="n">
-        <v>7203673</v>
+        <v>7203701</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125779769</v>
+        <v>125781663</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1913,37 +1918,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611696</v>
+        <v>611570</v>
       </c>
       <c r="R14" t="n">
-        <v>7203681</v>
+        <v>7203700</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,9 +1975,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1987,57 +2002,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125779322</v>
+        <v>125779769</v>
       </c>
       <c r="B15" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611700</v>
+        <v>611696</v>
       </c>
       <c r="R15" t="n">
-        <v>7203701</v>
+        <v>7203681</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2084,65 +2099,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125781637</v>
+        <v>125779323</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>80104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611631</v>
+        <v>611667</v>
       </c>
       <c r="R16" t="n">
-        <v>7203695</v>
+        <v>7203673</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2169,19 +2179,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,12 +2196,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2310,45 +2310,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779311</v>
+        <v>125779864</v>
       </c>
       <c r="B18" t="n">
-        <v>98362</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611690</v>
+        <v>611742</v>
       </c>
       <c r="R18" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,6 +2391,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2395,22 +2408,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125776366</v>
+        <v>125779311</v>
       </c>
       <c r="B19" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,11 +2451,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611679</v>
+        <v>611690</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2492,65 +2505,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125779864</v>
+        <v>125776366</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611742</v>
+        <v>611679</v>
       </c>
       <c r="R20" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2585,11 +2590,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,22 +2602,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125779336</v>
+        <v>125779317</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,34 +2625,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611575</v>
+        <v>611723</v>
       </c>
       <c r="R21" t="n">
-        <v>7203712</v>
+        <v>7203703</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,6 +2693,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2711,7 +2724,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125779338</v>
+        <v>125779336</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2746,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611631</v>
+        <v>611575</v>
       </c>
       <c r="R22" t="n">
-        <v>7203681</v>
+        <v>7203712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,10 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779317</v>
+        <v>125779338</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,42 +2929,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611723</v>
+        <v>611631</v>
       </c>
       <c r="R24" t="n">
-        <v>7203703</v>
+        <v>7203681</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2984,11 +2989,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3018,7 +3018,7 @@
         <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>125781660</v>
       </c>
       <c r="B27" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
         <v>125779886</v>
       </c>
       <c r="B28" t="n">
-        <v>91808</v>
+        <v>91810</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,45 +3413,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125779763</v>
+        <v>125780614</v>
       </c>
       <c r="B29" t="n">
-        <v>80105</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611644</v>
+        <v>611292</v>
       </c>
       <c r="R29" t="n">
-        <v>7203694</v>
+        <v>7203687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3478,12 +3483,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3498,22 +3503,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125779838</v>
+        <v>125779767</v>
       </c>
       <c r="B30" t="n">
-        <v>80105</v>
+        <v>98364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3521,21 +3526,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611513</v>
+        <v>611673</v>
       </c>
       <c r="R30" t="n">
-        <v>7203698</v>
+        <v>7203670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3595,62 +3600,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125780614</v>
+        <v>125779763</v>
       </c>
       <c r="B31" t="n">
-        <v>57652</v>
+        <v>80105</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611292</v>
+        <v>611644</v>
       </c>
       <c r="R31" t="n">
-        <v>7203687</v>
+        <v>7203694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,22 +3697,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125779767</v>
+        <v>125779838</v>
       </c>
       <c r="B32" t="n">
-        <v>98362</v>
+        <v>80105</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611673</v>
+        <v>611513</v>
       </c>
       <c r="R32" t="n">
-        <v>7203670</v>
+        <v>7203698</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,60 +3794,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125781666</v>
+        <v>125779848</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611652</v>
+        <v>611545</v>
       </c>
       <c r="R33" t="n">
-        <v>7203680</v>
+        <v>7203710</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,19 +3874,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125779834</v>
+        <v>125781666</v>
       </c>
       <c r="B34" t="n">
-        <v>75068</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,37 +3914,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611547</v>
+        <v>611652</v>
       </c>
       <c r="R34" t="n">
-        <v>7203635</v>
+        <v>7203680</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3981,9 +3971,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,22 +3998,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125779884</v>
+        <v>125780608</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,34 +4021,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611666</v>
+        <v>611445</v>
       </c>
       <c r="R35" t="n">
-        <v>7203678</v>
+        <v>7203816</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4075,12 +4075,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,22 +4095,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125780606</v>
+        <v>125779834</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>75068</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611311</v>
+        <v>611547</v>
       </c>
       <c r="R36" t="n">
-        <v>7203689</v>
+        <v>7203635</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,22 +4192,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125780608</v>
+        <v>125779884</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611445</v>
+        <v>611666</v>
       </c>
       <c r="R37" t="n">
-        <v>7203816</v>
+        <v>7203678</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,57 +4289,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779848</v>
+        <v>125780606</v>
       </c>
       <c r="B38" t="n">
-        <v>98362</v>
+        <v>80076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611545</v>
+        <v>611311</v>
       </c>
       <c r="R38" t="n">
-        <v>7203710</v>
+        <v>7203689</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,57 +4386,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779337</v>
+        <v>125779844</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611615</v>
+        <v>611644</v>
       </c>
       <c r="R39" t="n">
-        <v>7203678</v>
+        <v>7203690</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,12 +4483,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4592,45 +4592,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779844</v>
+        <v>125779337</v>
       </c>
       <c r="B41" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611644</v>
+        <v>611615</v>
       </c>
       <c r="R41" t="n">
-        <v>7203690</v>
+        <v>7203678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4677,12 +4677,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5022,7 +5022,7 @@
         <v>125779853</v>
       </c>
       <c r="B45" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5116,48 +5116,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125781648</v>
+        <v>125776134</v>
       </c>
       <c r="B46" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>611683</v>
+        <v>611647</v>
       </c>
       <c r="R46" t="n">
-        <v>7203710</v>
+        <v>7203694</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5184,19 +5184,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5211,57 +5201,65 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125776134</v>
+        <v>125779346</v>
       </c>
       <c r="B47" t="n">
-        <v>80105</v>
+        <v>57652</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>611647</v>
+        <v>611666</v>
       </c>
       <c r="R47" t="n">
-        <v>7203694</v>
+        <v>7203652</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5296,6 +5294,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5308,22 +5311,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125779346</v>
+        <v>125781648</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5331,45 +5334,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>611666</v>
+        <v>611683</v>
       </c>
       <c r="R48" t="n">
-        <v>7203652</v>
+        <v>7203710</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5396,14 +5391,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5433,7 +5433,7 @@
         <v>125781628</v>
       </c>
       <c r="B49" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5634,32 +5634,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779343</v>
+        <v>125779309</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611670</v>
+        <v>611679</v>
       </c>
       <c r="R51" t="n">
-        <v>7203656</v>
+        <v>7203682</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5731,53 +5731,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779863</v>
+        <v>125779876</v>
       </c>
       <c r="B52" t="n">
-        <v>57652</v>
+        <v>80112</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611623</v>
+        <v>611661</v>
       </c>
       <c r="R52" t="n">
-        <v>7203692</v>
+        <v>7203604</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5810,11 +5802,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5841,32 +5828,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779309</v>
+        <v>125779343</v>
       </c>
       <c r="B53" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5876,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611679</v>
+        <v>611670</v>
       </c>
       <c r="R53" t="n">
-        <v>7203682</v>
+        <v>7203656</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5938,45 +5925,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779876</v>
+        <v>125779863</v>
       </c>
       <c r="B54" t="n">
-        <v>80112</v>
+        <v>57652</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611661</v>
+        <v>611623</v>
       </c>
       <c r="R54" t="n">
-        <v>7203604</v>
+        <v>7203692</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6009,6 +6004,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6038,7 +6038,7 @@
         <v>125779320</v>
       </c>
       <c r="B55" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6132,10 +6132,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125781664</v>
+        <v>125779881</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>91254</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,37 +6143,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611539</v>
+        <v>611650</v>
       </c>
       <c r="R56" t="n">
-        <v>7203643</v>
+        <v>7203647</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6200,19 +6200,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,19 +6217,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779344</v>
+        <v>125781664</v>
       </c>
       <c r="B57" t="n">
         <v>78973</v>
@@ -6274,13 +6264,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611653</v>
+        <v>611539</v>
       </c>
       <c r="R57" t="n">
-        <v>7203626</v>
+        <v>7203643</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6307,9 +6297,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6324,22 +6324,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779881</v>
+        <v>125779869</v>
       </c>
       <c r="B58" t="n">
-        <v>91252</v>
+        <v>80076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6347,21 +6347,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611650</v>
+        <v>611687</v>
       </c>
       <c r="R58" t="n">
-        <v>7203647</v>
+        <v>7203684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6433,32 +6433,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779842</v>
+        <v>125779867</v>
       </c>
       <c r="B59" t="n">
-        <v>80105</v>
+        <v>80076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611593</v>
+        <v>611694</v>
       </c>
       <c r="R59" t="n">
-        <v>7203711</v>
+        <v>7203678</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779867</v>
+        <v>125779344</v>
       </c>
       <c r="B60" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6541,34 +6541,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611694</v>
+        <v>611653</v>
       </c>
       <c r="R60" t="n">
-        <v>7203678</v>
+        <v>7203626</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6615,44 +6615,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779869</v>
+        <v>125779842</v>
       </c>
       <c r="B61" t="n">
-        <v>80076</v>
+        <v>80105</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611687</v>
+        <v>611593</v>
       </c>
       <c r="R61" t="n">
-        <v>7203684</v>
+        <v>7203711</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125776365</v>
+        <v>125779850</v>
       </c>
       <c r="B63" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611567</v>
+        <v>611637</v>
       </c>
       <c r="R63" t="n">
-        <v>7203714</v>
+        <v>7203685</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,22 +6911,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125779850</v>
+        <v>125776365</v>
       </c>
       <c r="B64" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611637</v>
+        <v>611567</v>
       </c>
       <c r="R64" t="n">
-        <v>7203685</v>
+        <v>7203714</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7008,65 +7008,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125781635</v>
+        <v>125779308</v>
       </c>
       <c r="B65" t="n">
-        <v>57652</v>
+        <v>80105</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611535</v>
+        <v>611684</v>
       </c>
       <c r="R65" t="n">
-        <v>7203644</v>
+        <v>7203690</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7093,19 +7088,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7120,19 +7105,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125780618</v>
+        <v>125781635</v>
       </c>
       <c r="B66" t="n">
         <v>57652</v>
@@ -7172,13 +7157,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611378</v>
+        <v>611535</v>
       </c>
       <c r="R66" t="n">
-        <v>7203714</v>
+        <v>7203644</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7202,12 +7187,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7227,45 +7222,45 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125781642</v>
+        <v>125780618</v>
       </c>
       <c r="B67" t="n">
-        <v>56844</v>
+        <v>57652</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7274,13 +7269,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611705</v>
+        <v>611378</v>
       </c>
       <c r="R67" t="n">
-        <v>7203676</v>
+        <v>7203714</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7304,22 +7299,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7339,17 +7324,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125779308</v>
+        <v>125781642</v>
       </c>
       <c r="B68" t="n">
-        <v>80105</v>
+        <v>56844</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7357,37 +7342,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611684</v>
+        <v>611705</v>
       </c>
       <c r="R68" t="n">
-        <v>7203690</v>
+        <v>7203676</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7414,9 +7404,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7431,57 +7431,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125779339</v>
+        <v>125776142</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>91810</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611640</v>
+        <v>611684</v>
       </c>
       <c r="R69" t="n">
-        <v>7203677</v>
+        <v>7203683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7528,12 +7528,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7641,7 +7641,7 @@
         <v>125779333</v>
       </c>
       <c r="B71" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7735,45 +7735,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125776142</v>
+        <v>125779339</v>
       </c>
       <c r="B72" t="n">
-        <v>91808</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611684</v>
+        <v>611640</v>
       </c>
       <c r="R72" t="n">
-        <v>7203683</v>
+        <v>7203677</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7820,12 +7820,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7835,7 +7835,7 @@
         <v>125779880</v>
       </c>
       <c r="B73" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779340</v>
+        <v>125779771</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,34 +7940,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611680</v>
+        <v>611686</v>
       </c>
       <c r="R74" t="n">
-        <v>7203713</v>
+        <v>7203685</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,44 +8014,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779312</v>
+        <v>125779340</v>
       </c>
       <c r="B75" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611683</v>
+        <v>611680</v>
       </c>
       <c r="R75" t="n">
-        <v>7203677</v>
+        <v>7203713</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779310</v>
+        <v>125779312</v>
       </c>
       <c r="B76" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611700</v>
+        <v>611683</v>
       </c>
       <c r="R76" t="n">
-        <v>7203703</v>
+        <v>7203677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779771</v>
+        <v>125779310</v>
       </c>
       <c r="B77" t="n">
-        <v>80076</v>
+        <v>98364</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611686</v>
+        <v>611700</v>
       </c>
       <c r="R77" t="n">
-        <v>7203685</v>
+        <v>7203703</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8305,12 +8305,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8320,7 +8320,7 @@
         <v>125781627</v>
       </c>
       <c r="B78" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8427,7 +8427,7 @@
         <v>125779332</v>
       </c>
       <c r="B79" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>125779313</v>
       </c>
       <c r="B82" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>125779847</v>
       </c>
       <c r="B83" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>125781650</v>
       </c>
       <c r="B84" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9019,7 +9019,7 @@
         <v>125776368</v>
       </c>
       <c r="B85" t="n">
-        <v>91808</v>
+        <v>91810</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125779324</v>
+        <v>125779874</v>
       </c>
       <c r="B89" t="n">
-        <v>80104</v>
+        <v>80112</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9443,34 +9443,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6461</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>611659</v>
+        <v>611704</v>
       </c>
       <c r="R89" t="n">
-        <v>7203623</v>
+        <v>7203676</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9517,22 +9517,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125779874</v>
+        <v>125779324</v>
       </c>
       <c r="B90" t="n">
-        <v>80112</v>
+        <v>80104</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9540,34 +9540,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6464</v>
+        <v>6461</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>611704</v>
+        <v>611659</v>
       </c>
       <c r="R90" t="n">
-        <v>7203676</v>
+        <v>7203623</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9614,22 +9614,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779852</v>
+        <v>125776127</v>
       </c>
       <c r="B91" t="n">
-        <v>98362</v>
+        <v>80112</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,31 +9637,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611711</v>
+        <v>611681</v>
       </c>
       <c r="R91" t="n">
         <v>7203685</v>
@@ -9711,19 +9711,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125779846</v>
+        <v>125779764</v>
       </c>
       <c r="B92" t="n">
         <v>80105</v>
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611717</v>
+        <v>611648</v>
       </c>
       <c r="R92" t="n">
-        <v>7203689</v>
+        <v>7203687</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9808,19 +9808,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125779764</v>
+        <v>125779846</v>
       </c>
       <c r="B93" t="n">
         <v>80105</v>
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611648</v>
+        <v>611717</v>
       </c>
       <c r="R93" t="n">
-        <v>7203687</v>
+        <v>7203689</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,22 +9905,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125776127</v>
+        <v>125779852</v>
       </c>
       <c r="B94" t="n">
-        <v>80112</v>
+        <v>98364</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9928,31 +9928,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611681</v>
+        <v>611711</v>
       </c>
       <c r="R94" t="n">
         <v>7203685</v>
@@ -10002,44 +10002,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779314</v>
+        <v>125779302</v>
       </c>
       <c r="B95" t="n">
-        <v>98362</v>
+        <v>91236</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10049,10 +10049,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611663</v>
+        <v>611618</v>
       </c>
       <c r="R95" t="n">
-        <v>7203673</v>
+        <v>7203674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10111,10 +10111,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779302</v>
+        <v>125779885</v>
       </c>
       <c r="B96" t="n">
-        <v>91234</v>
+        <v>78973</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10122,34 +10122,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611618</v>
+        <v>611661</v>
       </c>
       <c r="R96" t="n">
-        <v>7203674</v>
+        <v>7203604</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,22 +10196,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779885</v>
+        <v>125779349</v>
       </c>
       <c r="B97" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10219,34 +10219,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611661</v>
+        <v>611652</v>
       </c>
       <c r="R97" t="n">
-        <v>7203604</v>
+        <v>7203627</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10281,6 +10289,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10293,65 +10306,57 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779349</v>
+        <v>125779314</v>
       </c>
       <c r="B98" t="n">
-        <v>57652</v>
+        <v>98364</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611652</v>
+        <v>611663</v>
       </c>
       <c r="R98" t="n">
-        <v>7203627</v>
+        <v>7203673</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10384,11 +10389,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10415,10 +10415,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779299</v>
+        <v>125779329</v>
       </c>
       <c r="B99" t="n">
-        <v>75068</v>
+        <v>80076</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611561</v>
+        <v>611623</v>
       </c>
       <c r="R99" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10512,45 +10512,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779329</v>
+        <v>125779772</v>
       </c>
       <c r="B100" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611623</v>
+        <v>611680</v>
       </c>
       <c r="R100" t="n">
-        <v>7203677</v>
+        <v>7203679</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,57 +10597,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779772</v>
+        <v>125779299</v>
       </c>
       <c r="B101" t="n">
-        <v>80112</v>
+        <v>75068</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611680</v>
+        <v>611561</v>
       </c>
       <c r="R101" t="n">
-        <v>7203679</v>
+        <v>7203692</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,12 +10694,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10709,7 +10709,7 @@
         <v>125779851</v>
       </c>
       <c r="B102" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>125803940</v>
       </c>
       <c r="B104" t="n">
-        <v>91230</v>
+        <v>91232</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>125803917</v>
       </c>
       <c r="B105" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11115,41 +11115,42 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125803950</v>
+        <v>125803668</v>
       </c>
       <c r="B106" t="n">
-        <v>91603</v>
+        <v>98364</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1506</v>
+        <v>221952</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11157,10 +11158,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>611534</v>
+        <v>611679</v>
       </c>
       <c r="R106" t="n">
-        <v>7203710</v>
+        <v>7203707</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11220,42 +11221,41 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125803668</v>
+        <v>125803950</v>
       </c>
       <c r="B107" t="n">
-        <v>98362</v>
+        <v>91605</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221952</v>
+        <v>1506</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>611679</v>
+        <v>611534</v>
       </c>
       <c r="R107" t="n">
-        <v>7203707</v>
+        <v>7203710</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1601,7 +1601,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125781637</v>
+        <v>125780615</v>
       </c>
       <c r="B11" t="n">
         <v>57652</v>
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611631</v>
+        <v>611292</v>
       </c>
       <c r="R11" t="n">
-        <v>7203695</v>
+        <v>7203703</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,22 +1671,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1706,17 +1696,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125776139</v>
+        <v>125781637</v>
       </c>
       <c r="B12" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1724,37 +1714,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611678</v>
+        <v>611631</v>
       </c>
       <c r="R12" t="n">
-        <v>7203688</v>
+        <v>7203695</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1781,9 +1776,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1798,57 +1803,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779322</v>
+        <v>125776139</v>
       </c>
       <c r="B13" t="n">
-        <v>80104</v>
+        <v>80077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611700</v>
+        <v>611678</v>
       </c>
       <c r="R13" t="n">
-        <v>7203701</v>
+        <v>7203688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,44 +1900,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125781663</v>
+        <v>125779322</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>80104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1942,13 +1947,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611570</v>
+        <v>611700</v>
       </c>
       <c r="R14" t="n">
-        <v>7203700</v>
+        <v>7203701</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,19 +1980,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2002,22 +1997,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125779769</v>
+        <v>125781663</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,37 +2020,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611696</v>
+        <v>611570</v>
       </c>
       <c r="R15" t="n">
-        <v>7203681</v>
+        <v>7203700</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2082,9 +2077,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,57 +2104,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125779323</v>
+        <v>125779769</v>
       </c>
       <c r="B16" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611667</v>
+        <v>611696</v>
       </c>
       <c r="R16" t="n">
-        <v>7203673</v>
+        <v>7203681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2196,62 +2201,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125780615</v>
+        <v>125779323</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>80104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611292</v>
+        <v>611667</v>
       </c>
       <c r="R17" t="n">
-        <v>7203703</v>
+        <v>7203673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125779317</v>
+        <v>125779336</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,42 +2625,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611723</v>
+        <v>611575</v>
       </c>
       <c r="R21" t="n">
-        <v>7203703</v>
+        <v>7203712</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,11 +2685,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,10 +2711,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125779336</v>
+        <v>125780607</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,21 +2722,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2759,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611575</v>
+        <v>611445</v>
       </c>
       <c r="R22" t="n">
-        <v>7203712</v>
+        <v>7203816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,12 +2776,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2809,22 +2796,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125780607</v>
+        <v>125779338</v>
       </c>
       <c r="B23" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,21 +2819,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2856,10 +2843,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611445</v>
+        <v>611631</v>
       </c>
       <c r="R23" t="n">
-        <v>7203816</v>
+        <v>7203681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,12 +2873,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2906,22 +2893,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779338</v>
+        <v>125779317</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,34 +2916,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611631</v>
+        <v>611723</v>
       </c>
       <c r="R24" t="n">
-        <v>7203681</v>
+        <v>7203703</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,6 +2984,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3413,50 +3413,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125780614</v>
+        <v>125779763</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>80105</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611292</v>
+        <v>611644</v>
       </c>
       <c r="R29" t="n">
-        <v>7203687</v>
+        <v>7203694</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,12 +3478,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3503,22 +3498,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125779767</v>
+        <v>125779838</v>
       </c>
       <c r="B30" t="n">
-        <v>98364</v>
+        <v>80105</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3526,21 +3521,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3550,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611673</v>
+        <v>611513</v>
       </c>
       <c r="R30" t="n">
-        <v>7203670</v>
+        <v>7203698</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,57 +3595,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125779763</v>
+        <v>125780614</v>
       </c>
       <c r="B31" t="n">
-        <v>80105</v>
+        <v>57652</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611644</v>
+        <v>611292</v>
       </c>
       <c r="R31" t="n">
-        <v>7203694</v>
+        <v>7203687</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3677,12 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,22 +3697,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125779838</v>
+        <v>125779767</v>
       </c>
       <c r="B32" t="n">
-        <v>80105</v>
+        <v>98364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611513</v>
+        <v>611673</v>
       </c>
       <c r="R32" t="n">
-        <v>7203698</v>
+        <v>7203670</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,12 +3794,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125781628</v>
+        <v>125779309</v>
       </c>
       <c r="B49" t="n">
-        <v>91201</v>
+        <v>80105</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,21 +5441,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5465,13 +5465,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611568</v>
+        <v>611679</v>
       </c>
       <c r="R49" t="n">
-        <v>7203718</v>
+        <v>7203682</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5498,19 +5498,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5525,57 +5515,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779315</v>
+        <v>125779876</v>
       </c>
       <c r="B50" t="n">
-        <v>80077</v>
+        <v>80112</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611617</v>
+        <v>611661</v>
       </c>
       <c r="R50" t="n">
-        <v>7203677</v>
+        <v>7203604</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5622,44 +5612,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779309</v>
+        <v>125779343</v>
       </c>
       <c r="B51" t="n">
-        <v>80105</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,10 +5659,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611679</v>
+        <v>611670</v>
       </c>
       <c r="R51" t="n">
-        <v>7203682</v>
+        <v>7203656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5731,10 +5721,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779876</v>
+        <v>125781628</v>
       </c>
       <c r="B52" t="n">
-        <v>80112</v>
+        <v>91201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5742,37 +5732,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611661</v>
+        <v>611568</v>
       </c>
       <c r="R52" t="n">
-        <v>7203604</v>
+        <v>7203718</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5799,9 +5789,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5816,22 +5816,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779343</v>
+        <v>125779315</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5839,21 +5839,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611670</v>
+        <v>611617</v>
       </c>
       <c r="R53" t="n">
-        <v>7203656</v>
+        <v>7203677</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -8909,48 +8909,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125781650</v>
+        <v>125779873</v>
       </c>
       <c r="B84" t="n">
-        <v>91605</v>
+        <v>80112</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611521</v>
+        <v>611693</v>
       </c>
       <c r="R84" t="n">
-        <v>7203626</v>
+        <v>7203707</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,19 +8977,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9004,60 +8994,65 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125776368</v>
+        <v>125781638</v>
       </c>
       <c r="B85" t="n">
-        <v>91810</v>
+        <v>57652</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611705</v>
+        <v>611645</v>
       </c>
       <c r="R85" t="n">
-        <v>7203679</v>
+        <v>7203676</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9084,9 +9079,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9101,60 +9106,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125779873</v>
+        <v>125781650</v>
       </c>
       <c r="B86" t="n">
-        <v>80112</v>
+        <v>91605</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611693</v>
+        <v>611521</v>
       </c>
       <c r="R86" t="n">
-        <v>7203707</v>
+        <v>7203626</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9181,9 +9186,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9198,65 +9213,60 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125781638</v>
+        <v>125776368</v>
       </c>
       <c r="B87" t="n">
-        <v>57652</v>
+        <v>91810</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611645</v>
+        <v>611705</v>
       </c>
       <c r="R87" t="n">
-        <v>7203676</v>
+        <v>7203679</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9283,19 +9293,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9310,12 +9310,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10415,45 +10415,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779329</v>
+        <v>125779851</v>
       </c>
       <c r="B99" t="n">
-        <v>80076</v>
+        <v>98364</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611623</v>
+        <v>611690</v>
       </c>
       <c r="R99" t="n">
-        <v>7203677</v>
+        <v>7203710</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10500,57 +10500,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779772</v>
+        <v>125779329</v>
       </c>
       <c r="B100" t="n">
-        <v>80112</v>
+        <v>80076</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611680</v>
+        <v>611623</v>
       </c>
       <c r="R100" t="n">
-        <v>7203679</v>
+        <v>7203677</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,57 +10597,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779299</v>
+        <v>125779772</v>
       </c>
       <c r="B101" t="n">
-        <v>75068</v>
+        <v>80112</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611561</v>
+        <v>611680</v>
       </c>
       <c r="R101" t="n">
-        <v>7203692</v>
+        <v>7203679</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,57 +10694,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779851</v>
+        <v>125779299</v>
       </c>
       <c r="B102" t="n">
-        <v>98364</v>
+        <v>75068</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611690</v>
+        <v>611561</v>
       </c>
       <c r="R102" t="n">
-        <v>7203710</v>
+        <v>7203692</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125776148</v>
+        <v>125776367</v>
       </c>
       <c r="B2" t="n">
         <v>78973</v>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611660</v>
+        <v>611653</v>
       </c>
       <c r="R2" t="n">
-        <v>7203684</v>
+        <v>7203665</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125776367</v>
+        <v>125776148</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611653</v>
+        <v>611660</v>
       </c>
       <c r="R3" t="n">
-        <v>7203665</v>
+        <v>7203684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125781662</v>
+        <v>125781649</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
+        <v>91534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611570</v>
+        <v>611536</v>
       </c>
       <c r="R6" t="n">
-        <v>7203707</v>
+        <v>7203694</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125781649</v>
+        <v>125779303</v>
       </c>
       <c r="B7" t="n">
-        <v>91532</v>
+        <v>91238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611536</v>
+        <v>611631</v>
       </c>
       <c r="R7" t="n">
-        <v>7203694</v>
+        <v>7203681</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1251,19 +1251,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1278,22 +1268,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125779303</v>
+        <v>125781662</v>
       </c>
       <c r="B8" t="n">
-        <v>91236</v>
+        <v>91256</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,21 +1291,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1325,13 +1315,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611631</v>
+        <v>611570</v>
       </c>
       <c r="R8" t="n">
-        <v>7203681</v>
+        <v>7203707</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1358,9 +1348,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1375,12 +1375,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125780615</v>
+        <v>125781663</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1612,42 +1612,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611292</v>
+        <v>611570</v>
       </c>
       <c r="R11" t="n">
-        <v>7203703</v>
+        <v>7203700</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1671,12 +1666,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,60 +1701,55 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125781637</v>
+        <v>125779323</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>80104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611631</v>
+        <v>611667</v>
       </c>
       <c r="R12" t="n">
-        <v>7203695</v>
+        <v>7203673</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1776,19 +1776,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1803,57 +1793,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125776139</v>
+        <v>125779322</v>
       </c>
       <c r="B13" t="n">
-        <v>80077</v>
+        <v>80104</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611678</v>
+        <v>611700</v>
       </c>
       <c r="R13" t="n">
-        <v>7203688</v>
+        <v>7203701</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,60 +1890,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125779322</v>
+        <v>125781637</v>
       </c>
       <c r="B14" t="n">
-        <v>80104</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611700</v>
+        <v>611631</v>
       </c>
       <c r="R14" t="n">
-        <v>7203701</v>
+        <v>7203695</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1980,9 +1975,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,22 +2002,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125781663</v>
+        <v>125780615</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2020,37 +2025,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611570</v>
+        <v>611292</v>
       </c>
       <c r="R15" t="n">
-        <v>7203700</v>
+        <v>7203703</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2074,22 +2084,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2213,45 +2213,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125779323</v>
+        <v>125776139</v>
       </c>
       <c r="B17" t="n">
-        <v>80104</v>
+        <v>80077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611667</v>
+        <v>611678</v>
       </c>
       <c r="R17" t="n">
-        <v>7203673</v>
+        <v>7203688</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>125779311</v>
       </c>
       <c r="B19" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>125776366</v>
       </c>
       <c r="B20" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125779336</v>
+        <v>125780607</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,21 +2625,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611575</v>
+        <v>611445</v>
       </c>
       <c r="R21" t="n">
-        <v>7203712</v>
+        <v>7203816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2699,22 +2699,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125780607</v>
+        <v>125779336</v>
       </c>
       <c r="B22" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,21 +2722,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611445</v>
+        <v>611575</v>
       </c>
       <c r="R22" t="n">
-        <v>7203816</v>
+        <v>7203712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2796,22 +2796,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125779338</v>
+        <v>125779317</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,34 +2819,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611631</v>
+        <v>611723</v>
       </c>
       <c r="R23" t="n">
-        <v>7203681</v>
+        <v>7203703</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2879,6 +2887,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2905,10 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779317</v>
+        <v>125779338</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,42 +2929,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611723</v>
+        <v>611631</v>
       </c>
       <c r="R24" t="n">
-        <v>7203703</v>
+        <v>7203681</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2984,11 +2989,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3018,7 +3018,7 @@
         <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>125781660</v>
       </c>
       <c r="B27" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
         <v>125779886</v>
       </c>
       <c r="B28" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>125779767</v>
       </c>
       <c r="B32" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3806,48 +3806,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779848</v>
+        <v>125781666</v>
       </c>
       <c r="B33" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611545</v>
+        <v>611652</v>
       </c>
       <c r="R33" t="n">
-        <v>7203710</v>
+        <v>7203680</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,9 +3874,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,22 +3901,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125781666</v>
+        <v>125779834</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>75068</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,37 +3924,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611652</v>
+        <v>611547</v>
       </c>
       <c r="R34" t="n">
-        <v>7203680</v>
+        <v>7203635</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3971,19 +3981,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,19 +3998,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125780608</v>
+        <v>125780606</v>
       </c>
       <c r="B35" t="n">
         <v>80076</v>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611445</v>
+        <v>611311</v>
       </c>
       <c r="R35" t="n">
-        <v>7203816</v>
+        <v>7203689</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125779834</v>
+        <v>125780608</v>
       </c>
       <c r="B36" t="n">
-        <v>75068</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611547</v>
+        <v>611445</v>
       </c>
       <c r="R36" t="n">
-        <v>7203635</v>
+        <v>7203816</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,12 +4192,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4301,45 +4301,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125780606</v>
+        <v>125779848</v>
       </c>
       <c r="B38" t="n">
-        <v>80076</v>
+        <v>98366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611311</v>
+        <v>611545</v>
       </c>
       <c r="R38" t="n">
-        <v>7203689</v>
+        <v>7203710</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,22 +4386,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779844</v>
+        <v>125779853</v>
       </c>
       <c r="B39" t="n">
-        <v>80105</v>
+        <v>98366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611644</v>
+        <v>611691</v>
       </c>
       <c r="R39" t="n">
-        <v>7203690</v>
+        <v>7203679</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4495,45 +4495,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779773</v>
+        <v>125779337</v>
       </c>
       <c r="B40" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611662</v>
+        <v>611615</v>
       </c>
       <c r="R40" t="n">
-        <v>7203612</v>
+        <v>7203678</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,22 +4580,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779337</v>
+        <v>125779319</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,34 +4603,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611615</v>
+        <v>611663</v>
       </c>
       <c r="R41" t="n">
-        <v>7203678</v>
+        <v>7203613</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4663,6 +4671,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4689,7 +4702,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779319</v>
+        <v>125779316</v>
       </c>
       <c r="B42" t="n">
         <v>57652</v>
@@ -4732,10 +4745,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611663</v>
+        <v>611507</v>
       </c>
       <c r="R42" t="n">
-        <v>7203613</v>
+        <v>7203685</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4772,7 +4785,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4799,7 +4812,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779316</v>
+        <v>125779318</v>
       </c>
       <c r="B43" t="n">
         <v>57652</v>
@@ -4842,10 +4855,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611507</v>
+        <v>611725</v>
       </c>
       <c r="R43" t="n">
-        <v>7203685</v>
+        <v>7203707</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,53 +4922,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779318</v>
+        <v>125779773</v>
       </c>
       <c r="B44" t="n">
-        <v>57652</v>
+        <v>80112</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611725</v>
+        <v>611662</v>
       </c>
       <c r="R44" t="n">
-        <v>7203707</v>
+        <v>7203612</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4990,11 +4995,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5007,22 +5007,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779853</v>
+        <v>125779844</v>
       </c>
       <c r="B45" t="n">
-        <v>98364</v>
+        <v>80105</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611691</v>
+        <v>611644</v>
       </c>
       <c r="R45" t="n">
-        <v>7203679</v>
+        <v>7203690</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5213,10 +5213,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125779346</v>
+        <v>125781648</v>
       </c>
       <c r="B47" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5224,45 +5224,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>611666</v>
+        <v>611683</v>
       </c>
       <c r="R47" t="n">
-        <v>7203652</v>
+        <v>7203710</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5289,14 +5281,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5311,22 +5308,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125781648</v>
+        <v>125779346</v>
       </c>
       <c r="B48" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,37 +5331,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>611683</v>
+        <v>611666</v>
       </c>
       <c r="R48" t="n">
-        <v>7203710</v>
+        <v>7203652</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5391,19 +5396,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5418,44 +5418,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125779309</v>
+        <v>125779315</v>
       </c>
       <c r="B49" t="n">
-        <v>80105</v>
+        <v>80077</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611679</v>
+        <v>611617</v>
       </c>
       <c r="R49" t="n">
-        <v>7203682</v>
+        <v>7203677</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5527,45 +5527,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779876</v>
+        <v>125779343</v>
       </c>
       <c r="B50" t="n">
-        <v>80112</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611661</v>
+        <v>611670</v>
       </c>
       <c r="R50" t="n">
-        <v>7203604</v>
+        <v>7203656</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5612,22 +5612,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779343</v>
+        <v>125779863</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5635,34 +5635,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611670</v>
+        <v>611623</v>
       </c>
       <c r="R51" t="n">
-        <v>7203656</v>
+        <v>7203692</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5697,6 +5705,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5709,12 +5722,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5724,7 +5737,7 @@
         <v>125781628</v>
       </c>
       <c r="B52" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5821,39 +5834,39 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779315</v>
+        <v>125779309</v>
       </c>
       <c r="B53" t="n">
-        <v>80077</v>
+        <v>80105</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,10 +5876,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611617</v>
+        <v>611679</v>
       </c>
       <c r="R53" t="n">
-        <v>7203677</v>
+        <v>7203682</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5925,53 +5938,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779863</v>
+        <v>125779876</v>
       </c>
       <c r="B54" t="n">
-        <v>57652</v>
+        <v>80112</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611623</v>
+        <v>611661</v>
       </c>
       <c r="R54" t="n">
-        <v>7203692</v>
+        <v>7203604</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6004,11 +6009,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6038,7 +6038,7 @@
         <v>125779320</v>
       </c>
       <c r="B55" t="n">
-        <v>91605</v>
+        <v>91607</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6132,10 +6132,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125779881</v>
+        <v>125781664</v>
       </c>
       <c r="B56" t="n">
-        <v>91254</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,37 +6143,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611650</v>
+        <v>611539</v>
       </c>
       <c r="R56" t="n">
-        <v>7203647</v>
+        <v>7203643</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6200,9 +6200,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6217,22 +6227,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125781664</v>
+        <v>125779881</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6240,37 +6250,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611539</v>
+        <v>611650</v>
       </c>
       <c r="R57" t="n">
-        <v>7203643</v>
+        <v>7203647</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6297,19 +6307,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6324,44 +6324,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779869</v>
+        <v>125779842</v>
       </c>
       <c r="B58" t="n">
-        <v>80076</v>
+        <v>80105</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611687</v>
+        <v>611593</v>
       </c>
       <c r="R58" t="n">
-        <v>7203684</v>
+        <v>7203711</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6530,45 +6530,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779344</v>
+        <v>125779850</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611653</v>
+        <v>611637</v>
       </c>
       <c r="R60" t="n">
-        <v>7203626</v>
+        <v>7203685</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6615,22 +6615,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779842</v>
+        <v>125776365</v>
       </c>
       <c r="B61" t="n">
-        <v>80105</v>
+        <v>98366</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6638,21 +6638,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611593</v>
+        <v>611567</v>
       </c>
       <c r="R61" t="n">
-        <v>7203711</v>
+        <v>7203714</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6712,22 +6712,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125780620</v>
+        <v>125779869</v>
       </c>
       <c r="B62" t="n">
-        <v>57652</v>
+        <v>80076</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6735,39 +6735,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611381</v>
+        <v>611687</v>
       </c>
       <c r="R62" t="n">
-        <v>7203809</v>
+        <v>7203684</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6794,12 +6789,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,57 +6809,62 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779850</v>
+        <v>125780620</v>
       </c>
       <c r="B63" t="n">
-        <v>98364</v>
+        <v>57652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611637</v>
+        <v>611381</v>
       </c>
       <c r="R63" t="n">
-        <v>7203685</v>
+        <v>7203809</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6891,12 +6891,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6911,57 +6911,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125776365</v>
+        <v>125779344</v>
       </c>
       <c r="B64" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611567</v>
+        <v>611653</v>
       </c>
       <c r="R64" t="n">
-        <v>7203714</v>
+        <v>7203626</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7008,12 +7008,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7446,7 +7446,7 @@
         <v>125776142</v>
       </c>
       <c r="B69" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779333</v>
+        <v>125779339</v>
       </c>
       <c r="B71" t="n">
-        <v>91254</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7649,21 +7649,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611659</v>
+        <v>611640</v>
       </c>
       <c r="R71" t="n">
-        <v>7203648</v>
+        <v>7203677</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7735,10 +7735,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125779339</v>
+        <v>125779333</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7746,21 +7746,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7770,10 +7770,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>611640</v>
+        <v>611659</v>
       </c>
       <c r="R72" t="n">
-        <v>7203677</v>
+        <v>7203648</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7835,7 +7835,7 @@
         <v>125779880</v>
       </c>
       <c r="B73" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>125779312</v>
       </c>
       <c r="B76" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>125779310</v>
       </c>
       <c r="B77" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125781627</v>
+        <v>125779847</v>
       </c>
       <c r="B78" t="n">
-        <v>91201</v>
+        <v>98366</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611526</v>
+        <v>611502</v>
       </c>
       <c r="R78" t="n">
-        <v>7203708</v>
+        <v>7203644</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,19 +8385,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8412,44 +8402,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779332</v>
+        <v>125781627</v>
       </c>
       <c r="B79" t="n">
-        <v>91254</v>
+        <v>91203</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8459,13 +8449,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611525</v>
+        <v>611526</v>
       </c>
       <c r="R79" t="n">
-        <v>7203705</v>
+        <v>7203708</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8492,9 +8482,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8509,57 +8509,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779875</v>
+        <v>125779332</v>
       </c>
       <c r="B80" t="n">
-        <v>80112</v>
+        <v>91256</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611687</v>
+        <v>611525</v>
       </c>
       <c r="R80" t="n">
-        <v>7203684</v>
+        <v>7203705</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8606,22 +8606,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779307</v>
+        <v>125779875</v>
       </c>
       <c r="B81" t="n">
-        <v>80105</v>
+        <v>80112</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8629,34 +8629,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611707</v>
+        <v>611687</v>
       </c>
       <c r="R81" t="n">
-        <v>7203701</v>
+        <v>7203684</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8703,22 +8703,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779313</v>
+        <v>125779307</v>
       </c>
       <c r="B82" t="n">
-        <v>98364</v>
+        <v>80105</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611663</v>
+        <v>611707</v>
       </c>
       <c r="R82" t="n">
-        <v>7203664</v>
+        <v>7203701</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8812,10 +8812,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779847</v>
+        <v>125779313</v>
       </c>
       <c r="B83" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,14 +8843,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611502</v>
+        <v>611663</v>
       </c>
       <c r="R83" t="n">
-        <v>7203644</v>
+        <v>7203664</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,60 +8897,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125779873</v>
+        <v>125781650</v>
       </c>
       <c r="B84" t="n">
-        <v>80112</v>
+        <v>91607</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
+        <v>1506</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611693</v>
+        <v>611521</v>
       </c>
       <c r="R84" t="n">
-        <v>7203707</v>
+        <v>7203626</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,9 +8977,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8994,12 +9004,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9111,55 +9121,63 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125781650</v>
+        <v>125779347</v>
       </c>
       <c r="B86" t="n">
-        <v>91605</v>
+        <v>57652</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611521</v>
+        <v>611688</v>
       </c>
       <c r="R86" t="n">
-        <v>7203626</v>
+        <v>7203713</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9186,19 +9204,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:16</t>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9213,12 +9226,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9228,7 +9241,7 @@
         <v>125776368</v>
       </c>
       <c r="B87" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9322,53 +9335,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125779347</v>
+        <v>125779873</v>
       </c>
       <c r="B88" t="n">
-        <v>57652</v>
+        <v>80112</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611688</v>
+        <v>611693</v>
       </c>
       <c r="R88" t="n">
-        <v>7203713</v>
+        <v>7203707</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9403,11 +9408,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,12 +9420,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125776127</v>
+        <v>125779764</v>
       </c>
       <c r="B91" t="n">
-        <v>80112</v>
+        <v>80105</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,34 +9637,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611681</v>
+        <v>611648</v>
       </c>
       <c r="R91" t="n">
-        <v>7203685</v>
+        <v>7203687</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9711,19 +9711,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125779764</v>
+        <v>125779846</v>
       </c>
       <c r="B92" t="n">
         <v>80105</v>
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611648</v>
+        <v>611717</v>
       </c>
       <c r="R92" t="n">
-        <v>7203687</v>
+        <v>7203689</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9808,22 +9808,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125779846</v>
+        <v>125776127</v>
       </c>
       <c r="B93" t="n">
-        <v>80105</v>
+        <v>80112</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611717</v>
+        <v>611681</v>
       </c>
       <c r="R93" t="n">
-        <v>7203689</v>
+        <v>7203685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,12 +9905,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -9920,7 +9920,7 @@
         <v>125779852</v>
       </c>
       <c r="B94" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10014,10 +10014,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779302</v>
+        <v>125779885</v>
       </c>
       <c r="B95" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,34 +10025,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611618</v>
+        <v>611661</v>
       </c>
       <c r="R95" t="n">
-        <v>7203674</v>
+        <v>7203604</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10099,57 +10099,57 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779885</v>
+        <v>125779314</v>
       </c>
       <c r="B96" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611661</v>
+        <v>611663</v>
       </c>
       <c r="R96" t="n">
-        <v>7203604</v>
+        <v>7203673</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,22 +10196,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779349</v>
+        <v>125779302</v>
       </c>
       <c r="B97" t="n">
-        <v>57652</v>
+        <v>91238</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10219,42 +10219,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611652</v>
+        <v>611618</v>
       </c>
       <c r="R97" t="n">
-        <v>7203627</v>
+        <v>7203674</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10287,11 +10279,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10318,45 +10305,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779314</v>
+        <v>125779349</v>
       </c>
       <c r="B98" t="n">
-        <v>98364</v>
+        <v>57652</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611663</v>
+        <v>611652</v>
       </c>
       <c r="R98" t="n">
-        <v>7203673</v>
+        <v>7203627</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10389,6 +10384,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10415,45 +10415,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779851</v>
+        <v>125779299</v>
       </c>
       <c r="B99" t="n">
-        <v>98364</v>
+        <v>75068</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611690</v>
+        <v>611561</v>
       </c>
       <c r="R99" t="n">
-        <v>7203710</v>
+        <v>7203692</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10500,57 +10500,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779329</v>
+        <v>125779772</v>
       </c>
       <c r="B100" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611623</v>
+        <v>611680</v>
       </c>
       <c r="R100" t="n">
-        <v>7203677</v>
+        <v>7203679</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,22 +10597,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779772</v>
+        <v>125779851</v>
       </c>
       <c r="B101" t="n">
-        <v>80112</v>
+        <v>98366</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10620,21 +10620,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611680</v>
+        <v>611690</v>
       </c>
       <c r="R101" t="n">
-        <v>7203679</v>
+        <v>7203710</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,22 +10694,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779299</v>
+        <v>125779329</v>
       </c>
       <c r="B102" t="n">
-        <v>75068</v>
+        <v>80076</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10717,21 +10717,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611561</v>
+        <v>611623</v>
       </c>
       <c r="R102" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>125803940</v>
       </c>
       <c r="B104" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>125803917</v>
       </c>
       <c r="B105" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11115,42 +11115,41 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125803668</v>
+        <v>125803950</v>
       </c>
       <c r="B106" t="n">
-        <v>98364</v>
+        <v>91607</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221952</v>
+        <v>1506</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11158,10 +11157,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>611679</v>
+        <v>611534</v>
       </c>
       <c r="R106" t="n">
-        <v>7203707</v>
+        <v>7203710</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11221,41 +11220,42 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125803950</v>
+        <v>125803668</v>
       </c>
       <c r="B107" t="n">
-        <v>91605</v>
+        <v>98366</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1506</v>
+        <v>221952</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11263,10 +11263,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>611534</v>
+        <v>611679</v>
       </c>
       <c r="R107" t="n">
-        <v>7203710</v>
+        <v>7203707</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1280,10 +1280,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125781662</v>
+        <v>125781636</v>
       </c>
       <c r="B8" t="n">
-        <v>91256</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,34 +1291,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611570</v>
+        <v>611590</v>
       </c>
       <c r="R8" t="n">
-        <v>7203707</v>
+        <v>7203713</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1350,7 +1355,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1360,7 +1365,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,7 +1392,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125781636</v>
+        <v>125780621</v>
       </c>
       <c r="B9" t="n">
         <v>57652</v>
@@ -1427,13 +1432,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611590</v>
+        <v>611445</v>
       </c>
       <c r="R9" t="n">
-        <v>7203713</v>
+        <v>7203814</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1457,22 +1462,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1492,17 +1487,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125780621</v>
+        <v>125781662</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>91256</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,42 +1505,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611445</v>
+        <v>611570</v>
       </c>
       <c r="R10" t="n">
-        <v>7203814</v>
+        <v>7203707</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1569,12 +1559,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125781663</v>
+        <v>125776139</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1612,37 +1612,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611570</v>
+        <v>611678</v>
       </c>
       <c r="R11" t="n">
-        <v>7203700</v>
+        <v>7203688</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,19 +1669,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,12 +1686,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1805,45 +1795,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779322</v>
+        <v>125779769</v>
       </c>
       <c r="B13" t="n">
-        <v>80104</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611700</v>
+        <v>611696</v>
       </c>
       <c r="R13" t="n">
-        <v>7203701</v>
+        <v>7203681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,65 +1880,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125781637</v>
+        <v>125779322</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>80104</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611631</v>
+        <v>611700</v>
       </c>
       <c r="R14" t="n">
-        <v>7203695</v>
+        <v>7203701</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1975,19 +1960,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2002,19 +1977,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125780615</v>
+        <v>125781637</v>
       </c>
       <c r="B15" t="n">
         <v>57652</v>
@@ -2054,13 +2029,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611292</v>
+        <v>611631</v>
       </c>
       <c r="R15" t="n">
-        <v>7203703</v>
+        <v>7203695</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2084,12 +2059,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2109,17 +2094,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125779769</v>
+        <v>125780615</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2127,34 +2112,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611696</v>
+        <v>611292</v>
       </c>
       <c r="R16" t="n">
-        <v>7203681</v>
+        <v>7203703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2181,12 +2171,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,22 +2191,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125776139</v>
+        <v>125781663</v>
       </c>
       <c r="B17" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2224,37 +2214,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611678</v>
+        <v>611570</v>
       </c>
       <c r="R17" t="n">
-        <v>7203688</v>
+        <v>7203700</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2281,9 +2271,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,65 +2298,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779864</v>
+        <v>125779311</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>98366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611742</v>
+        <v>611690</v>
       </c>
       <c r="R18" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,11 +2383,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2408,19 +2395,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125779311</v>
+        <v>125776366</v>
       </c>
       <c r="B19" t="n">
         <v>98366</v>
@@ -2451,11 +2438,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611690</v>
+        <v>611679</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2505,57 +2492,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125776366</v>
+        <v>125779864</v>
       </c>
       <c r="B20" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611679</v>
+        <v>611742</v>
       </c>
       <c r="R20" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,6 +2585,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,12 +2602,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125781666</v>
+        <v>125779884</v>
       </c>
       <c r="B33" t="n">
         <v>78973</v>
@@ -3837,17 +3837,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611652</v>
+        <v>611666</v>
       </c>
       <c r="R33" t="n">
-        <v>7203680</v>
+        <v>7203678</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,19 +3874,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125779834</v>
+        <v>125780606</v>
       </c>
       <c r="B34" t="n">
-        <v>75068</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,34 +3914,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611547</v>
+        <v>611311</v>
       </c>
       <c r="R34" t="n">
-        <v>7203635</v>
+        <v>7203689</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3978,12 +3968,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,19 +3988,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125780606</v>
+        <v>125780608</v>
       </c>
       <c r="B35" t="n">
         <v>80076</v>
@@ -4045,10 +4035,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611311</v>
+        <v>611445</v>
       </c>
       <c r="R35" t="n">
-        <v>7203689</v>
+        <v>7203816</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4107,10 +4097,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125780608</v>
+        <v>125781666</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,21 +4108,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4142,13 +4132,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611445</v>
+        <v>611652</v>
       </c>
       <c r="R36" t="n">
-        <v>7203816</v>
+        <v>7203680</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4172,12 +4162,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779884</v>
+        <v>125779834</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>75068</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,21 +4215,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611666</v>
+        <v>611547</v>
       </c>
       <c r="R37" t="n">
-        <v>7203678</v>
+        <v>7203635</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -6035,45 +6035,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779320</v>
+        <v>125779850</v>
       </c>
       <c r="B55" t="n">
-        <v>91607</v>
+        <v>98366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611543</v>
+        <v>611637</v>
       </c>
       <c r="R55" t="n">
-        <v>7203697</v>
+        <v>7203685</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6120,60 +6120,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125781664</v>
+        <v>125776365</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611539</v>
+        <v>611567</v>
       </c>
       <c r="R56" t="n">
-        <v>7203643</v>
+        <v>7203714</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6200,19 +6200,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,57 +6217,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779881</v>
+        <v>125779320</v>
       </c>
       <c r="B57" t="n">
-        <v>91256</v>
+        <v>91607</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611650</v>
+        <v>611543</v>
       </c>
       <c r="R57" t="n">
-        <v>7203647</v>
+        <v>7203697</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6324,44 +6314,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779842</v>
+        <v>125779881</v>
       </c>
       <c r="B58" t="n">
-        <v>80105</v>
+        <v>91256</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6371,10 +6361,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611593</v>
+        <v>611650</v>
       </c>
       <c r="R58" t="n">
-        <v>7203711</v>
+        <v>7203647</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6530,32 +6520,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779850</v>
+        <v>125779869</v>
       </c>
       <c r="B60" t="n">
-        <v>98366</v>
+        <v>80076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6565,10 +6555,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611637</v>
+        <v>611687</v>
       </c>
       <c r="R60" t="n">
-        <v>7203685</v>
+        <v>7203684</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6627,45 +6617,50 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125776365</v>
+        <v>125780620</v>
       </c>
       <c r="B61" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611567</v>
+        <v>611381</v>
       </c>
       <c r="R61" t="n">
-        <v>7203714</v>
+        <v>7203809</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6692,12 +6687,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6712,22 +6707,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779869</v>
+        <v>125779344</v>
       </c>
       <c r="B62" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6735,34 +6730,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611687</v>
+        <v>611653</v>
       </c>
       <c r="R62" t="n">
-        <v>7203684</v>
+        <v>7203626</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6809,22 +6804,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125780620</v>
+        <v>125781664</v>
       </c>
       <c r="B63" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6832,42 +6827,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611381</v>
+        <v>611539</v>
       </c>
       <c r="R63" t="n">
-        <v>7203809</v>
+        <v>7203643</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6891,12 +6881,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6916,52 +6916,52 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125779344</v>
+        <v>125779842</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>80105</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611653</v>
+        <v>611593</v>
       </c>
       <c r="R64" t="n">
-        <v>7203626</v>
+        <v>7203711</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7008,22 +7008,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125779308</v>
+        <v>125781642</v>
       </c>
       <c r="B65" t="n">
-        <v>80105</v>
+        <v>56844</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7031,37 +7031,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611684</v>
+        <v>611705</v>
       </c>
       <c r="R65" t="n">
-        <v>7203690</v>
+        <v>7203676</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7088,9 +7093,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7105,65 +7120,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125781635</v>
+        <v>125779308</v>
       </c>
       <c r="B66" t="n">
-        <v>57652</v>
+        <v>80105</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611535</v>
+        <v>611684</v>
       </c>
       <c r="R66" t="n">
-        <v>7203644</v>
+        <v>7203690</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7190,19 +7200,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,19 +7217,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125780618</v>
+        <v>125781635</v>
       </c>
       <c r="B67" t="n">
         <v>57652</v>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611378</v>
+        <v>611535</v>
       </c>
       <c r="R67" t="n">
-        <v>7203714</v>
+        <v>7203644</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7299,12 +7299,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7324,45 +7334,45 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125781642</v>
+        <v>125780618</v>
       </c>
       <c r="B68" t="n">
-        <v>56844</v>
+        <v>57652</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7371,13 +7381,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611705</v>
+        <v>611378</v>
       </c>
       <c r="R68" t="n">
-        <v>7203676</v>
+        <v>7203714</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7401,22 +7411,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125779847</v>
+        <v>125781627</v>
       </c>
       <c r="B78" t="n">
-        <v>98366</v>
+        <v>91203</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611502</v>
+        <v>611526</v>
       </c>
       <c r="R78" t="n">
-        <v>7203644</v>
+        <v>7203708</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,9 +8385,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8402,44 +8412,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125781627</v>
+        <v>125779332</v>
       </c>
       <c r="B79" t="n">
-        <v>91203</v>
+        <v>91256</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8449,13 +8459,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611526</v>
+        <v>611525</v>
       </c>
       <c r="R79" t="n">
-        <v>7203708</v>
+        <v>7203705</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8482,19 +8492,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8509,57 +8509,57 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779332</v>
+        <v>125779875</v>
       </c>
       <c r="B80" t="n">
-        <v>91256</v>
+        <v>80112</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611525</v>
+        <v>611687</v>
       </c>
       <c r="R80" t="n">
-        <v>7203705</v>
+        <v>7203684</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8606,22 +8606,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779875</v>
+        <v>125779307</v>
       </c>
       <c r="B81" t="n">
-        <v>80112</v>
+        <v>80105</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8629,34 +8629,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611687</v>
+        <v>611707</v>
       </c>
       <c r="R81" t="n">
-        <v>7203684</v>
+        <v>7203701</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8703,22 +8703,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779307</v>
+        <v>125779313</v>
       </c>
       <c r="B82" t="n">
-        <v>80105</v>
+        <v>98366</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8726,21 +8726,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8750,10 +8750,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611707</v>
+        <v>611663</v>
       </c>
       <c r="R82" t="n">
-        <v>7203701</v>
+        <v>7203664</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8812,7 +8812,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779313</v>
+        <v>125779847</v>
       </c>
       <c r="B83" t="n">
         <v>98366</v>
@@ -8843,14 +8843,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611663</v>
+        <v>611502</v>
       </c>
       <c r="R83" t="n">
-        <v>7203664</v>
+        <v>7203644</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,12 +8897,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10111,45 +10111,53 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779314</v>
+        <v>125779349</v>
       </c>
       <c r="B96" t="n">
-        <v>98366</v>
+        <v>57652</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611663</v>
+        <v>611652</v>
       </c>
       <c r="R96" t="n">
-        <v>7203673</v>
+        <v>7203627</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10182,6 +10190,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10208,32 +10221,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779302</v>
+        <v>125779314</v>
       </c>
       <c r="B97" t="n">
-        <v>91238</v>
+        <v>98366</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10243,10 +10256,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611618</v>
+        <v>611663</v>
       </c>
       <c r="R97" t="n">
-        <v>7203674</v>
+        <v>7203673</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10305,10 +10318,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779349</v>
+        <v>125779302</v>
       </c>
       <c r="B98" t="n">
-        <v>57652</v>
+        <v>91238</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10316,42 +10329,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611652</v>
+        <v>611618</v>
       </c>
       <c r="R98" t="n">
-        <v>7203627</v>
+        <v>7203674</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10384,11 +10389,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10905,10 +10905,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125803940</v>
+        <v>125803917</v>
       </c>
       <c r="B104" t="n">
-        <v>91234</v>
+        <v>91256</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10916,21 +10916,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10947,10 +10947,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>611534</v>
+        <v>611560</v>
       </c>
       <c r="R104" t="n">
-        <v>7203710</v>
+        <v>7203700</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11010,10 +11010,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125803917</v>
+        <v>125803940</v>
       </c>
       <c r="B105" t="n">
-        <v>91256</v>
+        <v>91234</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11021,21 +11021,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>611560</v>
+        <v>611534</v>
       </c>
       <c r="R105" t="n">
-        <v>7203700</v>
+        <v>7203710</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125776367</v>
+        <v>125776148</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611653</v>
+        <v>611660</v>
       </c>
       <c r="R2" t="n">
-        <v>7203665</v>
+        <v>7203684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125776148</v>
+        <v>125776367</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611660</v>
+        <v>611653</v>
       </c>
       <c r="R3" t="n">
-        <v>7203684</v>
+        <v>7203665</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>125779334</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125779345</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>125781649</v>
       </c>
       <c r="B6" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125779303</v>
+        <v>125781662</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611631</v>
+        <v>611570</v>
       </c>
       <c r="R7" t="n">
-        <v>7203681</v>
+        <v>7203707</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1251,9 +1251,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,22 +1278,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125781636</v>
+        <v>125779303</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>91242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,42 +1301,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611590</v>
+        <v>611631</v>
       </c>
       <c r="R8" t="n">
-        <v>7203713</v>
+        <v>7203681</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1353,19 +1358,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,22 +1375,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125780621</v>
+        <v>125781636</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1432,13 +1427,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611445</v>
+        <v>611590</v>
       </c>
       <c r="R9" t="n">
-        <v>7203814</v>
+        <v>7203713</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,12 +1457,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,17 +1492,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125781662</v>
+        <v>125780621</v>
       </c>
       <c r="B10" t="n">
-        <v>91256</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,37 +1510,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611570</v>
+        <v>611445</v>
       </c>
       <c r="R10" t="n">
-        <v>7203707</v>
+        <v>7203814</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1559,22 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1594,52 +1594,52 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125776139</v>
+        <v>125779322</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>80108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611678</v>
+        <v>611700</v>
       </c>
       <c r="R11" t="n">
-        <v>7203688</v>
+        <v>7203701</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,57 +1686,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125779323</v>
+        <v>125779769</v>
       </c>
       <c r="B12" t="n">
-        <v>80104</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611667</v>
+        <v>611696</v>
       </c>
       <c r="R12" t="n">
-        <v>7203673</v>
+        <v>7203681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,57 +1783,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779769</v>
+        <v>125779323</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611696</v>
+        <v>611667</v>
       </c>
       <c r="R13" t="n">
-        <v>7203681</v>
+        <v>7203673</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,60 +1880,65 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125779322</v>
+        <v>125781637</v>
       </c>
       <c r="B14" t="n">
-        <v>80104</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611700</v>
+        <v>611631</v>
       </c>
       <c r="R14" t="n">
-        <v>7203701</v>
+        <v>7203695</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1960,9 +1965,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1977,22 +1992,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125781637</v>
+        <v>125780615</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,13 +2044,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611631</v>
+        <v>611292</v>
       </c>
       <c r="R15" t="n">
-        <v>7203695</v>
+        <v>7203703</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2059,22 +2074,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:59</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2094,17 +2099,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125780615</v>
+        <v>125781663</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2112,42 +2117,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611292</v>
+        <v>611570</v>
       </c>
       <c r="R16" t="n">
-        <v>7203703</v>
+        <v>7203700</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2171,12 +2171,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2196,17 +2206,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125781663</v>
+        <v>125776139</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>80081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2214,37 +2224,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611570</v>
+        <v>611678</v>
       </c>
       <c r="R17" t="n">
-        <v>7203700</v>
+        <v>7203688</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,19 +2281,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,57 +2298,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125779311</v>
+        <v>125779864</v>
       </c>
       <c r="B18" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611690</v>
+        <v>611742</v>
       </c>
       <c r="R18" t="n">
-        <v>7203691</v>
+        <v>7203697</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,6 +2391,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2395,12 +2408,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2410,7 +2423,7 @@
         <v>125776366</v>
       </c>
       <c r="B19" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2504,53 +2517,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125779864</v>
+        <v>125779311</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>98370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611742</v>
+        <v>611690</v>
       </c>
       <c r="R20" t="n">
-        <v>7203697</v>
+        <v>7203691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2585,11 +2590,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2602,12 +2602,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2617,7 +2617,7 @@
         <v>125780607</v>
       </c>
       <c r="B21" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>125779336</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125779317</v>
+        <v>125779338</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,42 +2819,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611723</v>
+        <v>611631</v>
       </c>
       <c r="R23" t="n">
-        <v>7203703</v>
+        <v>7203681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,11 +2879,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2918,10 +2905,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779338</v>
+        <v>125779317</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,34 +2916,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611631</v>
+        <v>611723</v>
       </c>
       <c r="R24" t="n">
-        <v>7203681</v>
+        <v>7203703</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,6 +2984,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3018,7 +3018,7 @@
         <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125776147</v>
+        <v>125781660</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,37 +3123,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611642</v>
+        <v>611570</v>
       </c>
       <c r="R26" t="n">
-        <v>7203689</v>
+        <v>7203708</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3180,9 +3180,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,60 +3207,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125781660</v>
+        <v>125779838</v>
       </c>
       <c r="B27" t="n">
-        <v>91252</v>
+        <v>80109</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611570</v>
+        <v>611513</v>
       </c>
       <c r="R27" t="n">
-        <v>7203708</v>
+        <v>7203698</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3277,19 +3287,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3304,12 +3304,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
         <v>125779886</v>
       </c>
       <c r="B28" t="n">
-        <v>91812</v>
+        <v>91816</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,45 +3413,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125779763</v>
+        <v>125776147</v>
       </c>
       <c r="B29" t="n">
-        <v>80105</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611644</v>
+        <v>611642</v>
       </c>
       <c r="R29" t="n">
-        <v>7203694</v>
+        <v>7203689</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,22 +3498,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125779838</v>
+        <v>125779767</v>
       </c>
       <c r="B30" t="n">
-        <v>80105</v>
+        <v>98370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3521,21 +3521,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611513</v>
+        <v>611673</v>
       </c>
       <c r="R30" t="n">
-        <v>7203698</v>
+        <v>7203670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3595,62 +3595,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125780614</v>
+        <v>125779763</v>
       </c>
       <c r="B31" t="n">
-        <v>57652</v>
+        <v>80109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611292</v>
+        <v>611644</v>
       </c>
       <c r="R31" t="n">
-        <v>7203687</v>
+        <v>7203694</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3677,12 +3672,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,57 +3692,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125779767</v>
+        <v>125780614</v>
       </c>
       <c r="B32" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611673</v>
+        <v>611292</v>
       </c>
       <c r="R32" t="n">
-        <v>7203670</v>
+        <v>7203687</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,22 +3794,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779884</v>
+        <v>125781666</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3837,17 +3837,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611666</v>
+        <v>611652</v>
       </c>
       <c r="R33" t="n">
-        <v>7203678</v>
+        <v>7203680</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,9 +3874,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,22 +3901,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780606</v>
+        <v>125780608</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3938,10 +3948,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611311</v>
+        <v>611445</v>
       </c>
       <c r="R34" t="n">
-        <v>7203689</v>
+        <v>7203816</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4000,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125780608</v>
+        <v>125779834</v>
       </c>
       <c r="B35" t="n">
-        <v>80076</v>
+        <v>75072</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,34 +4021,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611445</v>
+        <v>611547</v>
       </c>
       <c r="R35" t="n">
-        <v>7203816</v>
+        <v>7203635</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4065,12 +4075,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4085,22 +4095,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125781666</v>
+        <v>125780606</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4118,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,13 +4142,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611652</v>
+        <v>611311</v>
       </c>
       <c r="R36" t="n">
-        <v>7203680</v>
+        <v>7203689</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4162,22 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4197,39 +4197,39 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779834</v>
+        <v>125779848</v>
       </c>
       <c r="B37" t="n">
-        <v>75068</v>
+        <v>98370</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611547</v>
+        <v>611545</v>
       </c>
       <c r="R37" t="n">
-        <v>7203635</v>
+        <v>7203710</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,32 +4301,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779848</v>
+        <v>125779884</v>
       </c>
       <c r="B38" t="n">
-        <v>98366</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611545</v>
+        <v>611666</v>
       </c>
       <c r="R38" t="n">
-        <v>7203710</v>
+        <v>7203678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779853</v>
+        <v>125779773</v>
       </c>
       <c r="B39" t="n">
-        <v>98366</v>
+        <v>80116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611691</v>
+        <v>611662</v>
       </c>
       <c r="R39" t="n">
-        <v>7203679</v>
+        <v>7203612</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,12 +4483,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4498,7 +4498,7 @@
         <v>125779337</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>125779319</v>
       </c>
       <c r="B41" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>125779316</v>
       </c>
       <c r="B42" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>125779318</v>
       </c>
       <c r="B43" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4922,10 +4922,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779773</v>
+        <v>125779844</v>
       </c>
       <c r="B44" t="n">
-        <v>80112</v>
+        <v>80109</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4933,21 +4933,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611662</v>
+        <v>611644</v>
       </c>
       <c r="R44" t="n">
-        <v>7203612</v>
+        <v>7203690</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5007,22 +5007,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125779844</v>
+        <v>125779853</v>
       </c>
       <c r="B45" t="n">
-        <v>80105</v>
+        <v>98370</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5030,21 +5030,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>611644</v>
+        <v>611691</v>
       </c>
       <c r="R45" t="n">
-        <v>7203690</v>
+        <v>7203679</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5119,7 +5119,7 @@
         <v>125776134</v>
       </c>
       <c r="B46" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>125781648</v>
       </c>
       <c r="B47" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>125779346</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125779315</v>
+        <v>125779863</v>
       </c>
       <c r="B49" t="n">
-        <v>80077</v>
+        <v>57656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,34 +5441,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611617</v>
+        <v>611623</v>
       </c>
       <c r="R49" t="n">
-        <v>7203677</v>
+        <v>7203692</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5503,6 +5511,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5515,22 +5528,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125779343</v>
+        <v>125779315</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>80081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5538,21 +5551,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5562,10 +5575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>611670</v>
+        <v>611617</v>
       </c>
       <c r="R50" t="n">
-        <v>7203656</v>
+        <v>7203677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5624,53 +5637,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779863</v>
+        <v>125779309</v>
       </c>
       <c r="B51" t="n">
-        <v>57652</v>
+        <v>80109</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611623</v>
+        <v>611679</v>
       </c>
       <c r="R51" t="n">
-        <v>7203692</v>
+        <v>7203682</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5705,11 +5710,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5722,22 +5722,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125781628</v>
+        <v>125779876</v>
       </c>
       <c r="B52" t="n">
-        <v>91203</v>
+        <v>80116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5745,37 +5745,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611568</v>
+        <v>611661</v>
       </c>
       <c r="R52" t="n">
-        <v>7203718</v>
+        <v>7203604</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5802,19 +5802,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5829,22 +5819,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779309</v>
+        <v>125781628</v>
       </c>
       <c r="B53" t="n">
-        <v>80105</v>
+        <v>91207</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,21 +5842,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5876,13 +5866,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611679</v>
+        <v>611568</v>
       </c>
       <c r="R53" t="n">
-        <v>7203682</v>
+        <v>7203718</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5909,9 +5899,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5926,57 +5926,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779876</v>
+        <v>125779343</v>
       </c>
       <c r="B54" t="n">
-        <v>80112</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611661</v>
+        <v>611670</v>
       </c>
       <c r="R54" t="n">
-        <v>7203604</v>
+        <v>7203656</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6023,44 +6023,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779850</v>
+        <v>125779869</v>
       </c>
       <c r="B55" t="n">
-        <v>98366</v>
+        <v>80080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611637</v>
+        <v>611687</v>
       </c>
       <c r="R55" t="n">
-        <v>7203685</v>
+        <v>7203684</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6132,10 +6132,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125776365</v>
+        <v>125779842</v>
       </c>
       <c r="B56" t="n">
-        <v>98366</v>
+        <v>80109</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611567</v>
+        <v>611593</v>
       </c>
       <c r="R56" t="n">
-        <v>7203714</v>
+        <v>7203711</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,12 +6217,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6232,7 +6232,7 @@
         <v>125779320</v>
       </c>
       <c r="B57" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779881</v>
+        <v>125779867</v>
       </c>
       <c r="B58" t="n">
-        <v>91256</v>
+        <v>80080</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6337,21 +6337,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611650</v>
+        <v>611694</v>
       </c>
       <c r="R58" t="n">
-        <v>7203647</v>
+        <v>7203678</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6423,10 +6423,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779867</v>
+        <v>125781664</v>
       </c>
       <c r="B59" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6434,37 +6434,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611694</v>
+        <v>611539</v>
       </c>
       <c r="R59" t="n">
-        <v>7203678</v>
+        <v>7203643</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6491,9 +6491,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6508,22 +6518,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779869</v>
+        <v>125779344</v>
       </c>
       <c r="B60" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6531,34 +6541,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611687</v>
+        <v>611653</v>
       </c>
       <c r="R60" t="n">
-        <v>7203684</v>
+        <v>7203626</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6605,22 +6615,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125780620</v>
+        <v>125779881</v>
       </c>
       <c r="B61" t="n">
-        <v>57652</v>
+        <v>91260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6628,39 +6638,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611381</v>
+        <v>611650</v>
       </c>
       <c r="R61" t="n">
-        <v>7203809</v>
+        <v>7203647</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6687,12 +6692,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6707,22 +6712,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779344</v>
+        <v>125780620</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6730,34 +6735,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611653</v>
+        <v>611381</v>
       </c>
       <c r="R62" t="n">
-        <v>7203626</v>
+        <v>7203809</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6784,12 +6794,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6804,60 +6814,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125781664</v>
+        <v>125779850</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>98370</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611539</v>
+        <v>611637</v>
       </c>
       <c r="R63" t="n">
-        <v>7203643</v>
+        <v>7203685</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6884,19 +6894,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6911,22 +6911,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125779842</v>
+        <v>125776365</v>
       </c>
       <c r="B64" t="n">
-        <v>80105</v>
+        <v>98370</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6934,21 +6934,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611593</v>
+        <v>611567</v>
       </c>
       <c r="R64" t="n">
-        <v>7203711</v>
+        <v>7203714</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7008,22 +7008,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125781642</v>
+        <v>125779308</v>
       </c>
       <c r="B65" t="n">
-        <v>56844</v>
+        <v>80109</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7031,42 +7031,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611705</v>
+        <v>611684</v>
       </c>
       <c r="R65" t="n">
-        <v>7203676</v>
+        <v>7203690</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7093,19 +7088,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7120,60 +7105,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125779308</v>
+        <v>125781635</v>
       </c>
       <c r="B66" t="n">
-        <v>80105</v>
+        <v>57656</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611684</v>
+        <v>611535</v>
       </c>
       <c r="R66" t="n">
-        <v>7203690</v>
+        <v>7203644</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7200,9 +7190,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,22 +7217,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125781635</v>
+        <v>125780618</v>
       </c>
       <c r="B67" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7269,13 +7269,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611535</v>
+        <v>611378</v>
       </c>
       <c r="R67" t="n">
-        <v>7203644</v>
+        <v>7203714</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7299,22 +7299,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7334,45 +7324,45 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125780618</v>
+        <v>125781642</v>
       </c>
       <c r="B68" t="n">
-        <v>57652</v>
+        <v>56848</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7381,13 +7371,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611378</v>
+        <v>611705</v>
       </c>
       <c r="R68" t="n">
-        <v>7203714</v>
+        <v>7203676</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7411,12 +7401,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7436,52 +7436,52 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125776142</v>
+        <v>125779859</v>
       </c>
       <c r="B69" t="n">
-        <v>91812</v>
+        <v>80081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611684</v>
+        <v>611687</v>
       </c>
       <c r="R69" t="n">
-        <v>7203683</v>
+        <v>7203684</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7522,63 +7522,64 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125779859</v>
+        <v>125776142</v>
       </c>
       <c r="B70" t="n">
-        <v>80077</v>
+        <v>91816</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611687</v>
+        <v>611684</v>
       </c>
       <c r="R70" t="n">
-        <v>7203684</v>
+        <v>7203683</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7619,19 +7620,18 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7641,7 +7641,7 @@
         <v>125779339</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>125779333</v>
       </c>
       <c r="B72" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>125779880</v>
       </c>
       <c r="B73" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779771</v>
+        <v>125779340</v>
       </c>
       <c r="B74" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,34 +7940,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611686</v>
+        <v>611680</v>
       </c>
       <c r="R74" t="n">
-        <v>7203685</v>
+        <v>7203713</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,44 +8014,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779340</v>
+        <v>125779312</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>98370</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611680</v>
+        <v>611683</v>
       </c>
       <c r="R75" t="n">
-        <v>7203713</v>
+        <v>7203677</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8123,10 +8123,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779312</v>
+        <v>125779310</v>
       </c>
       <c r="B76" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611683</v>
+        <v>611700</v>
       </c>
       <c r="R76" t="n">
-        <v>7203677</v>
+        <v>7203703</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779310</v>
+        <v>125779771</v>
       </c>
       <c r="B77" t="n">
-        <v>98366</v>
+        <v>80080</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611700</v>
+        <v>611686</v>
       </c>
       <c r="R77" t="n">
-        <v>7203703</v>
+        <v>7203685</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8305,22 +8305,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125781627</v>
+        <v>125779875</v>
       </c>
       <c r="B78" t="n">
-        <v>91203</v>
+        <v>80116</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611526</v>
+        <v>611687</v>
       </c>
       <c r="R78" t="n">
-        <v>7203708</v>
+        <v>7203684</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,19 +8385,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8412,44 +8402,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779332</v>
+        <v>125779307</v>
       </c>
       <c r="B79" t="n">
-        <v>91256</v>
+        <v>80109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8459,10 +8449,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611525</v>
+        <v>611707</v>
       </c>
       <c r="R79" t="n">
-        <v>7203705</v>
+        <v>7203701</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8521,10 +8511,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779875</v>
+        <v>125781627</v>
       </c>
       <c r="B80" t="n">
-        <v>80112</v>
+        <v>91207</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8532,37 +8522,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611687</v>
+        <v>611526</v>
       </c>
       <c r="R80" t="n">
-        <v>7203684</v>
+        <v>7203708</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8589,9 +8579,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,44 +8606,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779307</v>
+        <v>125779332</v>
       </c>
       <c r="B81" t="n">
-        <v>80105</v>
+        <v>91260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611707</v>
+        <v>611525</v>
       </c>
       <c r="R81" t="n">
-        <v>7203701</v>
+        <v>7203705</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779313</v>
+        <v>125779847</v>
       </c>
       <c r="B82" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8746,14 +8746,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611663</v>
+        <v>611502</v>
       </c>
       <c r="R82" t="n">
-        <v>7203664</v>
+        <v>7203644</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8800,22 +8800,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779847</v>
+        <v>125779313</v>
       </c>
       <c r="B83" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,14 +8843,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611502</v>
+        <v>611663</v>
       </c>
       <c r="R83" t="n">
-        <v>7203644</v>
+        <v>7203664</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,22 +8897,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125781650</v>
+        <v>125776368</v>
       </c>
       <c r="B84" t="n">
-        <v>91607</v>
+        <v>91816</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8920,37 +8920,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1506</v>
+        <v>760</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611521</v>
+        <v>611705</v>
       </c>
       <c r="R84" t="n">
-        <v>7203626</v>
+        <v>7203679</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,19 +8977,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9004,62 +8994,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125781638</v>
+        <v>125781650</v>
       </c>
       <c r="B85" t="n">
-        <v>57652</v>
+        <v>91611</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611645</v>
+        <v>611521</v>
       </c>
       <c r="R85" t="n">
-        <v>7203676</v>
+        <v>7203626</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9091,7 +9076,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9101,7 +9086,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9128,53 +9113,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125779347</v>
+        <v>125779873</v>
       </c>
       <c r="B86" t="n">
-        <v>57652</v>
+        <v>80116</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611688</v>
+        <v>611693</v>
       </c>
       <c r="R86" t="n">
-        <v>7203713</v>
+        <v>7203707</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9209,11 +9186,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9226,60 +9198,65 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125776368</v>
+        <v>125781638</v>
       </c>
       <c r="B87" t="n">
-        <v>91812</v>
+        <v>57656</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611705</v>
+        <v>611645</v>
       </c>
       <c r="R87" t="n">
-        <v>7203679</v>
+        <v>7203676</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9306,9 +9283,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9323,57 +9310,65 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125779873</v>
+        <v>125779347</v>
       </c>
       <c r="B88" t="n">
-        <v>80112</v>
+        <v>57656</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611693</v>
+        <v>611688</v>
       </c>
       <c r="R88" t="n">
-        <v>7203707</v>
+        <v>7203713</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9408,6 +9403,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,12 +9420,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9435,7 +9435,7 @@
         <v>125779874</v>
       </c>
       <c r="B89" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>125779324</v>
       </c>
       <c r="B90" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779764</v>
+        <v>125779846</v>
       </c>
       <c r="B91" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611648</v>
+        <v>611717</v>
       </c>
       <c r="R91" t="n">
-        <v>7203687</v>
+        <v>7203689</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9711,22 +9711,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125779846</v>
+        <v>125779852</v>
       </c>
       <c r="B92" t="n">
-        <v>80105</v>
+        <v>98370</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9734,21 +9734,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9758,10 +9758,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611717</v>
+        <v>611711</v>
       </c>
       <c r="R92" t="n">
-        <v>7203689</v>
+        <v>7203685</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9823,7 +9823,7 @@
         <v>125776127</v>
       </c>
       <c r="B93" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9917,10 +9917,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125779852</v>
+        <v>125779764</v>
       </c>
       <c r="B94" t="n">
-        <v>98366</v>
+        <v>80109</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9928,21 +9928,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9952,10 +9952,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611711</v>
+        <v>611648</v>
       </c>
       <c r="R94" t="n">
-        <v>7203685</v>
+        <v>7203687</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10002,22 +10002,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779885</v>
+        <v>125779302</v>
       </c>
       <c r="B95" t="n">
-        <v>78973</v>
+        <v>91242</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,34 +10025,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611661</v>
+        <v>611618</v>
       </c>
       <c r="R95" t="n">
-        <v>7203604</v>
+        <v>7203674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10099,22 +10099,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779349</v>
+        <v>125779885</v>
       </c>
       <c r="B96" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10122,42 +10122,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611652</v>
+        <v>611661</v>
       </c>
       <c r="R96" t="n">
-        <v>7203627</v>
+        <v>7203604</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10192,11 +10184,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -10209,57 +10196,65 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779314</v>
+        <v>125779349</v>
       </c>
       <c r="B97" t="n">
-        <v>98366</v>
+        <v>57656</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611663</v>
+        <v>611652</v>
       </c>
       <c r="R97" t="n">
-        <v>7203673</v>
+        <v>7203627</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10292,6 +10287,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10318,32 +10318,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779302</v>
+        <v>125779314</v>
       </c>
       <c r="B98" t="n">
-        <v>91238</v>
+        <v>98370</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10353,10 +10353,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611618</v>
+        <v>611663</v>
       </c>
       <c r="R98" t="n">
-        <v>7203674</v>
+        <v>7203673</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10418,7 +10418,7 @@
         <v>125779299</v>
       </c>
       <c r="B99" t="n">
-        <v>75068</v>
+        <v>75072</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10512,45 +10512,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779772</v>
+        <v>125779329</v>
       </c>
       <c r="B100" t="n">
-        <v>80112</v>
+        <v>80080</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611680</v>
+        <v>611623</v>
       </c>
       <c r="R100" t="n">
-        <v>7203679</v>
+        <v>7203677</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,22 +10597,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779851</v>
+        <v>125779772</v>
       </c>
       <c r="B101" t="n">
-        <v>98366</v>
+        <v>80116</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10620,21 +10620,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611690</v>
+        <v>611680</v>
       </c>
       <c r="R101" t="n">
-        <v>7203710</v>
+        <v>7203679</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,57 +10694,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779329</v>
+        <v>125779851</v>
       </c>
       <c r="B102" t="n">
-        <v>80076</v>
+        <v>98370</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611623</v>
+        <v>611690</v>
       </c>
       <c r="R102" t="n">
-        <v>7203677</v>
+        <v>7203710</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>125803917</v>
       </c>
       <c r="B104" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>125803940</v>
       </c>
       <c r="B105" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>125803950</v>
       </c>
       <c r="B106" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>125803668</v>
       </c>
       <c r="B107" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>125803829</v>
       </c>
       <c r="B109" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>125804619</v>
       </c>
       <c r="B110" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>125803771</v>
       </c>
       <c r="B111" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>125779762</v>
       </c>
       <c r="B113" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -3112,48 +3112,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125781660</v>
+        <v>125779886</v>
       </c>
       <c r="B26" t="n">
-        <v>91256</v>
+        <v>91816</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611570</v>
+        <v>611704</v>
       </c>
       <c r="R26" t="n">
-        <v>7203708</v>
+        <v>7203679</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3180,19 +3180,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,12 +3197,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3316,48 +3306,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125779886</v>
+        <v>125781660</v>
       </c>
       <c r="B28" t="n">
-        <v>91816</v>
+        <v>91256</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>760</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611704</v>
+        <v>611570</v>
       </c>
       <c r="R28" t="n">
-        <v>7203679</v>
+        <v>7203708</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3384,9 +3374,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3401,57 +3401,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125776147</v>
+        <v>125779763</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611642</v>
+        <v>611644</v>
       </c>
       <c r="R29" t="n">
-        <v>7203689</v>
+        <v>7203694</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,57 +3498,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125779767</v>
+        <v>125776147</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611673</v>
+        <v>611642</v>
       </c>
       <c r="R30" t="n">
-        <v>7203670</v>
+        <v>7203689</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3595,57 +3595,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125779763</v>
+        <v>125780614</v>
       </c>
       <c r="B31" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611644</v>
+        <v>611292</v>
       </c>
       <c r="R31" t="n">
-        <v>7203694</v>
+        <v>7203687</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3672,12 +3677,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3692,62 +3697,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125780614</v>
+        <v>125779767</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>98370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611292</v>
+        <v>611673</v>
       </c>
       <c r="R32" t="n">
-        <v>7203687</v>
+        <v>7203670</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,12 +3794,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5116,45 +5116,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125776134</v>
+        <v>125779346</v>
       </c>
       <c r="B46" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>611647</v>
+        <v>611666</v>
       </c>
       <c r="R46" t="n">
-        <v>7203694</v>
+        <v>7203652</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5189,6 +5197,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5201,60 +5214,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125781648</v>
+        <v>125776134</v>
       </c>
       <c r="B47" t="n">
-        <v>80081</v>
+        <v>80109</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>611683</v>
+        <v>611647</v>
       </c>
       <c r="R47" t="n">
-        <v>7203710</v>
+        <v>7203694</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5281,19 +5294,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5308,22 +5311,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125779346</v>
+        <v>125781648</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5331,45 +5334,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>611666</v>
+        <v>611683</v>
       </c>
       <c r="R48" t="n">
-        <v>7203652</v>
+        <v>7203710</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5396,14 +5391,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5418,12 +5418,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7020,48 +7020,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125779308</v>
+        <v>125781635</v>
       </c>
       <c r="B65" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611684</v>
+        <v>611535</v>
       </c>
       <c r="R65" t="n">
-        <v>7203690</v>
+        <v>7203644</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7088,9 +7093,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7105,19 +7120,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125781635</v>
+        <v>125780618</v>
       </c>
       <c r="B66" t="n">
         <v>57656</v>
@@ -7157,13 +7172,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611535</v>
+        <v>611378</v>
       </c>
       <c r="R66" t="n">
-        <v>7203644</v>
+        <v>7203714</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7187,22 +7202,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7222,45 +7227,45 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125780618</v>
+        <v>125781642</v>
       </c>
       <c r="B67" t="n">
-        <v>57656</v>
+        <v>56848</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7269,13 +7274,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611378</v>
+        <v>611705</v>
       </c>
       <c r="R67" t="n">
-        <v>7203714</v>
+        <v>7203676</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7299,12 +7304,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7324,17 +7339,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125781642</v>
+        <v>125779308</v>
       </c>
       <c r="B68" t="n">
-        <v>56848</v>
+        <v>80109</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7342,42 +7357,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611705</v>
+        <v>611684</v>
       </c>
       <c r="R68" t="n">
-        <v>7203676</v>
+        <v>7203690</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7404,19 +7414,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7431,12 +7431,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7832,45 +7832,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779880</v>
+        <v>125779312</v>
       </c>
       <c r="B73" t="n">
-        <v>91260</v>
+        <v>98370</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611743</v>
+        <v>611683</v>
       </c>
       <c r="R73" t="n">
-        <v>7203706</v>
+        <v>7203677</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7917,44 +7917,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779340</v>
+        <v>125779310</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>98370</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7964,10 +7964,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611680</v>
+        <v>611700</v>
       </c>
       <c r="R74" t="n">
-        <v>7203713</v>
+        <v>7203703</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8026,45 +8026,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779312</v>
+        <v>125779771</v>
       </c>
       <c r="B75" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611683</v>
+        <v>611686</v>
       </c>
       <c r="R75" t="n">
-        <v>7203677</v>
+        <v>7203685</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,57 +8111,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779310</v>
+        <v>125779880</v>
       </c>
       <c r="B76" t="n">
-        <v>98370</v>
+        <v>91260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611700</v>
+        <v>611743</v>
       </c>
       <c r="R76" t="n">
-        <v>7203703</v>
+        <v>7203706</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8208,22 +8208,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779771</v>
+        <v>125779340</v>
       </c>
       <c r="B77" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8231,34 +8231,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611686</v>
+        <v>611680</v>
       </c>
       <c r="R77" t="n">
-        <v>7203685</v>
+        <v>7203713</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8305,22 +8305,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125779875</v>
+        <v>125781627</v>
       </c>
       <c r="B78" t="n">
-        <v>80116</v>
+        <v>91207</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611687</v>
+        <v>611526</v>
       </c>
       <c r="R78" t="n">
-        <v>7203684</v>
+        <v>7203708</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,9 +8385,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8402,44 +8412,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779307</v>
+        <v>125779332</v>
       </c>
       <c r="B79" t="n">
-        <v>80109</v>
+        <v>91260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8449,10 +8459,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611707</v>
+        <v>611525</v>
       </c>
       <c r="R79" t="n">
-        <v>7203701</v>
+        <v>7203705</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8511,10 +8521,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125781627</v>
+        <v>125779875</v>
       </c>
       <c r="B80" t="n">
-        <v>91207</v>
+        <v>80116</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8522,37 +8532,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611526</v>
+        <v>611687</v>
       </c>
       <c r="R80" t="n">
-        <v>7203708</v>
+        <v>7203684</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8579,19 +8589,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,44 +8606,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779332</v>
+        <v>125779307</v>
       </c>
       <c r="B81" t="n">
-        <v>91260</v>
+        <v>80109</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611525</v>
+        <v>611707</v>
       </c>
       <c r="R81" t="n">
-        <v>7203705</v>
+        <v>7203701</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779299</v>
+        <v>125779329</v>
       </c>
       <c r="B99" t="n">
-        <v>75072</v>
+        <v>80080</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10426,21 +10426,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611561</v>
+        <v>611623</v>
       </c>
       <c r="R99" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10512,45 +10512,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779329</v>
+        <v>125779772</v>
       </c>
       <c r="B100" t="n">
-        <v>80080</v>
+        <v>80116</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611623</v>
+        <v>611680</v>
       </c>
       <c r="R100" t="n">
-        <v>7203677</v>
+        <v>7203679</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,57 +10597,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779772</v>
+        <v>125779299</v>
       </c>
       <c r="B101" t="n">
-        <v>80116</v>
+        <v>75072</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611680</v>
+        <v>611561</v>
       </c>
       <c r="R101" t="n">
-        <v>7203679</v>
+        <v>7203692</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10694,12 +10694,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125781649</v>
+        <v>125781662</v>
       </c>
       <c r="B6" t="n">
-        <v>91538</v>
+        <v>91260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611536</v>
+        <v>611570</v>
       </c>
       <c r="R6" t="n">
-        <v>7203694</v>
+        <v>7203707</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125781662</v>
+        <v>125781649</v>
       </c>
       <c r="B7" t="n">
-        <v>91260</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611570</v>
+        <v>611536</v>
       </c>
       <c r="R7" t="n">
-        <v>7203707</v>
+        <v>7203694</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1601,32 +1601,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125779322</v>
+        <v>125781663</v>
       </c>
       <c r="B11" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611700</v>
+        <v>611570</v>
       </c>
       <c r="R11" t="n">
-        <v>7203701</v>
+        <v>7203700</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,9 +1669,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,22 +1696,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125779769</v>
+        <v>125776139</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1709,34 +1719,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611696</v>
+        <v>611678</v>
       </c>
       <c r="R12" t="n">
-        <v>7203681</v>
+        <v>7203688</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1783,19 +1793,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779323</v>
+        <v>125779322</v>
       </c>
       <c r="B13" t="n">
         <v>80108</v>
@@ -1830,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611667</v>
+        <v>611700</v>
       </c>
       <c r="R13" t="n">
-        <v>7203673</v>
+        <v>7203701</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,10 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125781637</v>
+        <v>125779769</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1903,42 +1913,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611631</v>
+        <v>611696</v>
       </c>
       <c r="R14" t="n">
-        <v>7203695</v>
+        <v>7203681</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,19 +1970,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1992,62 +1987,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125780615</v>
+        <v>125779323</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>80108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611292</v>
+        <v>611667</v>
       </c>
       <c r="R15" t="n">
-        <v>7203703</v>
+        <v>7203673</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2074,12 +2064,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2094,22 +2084,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125781663</v>
+        <v>125781637</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2117,34 +2107,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611570</v>
+        <v>611631</v>
       </c>
       <c r="R16" t="n">
-        <v>7203700</v>
+        <v>7203695</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,7 +2171,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2186,7 +2181,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2206,17 +2201,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125776139</v>
+        <v>125780615</v>
       </c>
       <c r="B17" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2224,34 +2219,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611678</v>
+        <v>611292</v>
       </c>
       <c r="R17" t="n">
-        <v>7203688</v>
+        <v>7203703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>125776366</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>125779311</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2614,32 +2614,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125780607</v>
+        <v>125780622</v>
       </c>
       <c r="B21" t="n">
-        <v>80081</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611445</v>
+        <v>611490</v>
       </c>
       <c r="R21" t="n">
-        <v>7203816</v>
+        <v>7203838</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779317</v>
+        <v>125780607</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,42 +2916,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611723</v>
+        <v>611445</v>
       </c>
       <c r="R24" t="n">
-        <v>7203703</v>
+        <v>7203816</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2978,17 +2970,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3003,57 +2990,65 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125780622</v>
+        <v>125779317</v>
       </c>
       <c r="B25" t="n">
-        <v>98349</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>611490</v>
+        <v>611723</v>
       </c>
       <c r="R25" t="n">
-        <v>7203838</v>
+        <v>7203703</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3080,12 +3075,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,44 +3100,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125779886</v>
+        <v>125779767</v>
       </c>
       <c r="B26" t="n">
-        <v>91816</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>221952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611704</v>
+        <v>611673</v>
       </c>
       <c r="R26" t="n">
-        <v>7203679</v>
+        <v>7203670</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3197,60 +3197,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125779838</v>
+        <v>125781660</v>
       </c>
       <c r="B27" t="n">
-        <v>80109</v>
+        <v>91256</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611513</v>
+        <v>611570</v>
       </c>
       <c r="R27" t="n">
-        <v>7203698</v>
+        <v>7203708</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3277,9 +3277,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3294,60 +3304,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125781660</v>
+        <v>125779886</v>
       </c>
       <c r="B28" t="n">
-        <v>91256</v>
+        <v>91816</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611570</v>
+        <v>611704</v>
       </c>
       <c r="R28" t="n">
-        <v>7203708</v>
+        <v>7203679</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3374,19 +3384,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3401,57 +3401,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125779763</v>
+        <v>125776147</v>
       </c>
       <c r="B29" t="n">
-        <v>80109</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611644</v>
+        <v>611642</v>
       </c>
       <c r="R29" t="n">
-        <v>7203694</v>
+        <v>7203689</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,57 +3498,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125776147</v>
+        <v>125779763</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611642</v>
+        <v>611644</v>
       </c>
       <c r="R30" t="n">
-        <v>7203689</v>
+        <v>7203694</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3595,62 +3595,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125780614</v>
+        <v>125779838</v>
       </c>
       <c r="B31" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611292</v>
+        <v>611513</v>
       </c>
       <c r="R31" t="n">
-        <v>7203687</v>
+        <v>7203698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3677,12 +3672,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,57 +3692,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125779767</v>
+        <v>125780614</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611673</v>
+        <v>611292</v>
       </c>
       <c r="R32" t="n">
-        <v>7203670</v>
+        <v>7203687</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,60 +3794,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125781666</v>
+        <v>125779848</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611652</v>
+        <v>611545</v>
       </c>
       <c r="R33" t="n">
-        <v>7203680</v>
+        <v>7203710</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,19 +3874,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780608</v>
+        <v>125781666</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3948,13 +3938,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611445</v>
+        <v>611652</v>
       </c>
       <c r="R34" t="n">
-        <v>7203816</v>
+        <v>7203680</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3978,12 +3968,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125780606</v>
+        <v>125779884</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611311</v>
+        <v>611666</v>
       </c>
       <c r="R36" t="n">
-        <v>7203689</v>
+        <v>7203678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,57 +4192,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779848</v>
+        <v>125780608</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611545</v>
+        <v>611445</v>
       </c>
       <c r="R37" t="n">
-        <v>7203710</v>
+        <v>7203816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,22 +4289,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779884</v>
+        <v>125780606</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4312,34 +4312,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611666</v>
+        <v>611311</v>
       </c>
       <c r="R38" t="n">
-        <v>7203678</v>
+        <v>7203689</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,57 +4386,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779773</v>
+        <v>125779337</v>
       </c>
       <c r="B39" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611662</v>
+        <v>611615</v>
       </c>
       <c r="R39" t="n">
-        <v>7203612</v>
+        <v>7203678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4483,57 +4483,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779337</v>
+        <v>125779844</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611615</v>
+        <v>611644</v>
       </c>
       <c r="R40" t="n">
-        <v>7203678</v>
+        <v>7203690</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4580,65 +4580,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779319</v>
+        <v>125779773</v>
       </c>
       <c r="B41" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611663</v>
+        <v>611662</v>
       </c>
       <c r="R41" t="n">
-        <v>7203613</v>
+        <v>7203612</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4673,11 +4665,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4690,19 +4677,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779316</v>
+        <v>125779319</v>
       </c>
       <c r="B42" t="n">
         <v>57656</v>
@@ -4745,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611507</v>
+        <v>611663</v>
       </c>
       <c r="R42" t="n">
-        <v>7203685</v>
+        <v>7203613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4785,7 +4772,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4812,7 +4799,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779318</v>
+        <v>125779316</v>
       </c>
       <c r="B43" t="n">
         <v>57656</v>
@@ -4855,10 +4842,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611725</v>
+        <v>611507</v>
       </c>
       <c r="R43" t="n">
-        <v>7203707</v>
+        <v>7203685</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,45 +4909,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779844</v>
+        <v>125779318</v>
       </c>
       <c r="B44" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611644</v>
+        <v>611725</v>
       </c>
       <c r="R44" t="n">
-        <v>7203690</v>
+        <v>7203707</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,6 +4990,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5007,12 +5007,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5022,7 +5022,7 @@
         <v>125779853</v>
       </c>
       <c r="B45" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5116,10 +5116,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125779346</v>
+        <v>125781648</v>
       </c>
       <c r="B46" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5127,45 +5127,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>611666</v>
+        <v>611683</v>
       </c>
       <c r="R46" t="n">
-        <v>7203652</v>
+        <v>7203710</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5192,14 +5184,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5214,12 +5211,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5323,10 +5320,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125781648</v>
+        <v>125779346</v>
       </c>
       <c r="B48" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,37 +5331,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>611683</v>
+        <v>611666</v>
       </c>
       <c r="R48" t="n">
-        <v>7203710</v>
+        <v>7203652</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5391,19 +5396,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:50</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:50</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5418,68 +5418,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125779863</v>
+        <v>125781628</v>
       </c>
       <c r="B49" t="n">
-        <v>57656</v>
+        <v>91207</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>611623</v>
+        <v>611568</v>
       </c>
       <c r="R49" t="n">
-        <v>7203692</v>
+        <v>7203718</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5506,14 +5498,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5528,12 +5525,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5637,32 +5634,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779309</v>
+        <v>125779343</v>
       </c>
       <c r="B51" t="n">
-        <v>80109</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5672,10 +5669,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611679</v>
+        <v>611670</v>
       </c>
       <c r="R51" t="n">
-        <v>7203682</v>
+        <v>7203656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5831,48 +5828,56 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125781628</v>
+        <v>125779863</v>
       </c>
       <c r="B53" t="n">
-        <v>91207</v>
+        <v>57656</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611568</v>
+        <v>611623</v>
       </c>
       <c r="R53" t="n">
-        <v>7203718</v>
+        <v>7203692</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5899,19 +5904,14 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>11:19</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5926,44 +5926,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779343</v>
+        <v>125779309</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611670</v>
+        <v>611679</v>
       </c>
       <c r="R54" t="n">
-        <v>7203656</v>
+        <v>7203682</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6035,45 +6035,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779869</v>
+        <v>125779320</v>
       </c>
       <c r="B55" t="n">
-        <v>80080</v>
+        <v>91611</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611687</v>
+        <v>611543</v>
       </c>
       <c r="R55" t="n">
-        <v>7203684</v>
+        <v>7203697</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6120,60 +6120,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125779842</v>
+        <v>125781664</v>
       </c>
       <c r="B56" t="n">
-        <v>80109</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611593</v>
+        <v>611539</v>
       </c>
       <c r="R56" t="n">
-        <v>7203711</v>
+        <v>7203643</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6200,9 +6200,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6217,44 +6227,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779320</v>
+        <v>125779344</v>
       </c>
       <c r="B57" t="n">
-        <v>91611</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6264,10 +6274,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611543</v>
+        <v>611653</v>
       </c>
       <c r="R57" t="n">
-        <v>7203697</v>
+        <v>7203626</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6326,10 +6336,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779867</v>
+        <v>125779881</v>
       </c>
       <c r="B58" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6337,21 +6347,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6361,10 +6371,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611694</v>
+        <v>611650</v>
       </c>
       <c r="R58" t="n">
-        <v>7203678</v>
+        <v>7203647</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6423,10 +6433,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125781664</v>
+        <v>125779869</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6434,37 +6444,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611539</v>
+        <v>611687</v>
       </c>
       <c r="R59" t="n">
-        <v>7203643</v>
+        <v>7203684</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6491,19 +6501,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6518,22 +6518,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779344</v>
+        <v>125779867</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6541,34 +6541,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611653</v>
+        <v>611694</v>
       </c>
       <c r="R60" t="n">
-        <v>7203626</v>
+        <v>7203678</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6615,44 +6615,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779881</v>
+        <v>125779842</v>
       </c>
       <c r="B61" t="n">
-        <v>91260</v>
+        <v>80109</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611650</v>
+        <v>611593</v>
       </c>
       <c r="R61" t="n">
-        <v>7203647</v>
+        <v>7203711</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6829,7 +6829,7 @@
         <v>125779850</v>
       </c>
       <c r="B63" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>125776365</v>
       </c>
       <c r="B64" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7020,53 +7020,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125781635</v>
+        <v>125779308</v>
       </c>
       <c r="B65" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>611535</v>
+        <v>611684</v>
       </c>
       <c r="R65" t="n">
-        <v>7203644</v>
+        <v>7203690</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7093,19 +7088,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7120,19 +7105,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125780618</v>
+        <v>125781635</v>
       </c>
       <c r="B66" t="n">
         <v>57656</v>
@@ -7172,13 +7157,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>611378</v>
+        <v>611535</v>
       </c>
       <c r="R66" t="n">
-        <v>7203714</v>
+        <v>7203644</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7202,12 +7187,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7227,45 +7222,45 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125781642</v>
+        <v>125780618</v>
       </c>
       <c r="B67" t="n">
-        <v>56848</v>
+        <v>57656</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7274,13 +7269,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>611705</v>
+        <v>611378</v>
       </c>
       <c r="R67" t="n">
-        <v>7203676</v>
+        <v>7203714</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7304,22 +7299,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7339,17 +7324,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125779308</v>
+        <v>125781642</v>
       </c>
       <c r="B68" t="n">
-        <v>80109</v>
+        <v>56848</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7357,37 +7342,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>611684</v>
+        <v>611705</v>
       </c>
       <c r="R68" t="n">
-        <v>7203690</v>
+        <v>7203676</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7414,9 +7404,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7431,57 +7431,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125779859</v>
+        <v>125776142</v>
       </c>
       <c r="B69" t="n">
-        <v>80081</v>
+        <v>91816</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611687</v>
+        <v>611684</v>
       </c>
       <c r="R69" t="n">
-        <v>7203684</v>
+        <v>7203683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7522,64 +7522,63 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125776142</v>
+        <v>125779339</v>
       </c>
       <c r="B70" t="n">
-        <v>91816</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611684</v>
+        <v>611640</v>
       </c>
       <c r="R70" t="n">
-        <v>7203683</v>
+        <v>7203677</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7626,22 +7625,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125779339</v>
+        <v>125779859</v>
       </c>
       <c r="B71" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7649,34 +7648,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>611640</v>
+        <v>611687</v>
       </c>
       <c r="R71" t="n">
-        <v>7203677</v>
+        <v>7203684</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,18 +7716,19 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7835,7 +7835,7 @@
         <v>125779312</v>
       </c>
       <c r="B73" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>125779310</v>
       </c>
       <c r="B74" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779771</v>
+        <v>125779880</v>
       </c>
       <c r="B75" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,21 +8037,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611686</v>
+        <v>611743</v>
       </c>
       <c r="R75" t="n">
-        <v>7203685</v>
+        <v>7203706</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,22 +8111,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779880</v>
+        <v>125779340</v>
       </c>
       <c r="B76" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8134,34 +8134,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611743</v>
+        <v>611680</v>
       </c>
       <c r="R76" t="n">
-        <v>7203706</v>
+        <v>7203713</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8208,22 +8208,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779340</v>
+        <v>125779771</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8231,34 +8231,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611680</v>
+        <v>611686</v>
       </c>
       <c r="R77" t="n">
-        <v>7203713</v>
+        <v>7203685</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8305,22 +8305,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125781627</v>
+        <v>125779875</v>
       </c>
       <c r="B78" t="n">
-        <v>91207</v>
+        <v>80116</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611526</v>
+        <v>611687</v>
       </c>
       <c r="R78" t="n">
-        <v>7203708</v>
+        <v>7203684</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,19 +8385,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8412,44 +8402,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779332</v>
+        <v>125779307</v>
       </c>
       <c r="B79" t="n">
-        <v>91260</v>
+        <v>80109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8459,10 +8449,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611525</v>
+        <v>611707</v>
       </c>
       <c r="R79" t="n">
-        <v>7203705</v>
+        <v>7203701</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8521,10 +8511,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125779875</v>
+        <v>125781627</v>
       </c>
       <c r="B80" t="n">
-        <v>80116</v>
+        <v>91207</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8532,37 +8522,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611687</v>
+        <v>611526</v>
       </c>
       <c r="R80" t="n">
-        <v>7203684</v>
+        <v>7203708</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8589,9 +8579,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,44 +8606,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125779307</v>
+        <v>125779332</v>
       </c>
       <c r="B81" t="n">
-        <v>80109</v>
+        <v>91260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>611707</v>
+        <v>611525</v>
       </c>
       <c r="R81" t="n">
-        <v>7203701</v>
+        <v>7203705</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125779847</v>
+        <v>125779313</v>
       </c>
       <c r="B82" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8746,14 +8746,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>611502</v>
+        <v>611663</v>
       </c>
       <c r="R82" t="n">
-        <v>7203644</v>
+        <v>7203664</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8800,22 +8800,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125779313</v>
+        <v>125779847</v>
       </c>
       <c r="B83" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8843,14 +8843,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>611663</v>
+        <v>611502</v>
       </c>
       <c r="R83" t="n">
-        <v>7203664</v>
+        <v>7203644</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8897,22 +8897,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125776368</v>
+        <v>125781650</v>
       </c>
       <c r="B84" t="n">
-        <v>91816</v>
+        <v>91611</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8920,37 +8920,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>760</v>
+        <v>1506</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611705</v>
+        <v>611521</v>
       </c>
       <c r="R84" t="n">
-        <v>7203679</v>
+        <v>7203626</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,9 +8977,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8994,22 +9004,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125781650</v>
+        <v>125776368</v>
       </c>
       <c r="B85" t="n">
-        <v>91611</v>
+        <v>91816</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9017,37 +9027,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1506</v>
+        <v>760</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611521</v>
+        <v>611705</v>
       </c>
       <c r="R85" t="n">
-        <v>7203626</v>
+        <v>7203679</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9074,19 +9084,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9101,12 +9101,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9315,7 +9315,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779846</v>
+        <v>125779852</v>
       </c>
       <c r="B91" t="n">
-        <v>80109</v>
+        <v>98373</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,21 +9637,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611717</v>
+        <v>611711</v>
       </c>
       <c r="R91" t="n">
-        <v>7203689</v>
+        <v>7203685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9723,10 +9723,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125779852</v>
+        <v>125776127</v>
       </c>
       <c r="B92" t="n">
-        <v>98370</v>
+        <v>80116</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9734,31 +9734,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611711</v>
+        <v>611681</v>
       </c>
       <c r="R92" t="n">
         <v>7203685</v>
@@ -9808,22 +9808,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125776127</v>
+        <v>125779764</v>
       </c>
       <c r="B93" t="n">
-        <v>80116</v>
+        <v>80109</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611681</v>
+        <v>611648</v>
       </c>
       <c r="R93" t="n">
-        <v>7203685</v>
+        <v>7203687</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,19 +9905,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125779764</v>
+        <v>125779846</v>
       </c>
       <c r="B94" t="n">
         <v>80109</v>
@@ -9952,10 +9952,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611648</v>
+        <v>611717</v>
       </c>
       <c r="R94" t="n">
-        <v>7203687</v>
+        <v>7203689</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10002,12 +10002,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10321,7 +10321,7 @@
         <v>125779314</v>
       </c>
       <c r="B98" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10415,45 +10415,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779329</v>
+        <v>125779851</v>
       </c>
       <c r="B99" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611623</v>
+        <v>611690</v>
       </c>
       <c r="R99" t="n">
-        <v>7203677</v>
+        <v>7203710</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10500,57 +10500,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779772</v>
+        <v>125779299</v>
       </c>
       <c r="B100" t="n">
-        <v>80116</v>
+        <v>75072</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611680</v>
+        <v>611561</v>
       </c>
       <c r="R100" t="n">
-        <v>7203679</v>
+        <v>7203692</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,22 +10597,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779299</v>
+        <v>125779329</v>
       </c>
       <c r="B101" t="n">
-        <v>75072</v>
+        <v>80080</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10620,21 +10620,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611561</v>
+        <v>611623</v>
       </c>
       <c r="R101" t="n">
-        <v>7203692</v>
+        <v>7203677</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10706,10 +10706,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779851</v>
+        <v>125779772</v>
       </c>
       <c r="B102" t="n">
-        <v>98370</v>
+        <v>80116</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10717,21 +10717,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611690</v>
+        <v>611680</v>
       </c>
       <c r="R102" t="n">
-        <v>7203710</v>
+        <v>7203679</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10806,7 +10806,7 @@
         <v>125803769</v>
       </c>
       <c r="B103" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>125803668</v>
       </c>
       <c r="B107" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>125803691</v>
       </c>
       <c r="B108" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>125803886</v>
       </c>
       <c r="B112" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1601,32 +1601,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125781663</v>
+        <v>125779322</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>80108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611570</v>
+        <v>611700</v>
       </c>
       <c r="R11" t="n">
-        <v>7203700</v>
+        <v>7203701</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,19 +1669,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,22 +1686,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125776139</v>
+        <v>125779769</v>
       </c>
       <c r="B12" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1719,34 +1709,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611678</v>
+        <v>611696</v>
       </c>
       <c r="R12" t="n">
-        <v>7203688</v>
+        <v>7203681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,19 +1783,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779322</v>
+        <v>125779323</v>
       </c>
       <c r="B13" t="n">
         <v>80108</v>
@@ -1840,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611700</v>
+        <v>611667</v>
       </c>
       <c r="R13" t="n">
-        <v>7203701</v>
+        <v>7203673</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,10 +1892,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125779769</v>
+        <v>125781637</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1913,37 +1903,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611696</v>
+        <v>611631</v>
       </c>
       <c r="R14" t="n">
-        <v>7203681</v>
+        <v>7203695</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1970,9 +1965,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1987,57 +1992,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125779323</v>
+        <v>125780615</v>
       </c>
       <c r="B15" t="n">
-        <v>80108</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611667</v>
+        <v>611292</v>
       </c>
       <c r="R15" t="n">
-        <v>7203673</v>
+        <v>7203703</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,12 +2074,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2084,22 +2094,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125781637</v>
+        <v>125781663</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,39 +2117,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611631</v>
+        <v>611570</v>
       </c>
       <c r="R16" t="n">
-        <v>7203695</v>
+        <v>7203700</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2171,7 +2176,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2181,7 +2186,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2208,10 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125780615</v>
+        <v>125776139</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>80081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2219,39 +2224,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611292</v>
+        <v>611678</v>
       </c>
       <c r="R17" t="n">
-        <v>7203703</v>
+        <v>7203688</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3806,48 +3806,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779848</v>
+        <v>125781666</v>
       </c>
       <c r="B33" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611545</v>
+        <v>611652</v>
       </c>
       <c r="R33" t="n">
-        <v>7203710</v>
+        <v>7203680</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,9 +3874,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,22 +3901,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125781666</v>
+        <v>125779834</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,37 +3924,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611652</v>
+        <v>611547</v>
       </c>
       <c r="R34" t="n">
-        <v>7203680</v>
+        <v>7203635</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3971,19 +3981,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,22 +3998,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125779834</v>
+        <v>125779884</v>
       </c>
       <c r="B35" t="n">
-        <v>75072</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611547</v>
+        <v>611666</v>
       </c>
       <c r="R35" t="n">
-        <v>7203635</v>
+        <v>7203678</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4107,10 +4107,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125779884</v>
+        <v>125780608</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611666</v>
+        <v>611445</v>
       </c>
       <c r="R36" t="n">
-        <v>7203678</v>
+        <v>7203816</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4172,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,19 +4192,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125780608</v>
+        <v>125780606</v>
       </c>
       <c r="B37" t="n">
         <v>80080</v>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611445</v>
+        <v>611311</v>
       </c>
       <c r="R37" t="n">
-        <v>7203816</v>
+        <v>7203689</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,45 +4301,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125780606</v>
+        <v>125779848</v>
       </c>
       <c r="B38" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611311</v>
+        <v>611545</v>
       </c>
       <c r="R38" t="n">
-        <v>7203689</v>
+        <v>7203710</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4386,22 +4386,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779337</v>
+        <v>125779319</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,34 +4409,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611615</v>
+        <v>611663</v>
       </c>
       <c r="R39" t="n">
-        <v>7203678</v>
+        <v>7203613</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,6 +4477,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4495,45 +4508,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779844</v>
+        <v>125779316</v>
       </c>
       <c r="B40" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611644</v>
+        <v>611507</v>
       </c>
       <c r="R40" t="n">
-        <v>7203690</v>
+        <v>7203685</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4568,6 +4589,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4580,57 +4606,65 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779773</v>
+        <v>125779318</v>
       </c>
       <c r="B41" t="n">
-        <v>80116</v>
+        <v>57656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611662</v>
+        <v>611725</v>
       </c>
       <c r="R41" t="n">
-        <v>7203612</v>
+        <v>7203707</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4665,6 +4699,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4677,22 +4716,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779319</v>
+        <v>125779337</v>
       </c>
       <c r="B42" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,42 +4739,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611663</v>
+        <v>611615</v>
       </c>
       <c r="R42" t="n">
-        <v>7203613</v>
+        <v>7203678</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,11 +4799,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4799,53 +4825,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779316</v>
+        <v>125779844</v>
       </c>
       <c r="B43" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611507</v>
+        <v>611644</v>
       </c>
       <c r="R43" t="n">
-        <v>7203685</v>
+        <v>7203690</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4880,11 +4898,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4897,65 +4910,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779318</v>
+        <v>125779773</v>
       </c>
       <c r="B44" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611725</v>
+        <v>611662</v>
       </c>
       <c r="R44" t="n">
-        <v>7203707</v>
+        <v>7203612</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4990,11 +4995,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5007,12 +5007,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6035,45 +6035,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779320</v>
+        <v>125780620</v>
       </c>
       <c r="B55" t="n">
-        <v>91611</v>
+        <v>57656</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611543</v>
+        <v>611381</v>
       </c>
       <c r="R55" t="n">
-        <v>7203697</v>
+        <v>7203809</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6100,12 +6105,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6120,60 +6125,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125781664</v>
+        <v>125779850</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611539</v>
+        <v>611637</v>
       </c>
       <c r="R56" t="n">
-        <v>7203643</v>
+        <v>7203685</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6200,19 +6205,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,57 +6222,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779344</v>
+        <v>125776365</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611653</v>
+        <v>611567</v>
       </c>
       <c r="R57" t="n">
-        <v>7203626</v>
+        <v>7203714</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6324,57 +6319,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779881</v>
+        <v>125779320</v>
       </c>
       <c r="B58" t="n">
-        <v>91260</v>
+        <v>91611</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611650</v>
+        <v>611543</v>
       </c>
       <c r="R58" t="n">
-        <v>7203647</v>
+        <v>7203697</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6421,22 +6416,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779869</v>
+        <v>125781664</v>
       </c>
       <c r="B59" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6444,37 +6439,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611687</v>
+        <v>611539</v>
       </c>
       <c r="R59" t="n">
-        <v>7203684</v>
+        <v>7203643</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6501,9 +6496,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6518,22 +6523,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779867</v>
+        <v>125779344</v>
       </c>
       <c r="B60" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6541,34 +6546,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611694</v>
+        <v>611653</v>
       </c>
       <c r="R60" t="n">
-        <v>7203678</v>
+        <v>7203626</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6615,44 +6620,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779842</v>
+        <v>125779881</v>
       </c>
       <c r="B61" t="n">
-        <v>80109</v>
+        <v>91260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6662,10 +6667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611593</v>
+        <v>611650</v>
       </c>
       <c r="R61" t="n">
-        <v>7203711</v>
+        <v>7203647</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6724,10 +6729,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125780620</v>
+        <v>125779869</v>
       </c>
       <c r="B62" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6735,39 +6740,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611381</v>
+        <v>611687</v>
       </c>
       <c r="R62" t="n">
-        <v>7203809</v>
+        <v>7203684</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6814,44 +6814,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779850</v>
+        <v>125779867</v>
       </c>
       <c r="B63" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611637</v>
+        <v>611694</v>
       </c>
       <c r="R63" t="n">
-        <v>7203685</v>
+        <v>7203678</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6923,10 +6923,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125776365</v>
+        <v>125779842</v>
       </c>
       <c r="B64" t="n">
-        <v>98373</v>
+        <v>80109</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6934,21 +6934,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611567</v>
+        <v>611593</v>
       </c>
       <c r="R64" t="n">
-        <v>7203714</v>
+        <v>7203711</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7008,12 +7008,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7832,45 +7832,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125779312</v>
+        <v>125779880</v>
       </c>
       <c r="B73" t="n">
-        <v>98373</v>
+        <v>91260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>611683</v>
+        <v>611743</v>
       </c>
       <c r="R73" t="n">
-        <v>7203677</v>
+        <v>7203706</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7917,44 +7917,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779310</v>
+        <v>125779340</v>
       </c>
       <c r="B74" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7964,10 +7964,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611700</v>
+        <v>611680</v>
       </c>
       <c r="R74" t="n">
-        <v>7203703</v>
+        <v>7203713</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779880</v>
+        <v>125779771</v>
       </c>
       <c r="B75" t="n">
-        <v>91260</v>
+        <v>80080</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8037,21 +8037,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8061,10 +8061,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611743</v>
+        <v>611686</v>
       </c>
       <c r="R75" t="n">
-        <v>7203706</v>
+        <v>7203685</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,44 +8111,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779340</v>
+        <v>125779312</v>
       </c>
       <c r="B76" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611680</v>
+        <v>611683</v>
       </c>
       <c r="R76" t="n">
-        <v>7203713</v>
+        <v>7203677</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,45 +8220,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779771</v>
+        <v>125779310</v>
       </c>
       <c r="B77" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611686</v>
+        <v>611700</v>
       </c>
       <c r="R77" t="n">
-        <v>7203685</v>
+        <v>7203703</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8305,12 +8305,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125781650</v>
+        <v>125776368</v>
       </c>
       <c r="B84" t="n">
-        <v>91611</v>
+        <v>91816</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8920,37 +8920,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1506</v>
+        <v>760</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611521</v>
+        <v>611705</v>
       </c>
       <c r="R84" t="n">
-        <v>7203626</v>
+        <v>7203679</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,19 +8977,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9004,60 +8994,65 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125776368</v>
+        <v>125781638</v>
       </c>
       <c r="B85" t="n">
-        <v>91816</v>
+        <v>57656</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611705</v>
+        <v>611645</v>
       </c>
       <c r="R85" t="n">
-        <v>7203679</v>
+        <v>7203676</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9084,9 +9079,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9101,57 +9106,65 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Isac Enetjärn, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125779873</v>
+        <v>125779347</v>
       </c>
       <c r="B86" t="n">
-        <v>80116</v>
+        <v>57656</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611693</v>
+        <v>611688</v>
       </c>
       <c r="R86" t="n">
-        <v>7203707</v>
+        <v>7203713</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9186,6 +9199,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9198,62 +9216,57 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125781638</v>
+        <v>125781650</v>
       </c>
       <c r="B87" t="n">
-        <v>57656</v>
+        <v>91611</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611645</v>
+        <v>611521</v>
       </c>
       <c r="R87" t="n">
-        <v>7203676</v>
+        <v>7203626</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9285,7 +9298,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9295,7 +9308,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9322,53 +9335,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125779347</v>
+        <v>125779873</v>
       </c>
       <c r="B88" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611688</v>
+        <v>611693</v>
       </c>
       <c r="R88" t="n">
-        <v>7203713</v>
+        <v>7203707</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9403,11 +9408,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,12 +9420,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10014,10 +10014,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779302</v>
+        <v>125779885</v>
       </c>
       <c r="B95" t="n">
-        <v>91242</v>
+        <v>78977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,34 +10025,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611618</v>
+        <v>611661</v>
       </c>
       <c r="R95" t="n">
-        <v>7203674</v>
+        <v>7203604</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10099,22 +10099,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779885</v>
+        <v>125779302</v>
       </c>
       <c r="B96" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10122,34 +10122,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611661</v>
+        <v>611618</v>
       </c>
       <c r="R96" t="n">
-        <v>7203604</v>
+        <v>7203674</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10196,12 +10196,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125776148</v>
+        <v>125779345</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611660</v>
+        <v>611661</v>
       </c>
       <c r="R2" t="n">
-        <v>7203684</v>
+        <v>7203650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +756,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -760,19 +773,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125776367</v>
+        <v>125776148</v>
       </c>
       <c r="B3" t="n">
         <v>78977</v>
@@ -803,14 +816,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611653</v>
+        <v>611660</v>
       </c>
       <c r="R3" t="n">
-        <v>7203665</v>
+        <v>7203684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +870,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125779334</v>
+        <v>125776367</v>
       </c>
       <c r="B4" t="n">
         <v>78977</v>
@@ -900,14 +913,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611526</v>
+        <v>611653</v>
       </c>
       <c r="R4" t="n">
-        <v>7203706</v>
+        <v>7203665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +967,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125779345</v>
+        <v>125779334</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611661</v>
+        <v>611526</v>
       </c>
       <c r="R5" t="n">
-        <v>7203650</v>
+        <v>7203706</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,11 +1050,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1601,48 +1601,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125779322</v>
+        <v>125781637</v>
       </c>
       <c r="B11" t="n">
-        <v>80108</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611700</v>
+        <v>611631</v>
       </c>
       <c r="R11" t="n">
-        <v>7203701</v>
+        <v>7203695</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,9 +1674,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,22 +1701,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125779769</v>
+        <v>125780615</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1709,34 +1724,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611696</v>
+        <v>611292</v>
       </c>
       <c r="R12" t="n">
-        <v>7203681</v>
+        <v>7203703</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,12 +1783,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1783,57 +1803,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125779323</v>
+        <v>125776139</v>
       </c>
       <c r="B13" t="n">
-        <v>80108</v>
+        <v>80081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611667</v>
+        <v>611678</v>
       </c>
       <c r="R13" t="n">
-        <v>7203673</v>
+        <v>7203688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1880,65 +1900,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125781637</v>
+        <v>125779322</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>80108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611631</v>
+        <v>611700</v>
       </c>
       <c r="R14" t="n">
-        <v>7203695</v>
+        <v>7203701</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1965,19 +1980,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1992,22 +1997,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125780615</v>
+        <v>125781663</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2015,42 +2020,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611292</v>
+        <v>611570</v>
       </c>
       <c r="R15" t="n">
-        <v>7203703</v>
+        <v>7203700</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2074,12 +2074,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,17 +2109,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125781663</v>
+        <v>125779769</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2117,37 +2127,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611570</v>
+        <v>611696</v>
       </c>
       <c r="R16" t="n">
-        <v>7203700</v>
+        <v>7203681</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2174,19 +2184,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,57 +2201,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125776139</v>
+        <v>125779323</v>
       </c>
       <c r="B17" t="n">
-        <v>80081</v>
+        <v>80108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611678</v>
+        <v>611667</v>
       </c>
       <c r="R17" t="n">
-        <v>7203688</v>
+        <v>7203673</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125776366</v>
+        <v>125779311</v>
       </c>
       <c r="B19" t="n">
         <v>98373</v>
@@ -2451,11 +2451,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611679</v>
+        <v>611690</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2505,19 +2505,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125779311</v>
+        <v>125776366</v>
       </c>
       <c r="B20" t="n">
         <v>98373</v>
@@ -2548,11 +2548,11 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611690</v>
+        <v>611679</v>
       </c>
       <c r="R20" t="n">
         <v>7203691</v>
@@ -2602,44 +2602,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125780622</v>
+        <v>125780607</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>80081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611490</v>
+        <v>611445</v>
       </c>
       <c r="R21" t="n">
-        <v>7203838</v>
+        <v>7203816</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125780607</v>
+        <v>125779317</v>
       </c>
       <c r="B24" t="n">
-        <v>80081</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,34 +2916,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611445</v>
+        <v>611723</v>
       </c>
       <c r="R24" t="n">
-        <v>7203816</v>
+        <v>7203703</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,12 +2978,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2990,65 +3003,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125779317</v>
+        <v>125780622</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>611723</v>
+        <v>611490</v>
       </c>
       <c r="R25" t="n">
-        <v>7203703</v>
+        <v>7203838</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3075,17 +3080,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,60 +3100,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125779767</v>
+        <v>125781660</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>91256</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611673</v>
+        <v>611570</v>
       </c>
       <c r="R26" t="n">
-        <v>7203670</v>
+        <v>7203708</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3180,9 +3180,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,60 +3207,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125781660</v>
+        <v>125779886</v>
       </c>
       <c r="B27" t="n">
-        <v>91256</v>
+        <v>91816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611570</v>
+        <v>611704</v>
       </c>
       <c r="R27" t="n">
-        <v>7203708</v>
+        <v>7203679</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3277,19 +3287,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3304,44 +3304,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125779886</v>
+        <v>125779763</v>
       </c>
       <c r="B28" t="n">
-        <v>91816</v>
+        <v>80109</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3351,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611704</v>
+        <v>611644</v>
       </c>
       <c r="R28" t="n">
-        <v>7203679</v>
+        <v>7203694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,22 +3401,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125776147</v>
+        <v>125780614</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3424,34 +3424,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611642</v>
+        <v>611292</v>
       </c>
       <c r="R29" t="n">
-        <v>7203689</v>
+        <v>7203687</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3478,12 +3483,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3498,22 +3503,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125779763</v>
+        <v>125779767</v>
       </c>
       <c r="B30" t="n">
-        <v>80109</v>
+        <v>98373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3521,21 +3526,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3545,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611644</v>
+        <v>611673</v>
       </c>
       <c r="R30" t="n">
-        <v>7203694</v>
+        <v>7203670</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3704,10 +3709,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125780614</v>
+        <v>125776147</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3715,39 +3720,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611292</v>
+        <v>611642</v>
       </c>
       <c r="R32" t="n">
-        <v>7203687</v>
+        <v>7203689</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,19 +3794,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125781666</v>
+        <v>125779884</v>
       </c>
       <c r="B33" t="n">
         <v>78977</v>
@@ -3837,17 +3837,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611652</v>
+        <v>611666</v>
       </c>
       <c r="R33" t="n">
-        <v>7203680</v>
+        <v>7203678</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,19 +3874,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3901,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125779834</v>
+        <v>125780606</v>
       </c>
       <c r="B34" t="n">
-        <v>75072</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3924,34 +3914,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611547</v>
+        <v>611311</v>
       </c>
       <c r="R34" t="n">
-        <v>7203635</v>
+        <v>7203689</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3978,12 +3968,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3998,19 +3988,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125779884</v>
+        <v>125781666</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -4041,17 +4031,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611666</v>
+        <v>611652</v>
       </c>
       <c r="R35" t="n">
-        <v>7203678</v>
+        <v>7203680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4078,9 +4068,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,12 +4095,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125780606</v>
+        <v>125779834</v>
       </c>
       <c r="B37" t="n">
-        <v>80080</v>
+        <v>75072</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,34 +4215,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611311</v>
+        <v>611547</v>
       </c>
       <c r="R37" t="n">
-        <v>7203689</v>
+        <v>7203635</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,12 +4289,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4398,53 +4398,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125779319</v>
+        <v>125779844</v>
       </c>
       <c r="B39" t="n">
-        <v>57656</v>
+        <v>80109</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>611663</v>
+        <v>611644</v>
       </c>
       <c r="R39" t="n">
-        <v>7203613</v>
+        <v>7203690</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4479,11 +4471,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4496,65 +4483,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125779316</v>
+        <v>125779773</v>
       </c>
       <c r="B40" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>611507</v>
+        <v>611662</v>
       </c>
       <c r="R40" t="n">
-        <v>7203685</v>
+        <v>7203612</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4589,11 +4568,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4606,22 +4580,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125779318</v>
+        <v>125779337</v>
       </c>
       <c r="B41" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,42 +4603,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>611725</v>
+        <v>611615</v>
       </c>
       <c r="R41" t="n">
-        <v>7203707</v>
+        <v>7203678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,11 +4663,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4728,10 +4689,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125779337</v>
+        <v>125779319</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4739,34 +4700,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>611615</v>
+        <v>611663</v>
       </c>
       <c r="R42" t="n">
-        <v>7203678</v>
+        <v>7203613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4799,6 +4768,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4825,45 +4799,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125779844</v>
+        <v>125779316</v>
       </c>
       <c r="B43" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>611644</v>
+        <v>611507</v>
       </c>
       <c r="R43" t="n">
-        <v>7203690</v>
+        <v>7203685</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4898,6 +4880,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4910,57 +4897,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125779773</v>
+        <v>125779318</v>
       </c>
       <c r="B44" t="n">
-        <v>80116</v>
+        <v>57656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>611662</v>
+        <v>611725</v>
       </c>
       <c r="R44" t="n">
-        <v>7203612</v>
+        <v>7203707</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,6 +4990,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5007,12 +5007,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5634,32 +5634,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779343</v>
+        <v>125779309</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611670</v>
+        <v>611679</v>
       </c>
       <c r="R51" t="n">
-        <v>7203656</v>
+        <v>7203682</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779863</v>
+        <v>125779343</v>
       </c>
       <c r="B53" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5839,42 +5839,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611623</v>
+        <v>611670</v>
       </c>
       <c r="R53" t="n">
-        <v>7203692</v>
+        <v>7203656</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5909,11 +5901,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5926,57 +5913,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125779309</v>
+        <v>125779863</v>
       </c>
       <c r="B54" t="n">
-        <v>80109</v>
+        <v>57656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>611679</v>
+        <v>611623</v>
       </c>
       <c r="R54" t="n">
-        <v>7203682</v>
+        <v>7203692</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6011,6 +6006,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6023,62 +6023,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125780620</v>
+        <v>125779320</v>
       </c>
       <c r="B55" t="n">
-        <v>57656</v>
+        <v>91611</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611381</v>
+        <v>611543</v>
       </c>
       <c r="R55" t="n">
-        <v>7203809</v>
+        <v>7203697</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6105,12 +6100,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6125,60 +6120,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125779850</v>
+        <v>125781664</v>
       </c>
       <c r="B56" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611637</v>
+        <v>611539</v>
       </c>
       <c r="R56" t="n">
-        <v>7203685</v>
+        <v>7203643</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6205,9 +6200,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6222,44 +6227,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125776365</v>
+        <v>125779869</v>
       </c>
       <c r="B57" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6269,10 +6274,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611567</v>
+        <v>611687</v>
       </c>
       <c r="R57" t="n">
-        <v>7203714</v>
+        <v>7203684</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6319,57 +6324,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779320</v>
+        <v>125779867</v>
       </c>
       <c r="B58" t="n">
-        <v>91611</v>
+        <v>80080</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1506</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611543</v>
+        <v>611694</v>
       </c>
       <c r="R58" t="n">
-        <v>7203697</v>
+        <v>7203678</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6416,19 +6421,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125781664</v>
+        <v>125779344</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6463,13 +6468,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611539</v>
+        <v>611653</v>
       </c>
       <c r="R59" t="n">
-        <v>7203643</v>
+        <v>7203626</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6496,19 +6501,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6523,57 +6518,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779344</v>
+        <v>125779842</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611653</v>
+        <v>611593</v>
       </c>
       <c r="R60" t="n">
-        <v>7203626</v>
+        <v>7203711</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6620,22 +6615,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125779881</v>
+        <v>125780620</v>
       </c>
       <c r="B61" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6643,34 +6638,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611650</v>
+        <v>611381</v>
       </c>
       <c r="R61" t="n">
-        <v>7203647</v>
+        <v>7203809</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6697,12 +6697,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6717,44 +6717,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779869</v>
+        <v>125779850</v>
       </c>
       <c r="B62" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611687</v>
+        <v>611637</v>
       </c>
       <c r="R62" t="n">
-        <v>7203684</v>
+        <v>7203685</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6826,10 +6826,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125779867</v>
+        <v>125779881</v>
       </c>
       <c r="B63" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6837,21 +6837,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>611694</v>
+        <v>611650</v>
       </c>
       <c r="R63" t="n">
-        <v>7203678</v>
+        <v>7203647</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6923,10 +6923,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125779842</v>
+        <v>125776365</v>
       </c>
       <c r="B64" t="n">
-        <v>80109</v>
+        <v>98373</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6934,21 +6934,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>611593</v>
+        <v>611567</v>
       </c>
       <c r="R64" t="n">
-        <v>7203711</v>
+        <v>7203714</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7008,12 +7008,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7436,52 +7436,52 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125776142</v>
+        <v>125779339</v>
       </c>
       <c r="B69" t="n">
-        <v>91816</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>611684</v>
+        <v>611640</v>
       </c>
       <c r="R69" t="n">
-        <v>7203683</v>
+        <v>7203677</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7528,57 +7528,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125779339</v>
+        <v>125776142</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>91816</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>611640</v>
+        <v>611684</v>
       </c>
       <c r="R70" t="n">
-        <v>7203677</v>
+        <v>7203683</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7625,12 +7625,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125779340</v>
+        <v>125779771</v>
       </c>
       <c r="B74" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7940,34 +7940,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>611680</v>
+        <v>611686</v>
       </c>
       <c r="R74" t="n">
-        <v>7203713</v>
+        <v>7203685</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8014,57 +8014,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125779771</v>
+        <v>125779312</v>
       </c>
       <c r="B75" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>611686</v>
+        <v>611683</v>
       </c>
       <c r="R75" t="n">
-        <v>7203685</v>
+        <v>7203677</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8111,19 +8111,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125779312</v>
+        <v>125779310</v>
       </c>
       <c r="B76" t="n">
         <v>98373</v>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>611683</v>
+        <v>611700</v>
       </c>
       <c r="R76" t="n">
-        <v>7203677</v>
+        <v>7203703</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8220,32 +8220,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125779310</v>
+        <v>125779340</v>
       </c>
       <c r="B77" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>611700</v>
+        <v>611680</v>
       </c>
       <c r="R77" t="n">
-        <v>7203703</v>
+        <v>7203713</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8317,10 +8317,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125779875</v>
+        <v>125781627</v>
       </c>
       <c r="B78" t="n">
-        <v>80116</v>
+        <v>91207</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8328,37 +8328,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>611687</v>
+        <v>611526</v>
       </c>
       <c r="R78" t="n">
-        <v>7203684</v>
+        <v>7203708</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8385,9 +8385,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8402,22 +8412,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125779307</v>
+        <v>125779875</v>
       </c>
       <c r="B79" t="n">
-        <v>80109</v>
+        <v>80116</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8425,34 +8435,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>611707</v>
+        <v>611687</v>
       </c>
       <c r="R79" t="n">
-        <v>7203701</v>
+        <v>7203684</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8499,22 +8509,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125781627</v>
+        <v>125779307</v>
       </c>
       <c r="B80" t="n">
-        <v>91207</v>
+        <v>80109</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8522,21 +8532,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8546,13 +8556,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>611526</v>
+        <v>611707</v>
       </c>
       <c r="R80" t="n">
-        <v>7203708</v>
+        <v>7203701</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8579,19 +8589,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:36</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8606,12 +8606,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125776368</v>
+        <v>125781650</v>
       </c>
       <c r="B84" t="n">
-        <v>91816</v>
+        <v>91611</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8920,37 +8920,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>760</v>
+        <v>1506</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>611705</v>
+        <v>611521</v>
       </c>
       <c r="R84" t="n">
-        <v>7203679</v>
+        <v>7203626</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8977,9 +8977,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8994,65 +9004,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125781638</v>
+        <v>125776368</v>
       </c>
       <c r="B85" t="n">
-        <v>57656</v>
+        <v>91816</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>611645</v>
+        <v>611705</v>
       </c>
       <c r="R85" t="n">
-        <v>7203676</v>
+        <v>7203679</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9079,19 +9084,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9106,65 +9101,57 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125779347</v>
+        <v>125779873</v>
       </c>
       <c r="B86" t="n">
-        <v>57656</v>
+        <v>80116</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>611688</v>
+        <v>611693</v>
       </c>
       <c r="R86" t="n">
-        <v>7203713</v>
+        <v>7203707</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9199,11 +9186,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9216,57 +9198,62 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125781650</v>
+        <v>125781638</v>
       </c>
       <c r="B87" t="n">
-        <v>91611</v>
+        <v>57656</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>611521</v>
+        <v>611645</v>
       </c>
       <c r="R87" t="n">
-        <v>7203626</v>
+        <v>7203676</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9298,7 +9285,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9308,7 +9295,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9328,52 +9315,60 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Isac Enetjärn, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125779873</v>
+        <v>125779347</v>
       </c>
       <c r="B88" t="n">
-        <v>80116</v>
+        <v>57656</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>611693</v>
+        <v>611688</v>
       </c>
       <c r="R88" t="n">
-        <v>7203707</v>
+        <v>7203713</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9408,6 +9403,11 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9420,12 +9420,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9626,10 +9626,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125779852</v>
+        <v>125776127</v>
       </c>
       <c r="B91" t="n">
-        <v>98373</v>
+        <v>80116</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9637,31 +9637,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>611711</v>
+        <v>611681</v>
       </c>
       <c r="R91" t="n">
         <v>7203685</v>
@@ -9711,22 +9711,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125776127</v>
+        <v>125779764</v>
       </c>
       <c r="B92" t="n">
-        <v>80116</v>
+        <v>80109</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9734,34 +9734,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>611681</v>
+        <v>611648</v>
       </c>
       <c r="R92" t="n">
-        <v>7203685</v>
+        <v>7203687</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9808,19 +9808,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125779764</v>
+        <v>125779846</v>
       </c>
       <c r="B93" t="n">
         <v>80109</v>
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>611648</v>
+        <v>611717</v>
       </c>
       <c r="R93" t="n">
-        <v>7203687</v>
+        <v>7203689</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9905,22 +9905,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125779846</v>
+        <v>125779852</v>
       </c>
       <c r="B94" t="n">
-        <v>80109</v>
+        <v>98373</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9928,21 +9928,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9952,10 +9952,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>611717</v>
+        <v>611711</v>
       </c>
       <c r="R94" t="n">
-        <v>7203689</v>
+        <v>7203685</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10014,10 +10014,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125779885</v>
+        <v>125779302</v>
       </c>
       <c r="B95" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10025,34 +10025,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>611661</v>
+        <v>611618</v>
       </c>
       <c r="R95" t="n">
-        <v>7203604</v>
+        <v>7203674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10099,44 +10099,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125779302</v>
+        <v>125779314</v>
       </c>
       <c r="B96" t="n">
-        <v>91242</v>
+        <v>98373</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>611618</v>
+        <v>611663</v>
       </c>
       <c r="R96" t="n">
-        <v>7203674</v>
+        <v>7203673</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10208,10 +10208,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125779349</v>
+        <v>125779885</v>
       </c>
       <c r="B97" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10219,42 +10219,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>611652</v>
+        <v>611661</v>
       </c>
       <c r="R97" t="n">
-        <v>7203627</v>
+        <v>7203604</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10289,11 +10281,6 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -10306,57 +10293,65 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125779314</v>
+        <v>125779349</v>
       </c>
       <c r="B98" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>611663</v>
+        <v>611652</v>
       </c>
       <c r="R98" t="n">
-        <v>7203673</v>
+        <v>7203627</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10389,6 +10384,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10415,45 +10415,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125779851</v>
+        <v>125779329</v>
       </c>
       <c r="B99" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>611690</v>
+        <v>611623</v>
       </c>
       <c r="R99" t="n">
-        <v>7203710</v>
+        <v>7203677</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10500,57 +10500,57 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125779299</v>
+        <v>125779772</v>
       </c>
       <c r="B100" t="n">
-        <v>75072</v>
+        <v>80116</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>611561</v>
+        <v>611680</v>
       </c>
       <c r="R100" t="n">
-        <v>7203692</v>
+        <v>7203679</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10597,22 +10597,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125779329</v>
+        <v>125779299</v>
       </c>
       <c r="B101" t="n">
-        <v>80080</v>
+        <v>75072</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10620,21 +10620,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10644,10 +10644,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>611623</v>
+        <v>611561</v>
       </c>
       <c r="R101" t="n">
-        <v>7203677</v>
+        <v>7203692</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10706,10 +10706,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125779772</v>
+        <v>125779851</v>
       </c>
       <c r="B102" t="n">
-        <v>80116</v>
+        <v>98373</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10717,21 +10717,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>611680</v>
+        <v>611690</v>
       </c>
       <c r="R102" t="n">
-        <v>7203679</v>
+        <v>7203710</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10791,12 +10791,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10905,10 +10905,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125803917</v>
+        <v>125803940</v>
       </c>
       <c r="B104" t="n">
-        <v>91260</v>
+        <v>91238</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10916,21 +10916,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10947,10 +10947,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>611560</v>
+        <v>611534</v>
       </c>
       <c r="R104" t="n">
-        <v>7203700</v>
+        <v>7203710</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11010,10 +11010,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125803940</v>
+        <v>125803917</v>
       </c>
       <c r="B105" t="n">
-        <v>91238</v>
+        <v>91260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11021,21 +11021,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11052,10 +11052,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>611534</v>
+        <v>611560</v>
       </c>
       <c r="R105" t="n">
-        <v>7203710</v>
+        <v>7203700</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>

--- a/artfynd/A 59975-2024 artfynd.xlsx
+++ b/artfynd/A 59975-2024 artfynd.xlsx
@@ -1601,53 +1601,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125781637</v>
+        <v>125779322</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>80108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611631</v>
+        <v>611700</v>
       </c>
       <c r="R11" t="n">
-        <v>7203695</v>
+        <v>7203701</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,19 +1669,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1701,22 +1686,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125780615</v>
+        <v>125781663</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1724,42 +1709,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611292</v>
+        <v>611570</v>
       </c>
       <c r="R12" t="n">
-        <v>7203703</v>
+        <v>7203700</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1783,12 +1763,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1808,17 +1798,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125776139</v>
+        <v>125779769</v>
       </c>
       <c r="B13" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1826,34 +1816,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gunnarn 07JUN2025, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611678</v>
+        <v>611696</v>
       </c>
       <c r="R13" t="n">
-        <v>7203688</v>
+        <v>7203681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,19 +1890,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125779322</v>
+        <v>125779323</v>
       </c>
       <c r="B14" t="n">
         <v>80108</v>
@@ -1947,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611700</v>
+        <v>611667</v>
       </c>
       <c r="R14" t="n">
-        <v>7203701</v>
+        <v>7203673</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,10 +1999,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125781663</v>
+        <v>125776139</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2020,37 +2010,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn 07JUN2025, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611570</v>
+        <v>611678</v>
       </c>
       <c r="R15" t="n">
-        <v>7203700</v>
+        <v>7203688</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2077,19 +2067,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2104,22 +2084,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125779769</v>
+        <v>125781637</v>
       </c>
       <c r="B16" t="n">
-        <v>80080</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2127,37 +2107,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611696</v>
+        <v>611631</v>
       </c>
       <c r="R16" t="n">
-        <v>7203681</v>
+        <v>7203695</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2184,9 +2169,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,57 +2196,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125779323</v>
+        <v>125780615</v>
       </c>
       <c r="B17" t="n">
-        <v>80108</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611667</v>
+        <v>611292</v>
       </c>
       <c r="R17" t="n">
-        <v>7203673</v>
+        <v>7203703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125779311</v>
+        <v>125776366</v>
       </c>
       <c r="B19" t="n">
         <v>98373</v>
@@ -2451,11 +2451,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611690</v>
+        <v>611679</v>
       </c>
       <c r="R19" t="n">
         <v>7203691</v>
@@ -2505,19 +2505,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125776366</v>
+        <v>125779311</v>
       </c>
       <c r="B20" t="n">
         <v>98373</v>
@@ -2548,11 +2548,11 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611679</v>
+        <v>611690</v>
       </c>
       <c r="R20" t="n">
         <v>7203691</v>
@@ -2602,22 +2602,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125780607</v>
+        <v>125779338</v>
       </c>
       <c r="B21" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,21 +2625,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611445</v>
+        <v>611631</v>
       </c>
       <c r="R21" t="n">
-        <v>7203816</v>
+        <v>7203681</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2699,22 +2699,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125779336</v>
+        <v>125779317</v>
       </c>
       <c r="B22" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2722,34 +2722,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611575</v>
+        <v>611723</v>
       </c>
       <c r="R22" t="n">
-        <v>7203712</v>
+        <v>7203703</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,6 +2790,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2808,10 +2821,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125779338</v>
+        <v>125780607</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,21 +2832,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2843,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611631</v>
+        <v>611445</v>
       </c>
       <c r="R23" t="n">
-        <v>7203681</v>
+        <v>7203816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2873,12 +2886,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2893,22 +2906,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125779317</v>
+        <v>125779336</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2916,42 +2929,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611723</v>
+        <v>611575</v>
       </c>
       <c r="R24" t="n">
-        <v>7203703</v>
+        <v>7203712</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2984,11 +2989,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125779884</v>
+        <v>125780608</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,34 +3817,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611666</v>
+        <v>611445</v>
       </c>
       <c r="R33" t="n">
-        <v>7203678</v>
+        <v>7203816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125780606</v>
+        <v>125779884</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,34 +3914,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>611311</v>
+        <v>611666</v>
       </c>
       <c r="R34" t="n">
-        <v>7203689</v>
+        <v>7203678</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3968,12 +3968,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,22 +3988,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125781666</v>
+        <v>125780606</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>611652</v>
+        <v>611311</v>
       </c>
       <c r="R35" t="n">
-        <v>7203680</v>
+        <v>7203689</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4065,22 +4065,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:58</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4100,52 +4090,52 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Yasmine Kindlund, Greger Thorsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125780608</v>
+        <v>125779848</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>611445</v>
+        <v>611545</v>
       </c>
       <c r="R36" t="n">
-        <v>7203816</v>
+        <v>7203710</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4172,12 +4162,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,22 +4182,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125779834</v>
+        <v>125781666</v>
       </c>
       <c r="B37" t="n">
-        <v>75072</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,37 +4205,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>611547</v>
+        <v>611652</v>
       </c>
       <c r="R37" t="n">
-        <v>7203635</v>
+        <v>7203680</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4272,9 +4262,19 @@
           <t>2025-06-07</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,44 +4289,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Yasmine Kindlund, Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125779848</v>
+        <v>125779834</v>
       </c>
       <c r="B38" t="n">
-        <v>98373</v>
+        <v>75072</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>611545</v>
+        <v>611547</v>
       </c>
       <c r="R38" t="n">
-        <v>7203710</v>
+        <v>7203635</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125779309</v>
+        <v>125779876</v>
       </c>
       <c r="B51" t="n">
-        <v>80109</v>
+        <v>80116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,34 +5645,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>611679</v>
+        <v>611661</v>
       </c>
       <c r="R51" t="n">
-        <v>7203682</v>
+        <v>7203604</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5719,57 +5719,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125779876</v>
+        <v>125779343</v>
       </c>
       <c r="B52" t="n">
-        <v>80116</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>611661</v>
+        <v>611670</v>
       </c>
       <c r="R52" t="n">
-        <v>7203604</v>
+        <v>7203656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5816,44 +5816,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125779343</v>
+        <v>125779309</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>80109</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5863,10 +5863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>611670</v>
+        <v>611679</v>
       </c>
       <c r="R53" t="n">
-        <v>7203656</v>
+        <v>7203682</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6035,45 +6035,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125779320</v>
+        <v>125779869</v>
       </c>
       <c r="B55" t="n">
-        <v>91611</v>
+        <v>80080</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1506</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>611543</v>
+        <v>611687</v>
       </c>
       <c r="R55" t="n">
-        <v>7203697</v>
+        <v>7203684</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6120,22 +6120,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125781664</v>
+        <v>125779867</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6143,37 +6143,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>611539</v>
+        <v>611694</v>
       </c>
       <c r="R56" t="n">
-        <v>7203643</v>
+        <v>7203678</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6200,19 +6200,9 @@
           <t>2025-06-07</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-06-07</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6227,22 +6217,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125779869</v>
+        <v>125779344</v>
       </c>
       <c r="B57" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6250,34 +6240,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>611687</v>
+        <v>611653</v>
       </c>
       <c r="R57" t="n">
-        <v>7203684</v>
+        <v>7203626</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6324,44 +6314,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125779867</v>
+        <v>125779842</v>
       </c>
       <c r="B58" t="n">
-        <v>80080</v>
+        <v>80109</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6371,10 +6361,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>611694</v>
+        <v>611593</v>
       </c>
       <c r="R58" t="n">
-        <v>7203678</v>
+        <v>7203711</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6433,45 +6423,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125779344</v>
+        <v>125779850</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>611653</v>
+        <v>611637</v>
       </c>
       <c r="R59" t="n">
-        <v>7203626</v>
+        <v>7203685</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6518,57 +6508,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125779842</v>
+        <v>125779320</v>
       </c>
       <c r="B60" t="n">
-        <v>80109</v>
+        <v>91611</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>1506</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>611593</v>
+        <v>611543</v>
       </c>
       <c r="R60" t="n">
-        <v>7203711</v>
+        <v>7203697</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6615,22 +6605,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125780620</v>
+        <v>125779881</v>
       </c>
       <c r="B61" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6638,39 +6628,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Liden, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>611381</v>
+        <v>611650</v>
       </c>
       <c r="R61" t="n">
-        <v>7203809</v>
+        <v>7203647</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6697,12 +6682,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6717,60 +6702,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Greger Thorsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125779850</v>
+        <v>125781664</v>
       </c>
       <c r="B62" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>Liden, Ly lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>611637</v>
+        <v>611539</v>
       </c>
       <c r="R62" t="n">
-        <v>7203685</v>
+        <v>7203643</v>
       </c>
       <c r="S